--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4522" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6CA305B-F91A-475B-BD75-B1AB0BE7BB8B}"/>
+  <xr:revisionPtr revIDLastSave="4534" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCED55E-7A8A-41A0-AE3B-0B4388F9A205}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
@@ -186,13 +186,13 @@
     <t>SoRoSim get_distal_value (lambda = 0.5)</t>
   </si>
   <si>
-    <t>SoRoSim get_distal_value (lambda = 1)</t>
-  </si>
-  <si>
     <t>SoRoSim get_distal_value (lambda = 1.5)</t>
   </si>
   <si>
     <t>ABS Distal Errors</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (lambda = 1)</t>
   </si>
 </sst>
 </file>
@@ -520,6 +520,9 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -530,9 +533,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -557,6 +557,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1713,11 +1717,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="T1" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -2754,11 +2758,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="T1" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -3727,11 +3731,11 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -5201,7 +5205,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="26"/>
@@ -5211,11 +5215,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="T1" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -5343,40 +5347,40 @@
         <v>0.34822303056716902</v>
       </c>
       <c r="M3" s="8">
-        <v>0.67139851672735462</v>
+        <v>0.40202965392158824</v>
       </c>
       <c r="N3" s="8">
-        <v>3.4795027648084176E-2</v>
+        <v>6.9789383849933759E-2</v>
       </c>
       <c r="O3" s="8">
-        <v>1.5830132450241412</v>
+        <v>1.58612318996072</v>
       </c>
       <c r="P3" s="8">
-        <v>5.3575615578369924E-7</v>
+        <v>1.6932000391698518E-4</v>
       </c>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>0.2713985167273546</v>
+        <v>2.0296539215882148E-3</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>-2.5204972351915822E-2</v>
+        <v>9.789383849933761E-3</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>1.2216918229244644E-2</v>
+        <v>1.5326863165823434E-2</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>0.2713985167273546</v>
+        <v>2.0296539215882148E-3</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
-        <v>2.5204972351915822E-2</v>
+        <v>9.789383849933761E-3</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>1.2216918229244644E-2</v>
+        <v>1.5326863165823434E-2</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -5438,52 +5442,52 @@
         <v>0.83409011363983199</v>
       </c>
       <c r="M4" s="8">
-        <v>0.55144834519266395</v>
+        <v>0.75713708359141785</v>
       </c>
       <c r="N4" s="8">
-        <v>0.10242924549222791</v>
+        <v>7.2421632945224593E-2</v>
       </c>
       <c r="O4" s="8">
-        <v>1.5854732614991216</v>
+        <v>1.5945817689101296</v>
       </c>
       <c r="P4" s="8">
-        <v>3.8208402130965473E-6</v>
+        <v>4.7490785077414997E-4</v>
       </c>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
-        <v>-0.2485516548073361</v>
+        <v>-4.2862916408582197E-2</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="1"/>
-        <v>4.2429245492227916E-2</v>
+        <v>1.2421632945224595E-2</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" si="1"/>
-        <v>1.4676934704225042E-2</v>
+        <v>2.3785442115233035E-2</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
-        <v>0.2485516548073361</v>
+        <v>4.2862916408582197E-2</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
-        <v>4.2429245492227916E-2</v>
+        <v>1.2421632945224595E-2</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>1.4676934704225042E-2</v>
+        <v>2.3785442115233035E-2</v>
       </c>
       <c r="W4" s="6" cm="1">
         <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.16406272325683752</v>
+        <v>2.3919911823198969E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
         <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>2.2452223951200032E-2</v>
+        <v>1.0326971317622804E-2</v>
       </c>
       <c r="Y4" s="6" cm="1">
         <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.805955078829562E-2</v>
+        <v>1.3631851876260814E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -5536,40 +5540,40 @@
         <v>0.269099742174149</v>
       </c>
       <c r="M5" s="8">
-        <v>0.77717545948473432</v>
+        <v>0.27154159433860381</v>
       </c>
       <c r="N5" s="8">
-        <v>3.0780918699422528E-2</v>
+        <v>8.7965747246715797E-2</v>
       </c>
       <c r="O5" s="8">
-        <v>1.5769468036762846</v>
+        <v>1.5813627191821027</v>
       </c>
       <c r="P5" s="8">
-        <v>1.9178444258213873E-7</v>
+        <v>2.4160611469808265E-5</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>0.47717545948473433</v>
+        <v>-2.845840566139618E-2</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="1"/>
-        <v>-4.9219081300577477E-2</v>
+        <v>7.9657472467157958E-3</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="1"/>
-        <v>6.1504768813880339E-3</v>
+        <v>1.0566392387206136E-2</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="2"/>
-        <v>0.47717545948473433</v>
+        <v>2.845840566139618E-2</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>4.9219081300577477E-2</v>
+        <v>7.9657472467157958E-3</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="0"/>
-        <v>6.1504768813880339E-3</v>
+        <v>1.0566392387206136E-2</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -5625,40 +5629,40 @@
         <v>0.47075057029724099</v>
       </c>
       <c r="M6" s="8">
-        <v>0.45505299733126359</v>
+        <v>0.47465787170457124</v>
       </c>
       <c r="N6" s="8">
-        <v>0.11586360002160032</v>
+        <v>0.11103571411521253</v>
       </c>
       <c r="O6" s="8">
-        <v>1.5886582899741697</v>
+        <v>1.5881187616702976</v>
       </c>
       <c r="P6" s="8">
-        <v>1.6934356118565107E-6</v>
+        <v>3.7665609979489553E-5</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-4.4947002668736413E-2</v>
+        <v>-2.5342128295428756E-2</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>1.586360002160031E-2</v>
+        <v>1.1035714115212522E-2</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="1"/>
-        <v>1.7861963179273133E-2</v>
+        <v>1.7322434875401083E-2</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="2"/>
-        <v>4.4947002668736413E-2</v>
+        <v>2.5342128295428756E-2</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>1.586360002160031E-2</v>
+        <v>1.1035714115212522E-2</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="0"/>
-        <v>1.7861963179273133E-2</v>
+        <v>1.7322434875401083E-2</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -5711,40 +5715,40 @@
         <v>0.69233715534210205</v>
       </c>
       <c r="M7" s="8">
-        <v>0.88640925397311576</v>
+        <v>0.69137551224771843</v>
       </c>
       <c r="N7" s="8">
-        <v>8.7361983850425831E-2</v>
+        <v>0.11069471761559577</v>
       </c>
       <c r="O7" s="8">
-        <v>1.5902180503654995</v>
+        <v>1.587425379177277</v>
       </c>
       <c r="P7" s="8">
-        <v>2.6778322074860991E-6</v>
+        <v>3.0100158065422581E-5</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>0.18640925397311581</v>
+        <v>-8.6244877522815289E-3</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
-        <v>-1.2638016149574174E-2</v>
+        <v>1.0694717615595761E-2</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="1"/>
-        <v>1.94217235706029E-2</v>
+        <v>1.6629052382380438E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>0.18640925397311581</v>
+        <v>8.6244877522815289E-3</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>1.2638016149574174E-2</v>
+        <v>1.0694717615595761E-2</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.94217235706029E-2</v>
+        <v>1.6629052382380438E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -5797,40 +5801,40 @@
         <v>0.33158546686172502</v>
       </c>
       <c r="M8" s="8">
-        <v>0.37049577545064055</v>
+        <v>0.37550210442667975</v>
       </c>
       <c r="N8" s="8">
-        <v>0.17780657979005726</v>
+        <v>0.17311447561668428</v>
       </c>
       <c r="O8" s="8">
-        <v>1.5913837089105622</v>
+        <v>1.5796254680421602</v>
       </c>
       <c r="P8" s="8">
-        <v>2.9097890883656551E-6</v>
+        <v>2.1109742122939963E-4</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>-2.950422454935947E-2</v>
+        <v>-2.4497895573320272E-2</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
-        <v>1.7806579790057259E-2</v>
+        <v>1.3114475616684274E-2</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="1"/>
-        <v>2.0587382115665687E-2</v>
+        <v>8.8291412472636388E-3</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="2"/>
-        <v>2.950422454935947E-2</v>
+        <v>2.4497895573320272E-2</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>1.7806579790057259E-2</v>
+        <v>1.3114475616684274E-2</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>2.0587382115665687E-2</v>
+        <v>8.8291412472636388E-3</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -5883,40 +5887,40 @@
         <v>0.469948559999466</v>
       </c>
       <c r="M9" s="8">
-        <v>0.74824967538359533</v>
+        <v>0.56497426045613874</v>
       </c>
       <c r="N9" s="8">
-        <v>0.13783904206507699</v>
+        <v>0.16528493275999942</v>
       </c>
       <c r="O9" s="8">
-        <v>1.594897830182626</v>
+        <v>1.580299241084306</v>
       </c>
       <c r="P9" s="8">
-        <v>4.674379950577917E-6</v>
+        <v>3.1827266330454809E-4</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>0.14824967538359535</v>
+        <v>-3.5025739543861234E-2</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
-        <v>-2.2160957934923009E-2</v>
+        <v>5.2849327599994167E-3</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="1"/>
-        <v>2.4101503387729428E-2</v>
+        <v>9.5029142894094143E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="2"/>
-        <v>0.14824967538359535</v>
+        <v>3.5025739543861234E-2</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>2.2160957934923009E-2</v>
+        <v>5.2849327599994167E-3</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>2.4101503387729428E-2</v>
+        <v>9.5029142894094143E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -5972,40 +5976,40 @@
         <v>0.27560678124427801</v>
       </c>
       <c r="M10" s="8">
-        <v>0.97142252093467496</v>
+        <v>0.83481970399375527</v>
       </c>
       <c r="N10" s="8">
-        <v>0.16023280923465782</v>
+        <v>0.16829695270786463</v>
       </c>
       <c r="O10" s="8">
-        <v>1.5958440699673537</v>
+        <v>1.5875321449709592</v>
       </c>
       <c r="P10" s="8">
-        <v>1.3264276233150466E-5</v>
+        <v>2.6277613828493574E-4</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>0.17142252093467492</v>
+        <v>3.4819703993755224E-2</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
-        <v>-1.9767190765342169E-2</v>
+        <v>-1.1703047292135366E-2</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="1"/>
-        <v>2.5047743172457171E-2</v>
+        <v>1.6735818176062622E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="2"/>
-        <v>0.17142252093467492</v>
+        <v>3.4819703993755224E-2</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>1.9767190765342169E-2</v>
+        <v>1.1703047292135366E-2</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>2.5047743172457171E-2</v>
+        <v>1.6735818176062622E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -6058,40 +6062,40 @@
         <v>0.21111465990543399</v>
       </c>
       <c r="M11" s="8">
-        <v>0.27977812852087819</v>
+        <v>0.30032903077135142</v>
       </c>
       <c r="N11" s="8">
-        <v>0.19999999999970047</v>
+        <v>0.19999999998884047</v>
       </c>
       <c r="O11" s="8">
-        <v>1.5865210387170547</v>
+        <v>1.577600833859351</v>
       </c>
       <c r="P11" s="8">
-        <v>5.2304243440508094E-6</v>
+        <v>5.7301024997264923E-4</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>-2.02218714791218E-2</v>
+        <v>3.290307713514351E-4</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
-        <v>-2.9953817204386723E-13</v>
+        <v>-1.1159545509897839E-11</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="1"/>
-        <v>1.5724711922158185E-2</v>
+        <v>6.804507064454457E-3</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="2"/>
-        <v>2.02218714791218E-2</v>
+        <v>3.290307713514351E-4</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>2.9953817204386723E-13</v>
+        <v>1.1159545509897839E-11</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.5724711922158185E-2</v>
+        <v>6.804507064454457E-3</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -6147,48 +6151,48 @@
         <v>0.17886316776275599</v>
       </c>
       <c r="M12" s="8">
-        <v>0.74274705256034634</v>
+        <v>0.6627908436895753</v>
       </c>
       <c r="N12" s="8">
-        <v>0.18056740429451734</v>
+        <v>0.178739938276433</v>
       </c>
       <c r="O12" s="8">
-        <v>1.5956024775151085</v>
+        <v>1.5816122798542704</v>
       </c>
       <c r="P12" s="8">
-        <v>1.2859177203812357E-5</v>
+        <v>2.8685918484907337E-4</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>4.2747052560346388E-2</v>
+        <v>-3.7209156310424651E-2</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
-        <v>-1.9432595705482669E-2</v>
+        <v>-2.1260061723567009E-2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="1"/>
-        <v>2.4806150720211972E-2</v>
+        <v>1.0815953059373884E-2</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="2"/>
-        <v>4.2747052560346388E-2</v>
+        <v>3.7209156310424651E-2</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>1.9432595705482669E-2</v>
+        <v>2.1260061723567009E-2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>2.4806150720211972E-2</v>
+        <v>1.0815953059373884E-2</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -7649,7 +7653,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="26"/>
@@ -7659,11 +7663,11 @@
       </c>
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
-      <c r="T1" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
+      <c r="T1" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
       <c r="W1" s="28"/>
       <c r="X1" s="28"/>
       <c r="Y1" s="28"/>
@@ -8632,11 +8636,11 @@
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -10061,22 +10065,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32"/>
-      <c r="H1" s="33" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="H1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -17021,16 +17025,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4534" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DCED55E-7A8A-41A0-AE3B-0B4388F9A205}"/>
+  <xr:revisionPtr revIDLastSave="4569" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30C4FC50-9AF3-43C4-8663-A7663941BC8F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="45">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -186,13 +186,19 @@
     <t>SoRoSim get_distal_value (lambda = 0.5)</t>
   </si>
   <si>
-    <t>SoRoSim get_distal_value (lambda = 1.5)</t>
-  </si>
-  <si>
     <t>ABS Distal Errors</t>
   </si>
   <si>
     <t>SoRoSim get_distal_value (lambda = 1)</t>
+  </si>
+  <si>
+    <t>3 Perturbations</t>
+  </si>
+  <si>
+    <t>3 Perturbation (relative only)</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (lambda = 0.3)</t>
   </si>
 </sst>
 </file>
@@ -459,7 +465,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -530,6 +536,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1718,7 +1727,7 @@
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
       <c r="T1" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U1" s="30"/>
       <c r="V1" s="30"/>
@@ -2759,7 +2768,7 @@
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
       <c r="T1" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U1" s="30"/>
       <c r="V1" s="30"/>
@@ -2890,40 +2899,40 @@
         <v>0.34822303056716902</v>
       </c>
       <c r="M3" s="5">
-        <v>0.63914340988147</v>
+        <v>0.41553954528208881</v>
       </c>
       <c r="N3" s="5">
-        <v>3.6527560754298423E-2</v>
+        <v>6.7586423368890466E-2</v>
       </c>
       <c r="O3" s="5">
-        <v>1.583640389744444</v>
+        <v>1.5942535066255172</v>
       </c>
       <c r="P3" s="11">
-        <v>1.0592777524235738E-7</v>
+        <v>3.1859655855985016E-4</v>
       </c>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>0.23914340988146998</v>
+        <v>1.5539545282088785E-2</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>-2.3472439245701575E-2</v>
+        <v>7.5864233688904686E-3</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>1.284406294954743E-2</v>
+        <v>2.3457179830620678E-2</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>0.23914340988146998</v>
+        <v>1.5539545282088785E-2</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V3" si="0">ABS(R3)</f>
-        <v>2.3472439245701575E-2</v>
+        <v>7.5864233688904686E-3</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>1.284406294954743E-2</v>
+        <v>2.3457179830620678E-2</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -2985,52 +2994,52 @@
         <v>0.83409011363983199</v>
       </c>
       <c r="M4" s="8">
-        <v>0.5479510710837473</v>
+        <v>0.84710125095211031</v>
       </c>
       <c r="N4" s="8">
-        <v>0.10307030173986728</v>
+        <v>6.9876606593779714E-2</v>
       </c>
       <c r="O4" s="8">
-        <v>1.5856822108880413</v>
+        <v>1.5975875435204436</v>
       </c>
       <c r="P4" s="12">
-        <v>8.312363092065551E-7</v>
+        <v>1.0595002718595083E-3</v>
       </c>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:Q12" si="1">M4-A4</f>
-        <v>-0.25204892891625275</v>
+        <v>4.7101250952110263E-2</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" ref="R4:R12" si="2">N4-B4</f>
-        <v>4.3070301739867284E-2</v>
+        <v>9.8766065937797159E-3</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S12" si="3">O4-C4</f>
-        <v>1.488588409314473E-2</v>
+        <v>2.6791216725547073E-2</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="4">ABS(Q4)</f>
-        <v>0.25204892891625275</v>
+        <v>4.7101250952110263E-2</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U12" si="5">ABS(R4)</f>
-        <v>4.3070301739867284E-2</v>
+        <v>9.8766065937797159E-3</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" ref="V4:V12" si="6">ABS(S4)</f>
-        <v>1.488588409314473E-2</v>
+        <v>2.6791216725547073E-2</v>
       </c>
       <c r="W4" s="6" cm="1">
         <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.17410052252268796</v>
+        <v>4.2523991372479829E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
         <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>2.4031151173268629E-2</v>
+        <v>1.0829170549000348E-2</v>
       </c>
       <c r="Y4" s="6" cm="1">
         <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.8262644766218084E-2</v>
+        <v>2.5292302579239822E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -3083,40 +3092,40 @@
         <v>0.269099742174149</v>
       </c>
       <c r="M5" s="5">
-        <v>0.78321097258028849</v>
+        <v>0.28522939561051408</v>
       </c>
       <c r="N5" s="5">
-        <v>3.0519902868094969E-2</v>
+        <v>8.4915813659740186E-2</v>
       </c>
       <c r="O5" s="5">
-        <v>1.5771255182633155</v>
+        <v>1.5827769924240351</v>
       </c>
       <c r="P5" s="11">
-        <v>5.514943758316573E-8</v>
+        <v>1.1970874690918172E-4</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>0.4832109725802885</v>
+        <v>-1.4770604389485908E-2</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="2"/>
-        <v>-4.9480097131905029E-2</v>
+        <v>4.9158136597401841E-3</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="3"/>
-        <v>6.3291914684189265E-3</v>
+        <v>1.1980665629138576E-2</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="4"/>
-        <v>0.4832109725802885</v>
+        <v>1.4770604389485908E-2</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="5"/>
-        <v>4.9480097131905029E-2</v>
+        <v>4.9158136597401841E-3</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="6"/>
-        <v>6.3291914684189265E-3</v>
+        <v>1.1980665629138576E-2</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -3172,40 +3181,40 @@
         <v>0.47075057029724099</v>
       </c>
       <c r="M6" s="5">
-        <v>0.46595931140117192</v>
+        <v>0.47643338484485187</v>
       </c>
       <c r="N6" s="5">
-        <v>0.11309742874563515</v>
+        <v>0.1105004765444883</v>
       </c>
       <c r="O6" s="5">
-        <v>1.5889644778593157</v>
+        <v>1.5830404836724534</v>
       </c>
       <c r="P6" s="11">
-        <v>4.6414689237263524E-7</v>
+        <v>1.0890150419537683E-4</v>
       </c>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-3.4040688598828084E-2</v>
+        <v>-2.356661515514813E-2</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="2"/>
-        <v>1.3097428745635145E-2</v>
+        <v>1.0500476544488296E-2</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="3"/>
-        <v>1.8168151064419158E-2</v>
+        <v>1.2244156877556867E-2</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>3.4040688598828084E-2</v>
+        <v>2.356661515514813E-2</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="5"/>
-        <v>1.3097428745635145E-2</v>
+        <v>1.0500476544488296E-2</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="6"/>
-        <v>1.8168151064419158E-2</v>
+        <v>1.2244156877556867E-2</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -3258,40 +3267,40 @@
         <v>0.69233715534210205</v>
       </c>
       <c r="M7" s="5">
-        <v>0.93692516169714024</v>
+        <v>0.76553039235818787</v>
       </c>
       <c r="N7" s="5">
-        <v>8.2665850962450424E-2</v>
+        <v>0.10073987505760774</v>
       </c>
       <c r="O7" s="5">
-        <v>1.5902621335915128</v>
+        <v>1.5591809194429029</v>
       </c>
       <c r="P7" s="11">
-        <v>9.799252638549781E-7</v>
+        <v>3.2442525164216813E-4</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>0.23692516169714029</v>
+        <v>6.5530392358187917E-2</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="2"/>
-        <v>-1.7334149037549582E-2</v>
+        <v>7.3987505760773897E-4</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="3"/>
-        <v>1.9465806796616247E-2</v>
+        <v>-1.1615407351993623E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>0.23692516169714029</v>
+        <v>6.5530392358187917E-2</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="5"/>
-        <v>1.7334149037549582E-2</v>
+        <v>7.3987505760773897E-4</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="6"/>
-        <v>1.9465806796616247E-2</v>
+        <v>1.1615407351993623E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -3344,40 +3353,40 @@
         <v>0.33158546686172502</v>
       </c>
       <c r="M8" s="5">
-        <v>0.38399846982742913</v>
+        <v>0.33534267112782717</v>
       </c>
       <c r="N8" s="5">
-        <v>0.17117564780221001</v>
+        <v>0.16956084100986696</v>
       </c>
       <c r="O8" s="5">
-        <v>1.5905615187571525</v>
+        <v>1.562285411805975</v>
       </c>
       <c r="P8" s="11">
-        <v>1.0155268914808618E-6</v>
+        <v>3.111200989257263E-4</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>-1.6001530172570888E-2</v>
+        <v>-6.4657328872172848E-2</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="2"/>
-        <v>1.1175647802210004E-2</v>
+        <v>9.560841009866955E-3</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="3"/>
-        <v>1.9765191962255901E-2</v>
+        <v>-8.5109149889215363E-3</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>1.6001530172570888E-2</v>
+        <v>6.4657328872172848E-2</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="5"/>
-        <v>1.1175647802210004E-2</v>
+        <v>9.560841009866955E-3</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="6"/>
-        <v>1.9765191962255901E-2</v>
+        <v>8.5109149889215363E-3</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -3430,40 +3439,40 @@
         <v>0.469948559999466</v>
       </c>
       <c r="M9" s="5">
-        <v>0.79794945155117092</v>
+        <v>0.60041075475288275</v>
       </c>
       <c r="N9" s="5">
-        <v>0.12890643568404961</v>
+        <v>0.1566705848227011</v>
       </c>
       <c r="O9" s="5">
-        <v>1.5947770010216074</v>
+        <v>1.5656310545718017</v>
       </c>
       <c r="P9" s="11">
-        <v>1.8150895339071014E-6</v>
+        <v>3.4944284913766577E-4</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>0.19794945155117094</v>
+        <v>4.107547528827693E-4</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="2"/>
-        <v>-3.1093564315950395E-2</v>
+        <v>-3.3294151772989E-3</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="3"/>
-        <v>2.3980674226710796E-2</v>
+        <v>-5.1652722230948189E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>0.19794945155117094</v>
+        <v>4.107547528827693E-4</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="5"/>
-        <v>3.1093564315950395E-2</v>
+        <v>3.3294151772989E-3</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="6"/>
-        <v>2.3980674226710796E-2</v>
+        <v>5.1652722230948189E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -3519,40 +3528,40 @@
         <v>0.27560678124427801</v>
       </c>
       <c r="M10" s="5">
-        <v>0.99998682576416487</v>
+        <v>0.75400562839900798</v>
       </c>
       <c r="N10" s="5">
-        <v>0.15403533930343935</v>
+        <v>0.18125389088066388</v>
       </c>
       <c r="O10" s="5">
-        <v>1.5962753346062015</v>
+        <v>1.6294545928293671</v>
       </c>
       <c r="P10" s="11">
-        <v>6.2819096877262139E-6</v>
+        <v>6.1455125978496618E-4</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>0.19998682576416482</v>
+        <v>-4.5994371600992068E-2</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="2"/>
-        <v>-2.5964660696560643E-2</v>
+        <v>1.2538908806638827E-3</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>2.5479007811304966E-2</v>
+        <v>5.8658266034470552E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>0.19998682576416482</v>
+        <v>4.5994371600992068E-2</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="5"/>
-        <v>2.5964660696560643E-2</v>
+        <v>1.2538908806638827E-3</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="6"/>
-        <v>2.5479007811304966E-2</v>
+        <v>5.8658266034470552E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -3605,40 +3614,40 @@
         <v>0.21111465990543399</v>
       </c>
       <c r="M11" s="5">
-        <v>0.27906459075164891</v>
+        <v>0.29413891095281969</v>
       </c>
       <c r="N11" s="5">
-        <v>0.19999999999944165</v>
+        <v>0.19999999999997781</v>
       </c>
       <c r="O11" s="5">
-        <v>1.5871697785148184</v>
+        <v>1.5421446553139395</v>
       </c>
       <c r="P11" s="11">
-        <v>1.7382266395466961E-6</v>
+        <v>9.4727875734425065E-4</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>-2.0935409248351078E-2</v>
+        <v>-5.8610890471803012E-3</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="2"/>
-        <v>-5.5835891465960685E-13</v>
+        <v>-2.2204460492503131E-14</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="3"/>
-        <v>1.6373451719921883E-2</v>
+        <v>-2.8651671480957042E-2</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>2.0935409248351078E-2</v>
+        <v>5.8610890471803012E-3</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="5"/>
-        <v>5.5835891465960685E-13</v>
+        <v>2.2204460492503131E-14</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="6"/>
-        <v>1.6373451719921883E-2</v>
+        <v>2.8651671480957042E-2</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -3694,40 +3703,40 @@
         <v>0.17886316776275599</v>
       </c>
       <c r="M12" s="5">
-        <v>0.76076284681664186</v>
+        <v>0.84180796131454927</v>
       </c>
       <c r="N12" s="5">
-        <v>0.17437677698325174</v>
+        <v>0.13947163680235489</v>
       </c>
       <c r="O12" s="5">
-        <v>1.5961313523647374</v>
+        <v>1.636644601444994</v>
       </c>
       <c r="P12" s="11">
-        <v>5.3920494955081985E-6</v>
+        <v>1.2213309215035062E-3</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>6.0762846816641902E-2</v>
+        <v>0.14180796131454931</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="2"/>
-        <v>-2.562322301674827E-2</v>
+        <v>-6.0528363197645124E-2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="3"/>
-        <v>2.5335025569840797E-2</v>
+        <v>6.584827465009746E-2</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="4"/>
-        <v>6.0762846816641902E-2</v>
+        <v>0.14180796131454931</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="5"/>
-        <v>2.562322301674827E-2</v>
+        <v>6.0528363197645124E-2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="6"/>
-        <v>2.5335025569840797E-2</v>
+        <v>6.584827465009746E-2</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -5165,7 +5174,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAE0736-1722-4350-9DE0-8A911956EF0F}">
-  <dimension ref="A1:Y60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
@@ -5187,1030 +5196,2051 @@
     <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="AA1" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+    </row>
+    <row r="2" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27" t="s">
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="30" t="s">
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="AA2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="AN2" s="26"/>
+      <c r="AO2" s="26"/>
+      <c r="AP2" s="26"/>
+      <c r="AQ2" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AU2" s="30"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+    </row>
+    <row r="3" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="29" t="s">
+      <c r="W3" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-    </row>
-    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="AA3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW3" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX3" s="29"/>
+      <c r="AY3" s="29"/>
+    </row>
+    <row r="4" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <f>'Proximal Validation'!A3</f>
         <v>0.4</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B4" s="5">
         <f>'Proximal Validation'!B3</f>
         <v>0.06</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C4" s="5">
         <f>'Proximal Validation'!C3</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D4" s="5">
         <f>'Proximal Validation'!D3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E4" s="5">
         <f>'Proximal Validation'!E3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F4" s="5">
         <f>'Proximal Validation'!F3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G4" s="5">
         <f>'Proximal Validation'!G3</f>
         <v>-4.37921960838139E-4</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H4" s="5">
         <f>'Proximal Validation'!H3</f>
         <v>-5.4464954882860198E-2</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I4" s="5">
         <f>'Proximal Validation'!I3</f>
         <v>-2.8745096642523999E-4</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J4" s="5">
         <f>'Proximal Validation'!J3</f>
         <v>-2.13129706680775E-2</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K4" s="5">
         <f>'Proximal Validation'!K3</f>
         <v>1.85158103704453E-4</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L4" s="5">
         <f>'Proximal Validation'!L3</f>
         <v>0.34822303056716902</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M4" s="8">
         <v>0.40202965392158824</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N4" s="8">
         <v>6.9789383849933759E-2</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O4" s="8">
         <v>1.58612318996072</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P4" s="8">
         <v>1.6932000391698518E-4</v>
       </c>
-      <c r="Q3" s="5">
-        <f>M3-A3</f>
+      <c r="Q4" s="5">
+        <f>M4-A4</f>
         <v>2.0296539215882148E-3</v>
       </c>
-      <c r="R3" s="5">
-        <f>N3-B3</f>
+      <c r="R4" s="5">
+        <f>N4-B4</f>
         <v>9.789383849933761E-3</v>
       </c>
-      <c r="S3" s="5">
-        <f>O3-C3</f>
+      <c r="S4" s="5">
+        <f>O4-C4</f>
         <v>1.5326863165823434E-2</v>
       </c>
-      <c r="T3" s="5">
-        <f>ABS(Q3)</f>
+      <c r="T4" s="5">
+        <f>ABS(Q4)</f>
         <v>2.0296539215882148E-3</v>
       </c>
-      <c r="U3" s="5">
-        <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
+      <c r="U4" s="5">
+        <f t="shared" ref="U4:V13" si="0">ABS(R4)</f>
         <v>9.789383849933761E-3</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V4" s="5">
         <f t="shared" si="0"/>
         <v>1.5326863165823434E-2</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="AA4" s="5">
+        <f>'Proximal Validation'!A3</f>
+        <v>0.4</v>
+      </c>
+      <c r="AB4" s="5">
+        <f>'Proximal Validation'!B3</f>
+        <v>0.06</v>
+      </c>
+      <c r="AC4" s="5">
+        <f>'Proximal Validation'!C3</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD4" s="5">
+        <f>'Proximal Validation'!D3</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5">
+        <f>'Proximal Validation'!E3</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="5">
+        <f>'Proximal Validation'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <f>'Proximal Validation'!G3</f>
+        <v>-4.37921960838139E-4</v>
+      </c>
+      <c r="AH4" s="5">
+        <f>'Proximal Validation'!H3</f>
+        <v>-5.4464954882860198E-2</v>
+      </c>
+      <c r="AI4" s="5">
+        <f>'Proximal Validation'!I3</f>
+        <v>-2.8745096642523999E-4</v>
+      </c>
+      <c r="AJ4" s="5">
+        <f>'Proximal Validation'!J3</f>
+        <v>-2.13129706680775E-2</v>
+      </c>
+      <c r="AK4" s="5">
+        <f>'Proximal Validation'!K3</f>
+        <v>1.85158103704453E-4</v>
+      </c>
+      <c r="AL4" s="5">
+        <f>'Proximal Validation'!L3</f>
+        <v>0.34822303056716902</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>0.90280937245662962</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>7.3504807421227364E-2</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>1.5860913566047261</v>
+      </c>
+      <c r="AP4" s="8">
+        <v>2.1199761470585318E-4</v>
+      </c>
+      <c r="AQ4" s="5">
+        <f>AM4-AA4</f>
+        <v>0.5028093724566296</v>
+      </c>
+      <c r="AR4" s="5">
+        <f>AN4-AB4</f>
+        <v>1.3504807421227366E-2</v>
+      </c>
+      <c r="AS4" s="5">
+        <f>AO4-AC4</f>
+        <v>1.5295029809829552E-2</v>
+      </c>
+      <c r="AT4" s="5">
+        <f>ABS(AQ4)</f>
+        <v>0.5028093724566296</v>
+      </c>
+      <c r="AU4" s="5">
+        <f t="shared" ref="AU4:AU13" si="1">ABS(AR4)</f>
+        <v>1.3504807421227366E-2</v>
+      </c>
+      <c r="AV4" s="5">
+        <f t="shared" ref="AV4:AV13" si="2">ABS(AS4)</f>
+        <v>1.5295029809829552E-2</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
         <f>'Proximal Validation'!A4</f>
         <v>0.8</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B5" s="8">
         <f>'Proximal Validation'!B4</f>
         <v>0.06</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C5" s="8">
         <f>'Proximal Validation'!C4</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D5" s="8">
         <f>'Proximal Validation'!D4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E5" s="8">
         <f>'Proximal Validation'!E4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F5" s="8">
         <f>'Proximal Validation'!F4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G5" s="8">
         <f>'Proximal Validation'!G4</f>
         <v>-1.2904058676213E-3</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H5" s="8">
         <f>'Proximal Validation'!H4</f>
         <v>-0.130890563130379</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I5" s="8">
         <f>'Proximal Validation'!I4</f>
         <v>-5.0724833272397496E-4</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J5" s="8">
         <f>'Proximal Validation'!J4</f>
         <v>-0.12710034847259499</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K5" s="8">
         <f>'Proximal Validation'!K4</f>
         <v>3.3702701330184902E-3</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L5" s="8">
         <f>'Proximal Validation'!L4</f>
         <v>0.83409011363983199</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M5" s="8">
         <v>0.75713708359141785</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N5" s="8">
         <v>7.2421632945224593E-2</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O5" s="8">
         <v>1.5945817689101296</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P5" s="8">
         <v>4.7490785077414997E-4</v>
       </c>
-      <c r="Q4" s="5">
-        <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
+      <c r="Q5" s="5">
+        <f t="shared" ref="Q5:S13" si="3">M5-A5</f>
         <v>-4.2862916408582197E-2</v>
       </c>
-      <c r="R4" s="5">
-        <f t="shared" si="1"/>
+      <c r="R5" s="5">
+        <f t="shared" si="3"/>
         <v>1.2421632945224595E-2</v>
       </c>
-      <c r="S4" s="5">
-        <f t="shared" si="1"/>
+      <c r="S5" s="5">
+        <f t="shared" si="3"/>
         <v>2.3785442115233035E-2</v>
       </c>
-      <c r="T4" s="5">
-        <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
+      <c r="T5" s="5">
+        <f t="shared" ref="T5:T13" si="4">ABS(Q5)</f>
         <v>4.2862916408582197E-2</v>
       </c>
-      <c r="U4" s="5">
+      <c r="U5" s="5">
         <f t="shared" si="0"/>
         <v>1.2421632945224595E-2</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V5" s="5">
         <f t="shared" si="0"/>
         <v>2.3785442115233035E-2</v>
       </c>
-      <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
+      <c r="W5" s="6" cm="1">
+        <f t="array" ref="W5">AVERAGE(ABS(Q4:Q13))</f>
         <v>2.3919911823198969E-2</v>
       </c>
-      <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
+      <c r="X5" s="6" cm="1">
+        <f t="array" ref="X5">AVERAGE(ABS(R4:R13))</f>
         <v>1.0326971317622804E-2</v>
       </c>
-      <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
+      <c r="Y5" s="6" cm="1">
+        <f t="array" ref="Y5">AVERAGE(ABS(S4:S13))</f>
         <v>1.3631851876260814E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="AA5" s="8">
+        <f>'Proximal Validation'!A4</f>
+        <v>0.8</v>
+      </c>
+      <c r="AB5" s="8">
+        <f>'Proximal Validation'!B4</f>
+        <v>0.06</v>
+      </c>
+      <c r="AC5" s="8">
+        <f>'Proximal Validation'!C4</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD5" s="8">
+        <f>'Proximal Validation'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="8">
+        <f>'Proximal Validation'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="8">
+        <f>'Proximal Validation'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="8">
+        <f>'Proximal Validation'!G4</f>
+        <v>-1.2904058676213E-3</v>
+      </c>
+      <c r="AH5" s="8">
+        <f>'Proximal Validation'!H4</f>
+        <v>-0.130890563130379</v>
+      </c>
+      <c r="AI5" s="8">
+        <f>'Proximal Validation'!I4</f>
+        <v>-5.0724833272397496E-4</v>
+      </c>
+      <c r="AJ5" s="8">
+        <f>'Proximal Validation'!J4</f>
+        <v>-0.12710034847259499</v>
+      </c>
+      <c r="AK5" s="8">
+        <f>'Proximal Validation'!K4</f>
+        <v>3.3702701330184902E-3</v>
+      </c>
+      <c r="AL5" s="8">
+        <f>'Proximal Validation'!L4</f>
+        <v>0.83409011363983199</v>
+      </c>
+      <c r="AM5" s="8">
+        <v>0.88619393783422673</v>
+      </c>
+      <c r="AN5" s="8">
+        <v>7.7520968239498028E-2</v>
+      </c>
+      <c r="AO5" s="8">
+        <v>1.5993199661293449</v>
+      </c>
+      <c r="AP5" s="8">
+        <v>7.7792135483811787E-4</v>
+      </c>
+      <c r="AQ5" s="5">
+        <f t="shared" ref="AQ5:AQ13" si="5">AM5-AA5</f>
+        <v>8.6193937834226686E-2</v>
+      </c>
+      <c r="AR5" s="5">
+        <f t="shared" ref="AR5:AR13" si="6">AN5-AB5</f>
+        <v>1.752096823949803E-2</v>
+      </c>
+      <c r="AS5" s="5">
+        <f t="shared" ref="AS5:AS13" si="7">AO5-AC5</f>
+        <v>2.8523639334448347E-2</v>
+      </c>
+      <c r="AT5" s="5">
+        <f t="shared" ref="AT5:AT13" si="8">ABS(AQ5)</f>
+        <v>8.6193937834226686E-2</v>
+      </c>
+      <c r="AU5" s="5">
+        <f t="shared" si="1"/>
+        <v>1.752096823949803E-2</v>
+      </c>
+      <c r="AV5" s="5">
+        <f t="shared" si="2"/>
+        <v>2.8523639334448347E-2</v>
+      </c>
+      <c r="AW5" s="6" cm="1">
+        <f t="array" ref="AW5">AVERAGE(ABS(AQ4:AQ13))</f>
+        <v>0.16765908823383766</v>
+      </c>
+      <c r="AX5" s="6" cm="1">
+        <f t="array" ref="AX5">AVERAGE(ABS(AR4:AR13))</f>
+        <v>1.0799263321470187E-2</v>
+      </c>
+      <c r="AY5" s="6" cm="1">
+        <f t="array" ref="AY5">AVERAGE(ABS(AS4:AS13))</f>
+        <v>1.3400209778654614E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <f>'Proximal Validation'!A5</f>
         <v>0.3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B6" s="5">
         <f>'Proximal Validation'!B5</f>
         <v>0.08</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C6" s="5">
         <f>'Proximal Validation'!C5</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D6" s="5">
         <f>'Proximal Validation'!D5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <f>'Proximal Validation'!E5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F6" s="5">
         <f>'Proximal Validation'!F5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G6" s="5">
         <f>'Proximal Validation'!G5</f>
         <v>-4.4532003812491899E-4</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="5">
         <f>'Proximal Validation'!H5</f>
         <v>-4.79050725698471E-2</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I6" s="5">
         <f>'Proximal Validation'!I5</f>
         <v>-1.45487196277827E-4</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J6" s="5">
         <f>'Proximal Validation'!J5</f>
         <v>-1.52218556031585E-2</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K6" s="5">
         <f>'Proximal Validation'!K5</f>
         <v>-1.61819159984589E-4</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L6" s="5">
         <f>'Proximal Validation'!L5</f>
         <v>0.269099742174149</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M6" s="8">
         <v>0.27154159433860381</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N6" s="8">
         <v>8.7965747246715797E-2</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O6" s="8">
         <v>1.5813627191821027</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P6" s="8">
         <v>2.4160611469808265E-5</v>
       </c>
-      <c r="Q5" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q6" s="5">
+        <f t="shared" si="3"/>
         <v>-2.845840566139618E-2</v>
       </c>
-      <c r="R5" s="5">
-        <f t="shared" si="1"/>
+      <c r="R6" s="5">
+        <f t="shared" si="3"/>
         <v>7.9657472467157958E-3</v>
       </c>
-      <c r="S5" s="5">
-        <f t="shared" si="1"/>
+      <c r="S6" s="5">
+        <f t="shared" si="3"/>
         <v>1.0566392387206136E-2</v>
       </c>
-      <c r="T5" s="5">
-        <f t="shared" si="2"/>
+      <c r="T6" s="5">
+        <f t="shared" si="4"/>
         <v>2.845840566139618E-2</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U6" s="5">
         <f t="shared" si="0"/>
         <v>7.9657472467157958E-3</v>
       </c>
-      <c r="V5" s="5">
+      <c r="V6" s="5">
         <f t="shared" si="0"/>
         <v>1.0566392387206136E-2</v>
       </c>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="AA6" s="5">
+        <f>'Proximal Validation'!A5</f>
+        <v>0.3</v>
+      </c>
+      <c r="AB6" s="5">
+        <f>'Proximal Validation'!B5</f>
+        <v>0.08</v>
+      </c>
+      <c r="AC6" s="5">
+        <f>'Proximal Validation'!C5</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD6" s="5">
+        <f>'Proximal Validation'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5">
+        <f>'Proximal Validation'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="5">
+        <f>'Proximal Validation'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="5">
+        <f>'Proximal Validation'!G5</f>
+        <v>-4.4532003812491899E-4</v>
+      </c>
+      <c r="AH6" s="5">
+        <f>'Proximal Validation'!H5</f>
+        <v>-4.79050725698471E-2</v>
+      </c>
+      <c r="AI6" s="5">
+        <f>'Proximal Validation'!I5</f>
+        <v>-1.45487196277827E-4</v>
+      </c>
+      <c r="AJ6" s="5">
+        <f>'Proximal Validation'!J5</f>
+        <v>-1.52218556031585E-2</v>
+      </c>
+      <c r="AK6" s="5">
+        <f>'Proximal Validation'!K5</f>
+        <v>-1.61819159984589E-4</v>
+      </c>
+      <c r="AL6" s="5">
+        <f>'Proximal Validation'!L5</f>
+        <v>0.269099742174149</v>
+      </c>
+      <c r="AM6" s="8">
+        <v>0.63721851611505154</v>
+      </c>
+      <c r="AN6" s="8">
+        <v>8.7793440106066878E-2</v>
+      </c>
+      <c r="AO6" s="8">
+        <v>1.5812845010112011</v>
+      </c>
+      <c r="AP6" s="8">
+        <v>2.1709110139151531E-5</v>
+      </c>
+      <c r="AQ6" s="5">
+        <f t="shared" si="5"/>
+        <v>0.33721851611505155</v>
+      </c>
+      <c r="AR6" s="5">
+        <f t="shared" si="6"/>
+        <v>7.7934401060668762E-3</v>
+      </c>
+      <c r="AS6" s="5">
+        <f t="shared" si="7"/>
+        <v>1.0488174216304547E-2</v>
+      </c>
+      <c r="AT6" s="5">
+        <f t="shared" si="8"/>
+        <v>0.33721851611505155</v>
+      </c>
+      <c r="AU6" s="5">
+        <f t="shared" si="1"/>
+        <v>7.7934401060668762E-3</v>
+      </c>
+      <c r="AV6" s="5">
+        <f t="shared" si="2"/>
+        <v>1.0488174216304547E-2</v>
+      </c>
+      <c r="AW6" s="24"/>
+      <c r="AX6" s="24"/>
+      <c r="AY6" s="24"/>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <f>'Proximal Validation'!A6</f>
         <v>0.5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B7" s="5">
         <f>'Proximal Validation'!B6</f>
         <v>0.1</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C7" s="5">
         <f>'Proximal Validation'!C6</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D7" s="5">
         <f>'Proximal Validation'!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E7" s="5">
         <f>'Proximal Validation'!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F7" s="5">
         <f>'Proximal Validation'!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G7" s="5">
         <f>'Proximal Validation'!G6</f>
         <v>-1.1705639772117101E-3</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H7" s="5">
         <f>'Proximal Validation'!H6</f>
         <v>-9.4456188380718203E-2</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I7" s="5">
         <f>'Proximal Validation'!I6</f>
         <v>-1.20323454029858E-3</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J7" s="5">
         <f>'Proximal Validation'!J6</f>
         <v>-0.111187651753426</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K7" s="5">
         <f>'Proximal Validation'!K6</f>
         <v>-3.2553412020206499E-3</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L7" s="5">
         <f>'Proximal Validation'!L6</f>
         <v>0.47075057029724099</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M7" s="8">
         <v>0.47465787170457124</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N7" s="8">
         <v>0.11103571411521253</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O7" s="8">
         <v>1.5881187616702976</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P7" s="8">
         <v>3.7665609979489553E-5</v>
       </c>
-      <c r="Q6" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q7" s="5">
+        <f t="shared" si="3"/>
         <v>-2.5342128295428756E-2</v>
       </c>
-      <c r="R6" s="5">
-        <f t="shared" si="1"/>
+      <c r="R7" s="5">
+        <f t="shared" si="3"/>
         <v>1.1035714115212522E-2</v>
       </c>
-      <c r="S6" s="5">
-        <f t="shared" si="1"/>
+      <c r="S7" s="5">
+        <f t="shared" si="3"/>
         <v>1.7322434875401083E-2</v>
       </c>
-      <c r="T6" s="5">
-        <f t="shared" si="2"/>
+      <c r="T7" s="5">
+        <f t="shared" si="4"/>
         <v>2.5342128295428756E-2</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U7" s="5">
         <f t="shared" si="0"/>
         <v>1.1035714115212522E-2</v>
       </c>
-      <c r="V6" s="5">
+      <c r="V7" s="5">
         <f t="shared" si="0"/>
         <v>1.7322434875401083E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="AA7" s="5">
+        <f>'Proximal Validation'!A6</f>
+        <v>0.5</v>
+      </c>
+      <c r="AB7" s="5">
+        <f>'Proximal Validation'!B6</f>
+        <v>0.1</v>
+      </c>
+      <c r="AC7" s="5">
+        <f>'Proximal Validation'!C6</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD7" s="5">
+        <f>'Proximal Validation'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
+        <f>'Proximal Validation'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="5">
+        <f>'Proximal Validation'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="5">
+        <f>'Proximal Validation'!G6</f>
+        <v>-1.1705639772117101E-3</v>
+      </c>
+      <c r="AH7" s="5">
+        <f>'Proximal Validation'!H6</f>
+        <v>-9.4456188380718203E-2</v>
+      </c>
+      <c r="AI7" s="5">
+        <f>'Proximal Validation'!I6</f>
+        <v>-1.20323454029858E-3</v>
+      </c>
+      <c r="AJ7" s="5">
+        <f>'Proximal Validation'!J6</f>
+        <v>-0.111187651753426</v>
+      </c>
+      <c r="AK7" s="5">
+        <f>'Proximal Validation'!K6</f>
+        <v>-3.2553412020206499E-3</v>
+      </c>
+      <c r="AL7" s="5">
+        <f>'Proximal Validation'!L6</f>
+        <v>0.47075057029724099</v>
+      </c>
+      <c r="AM7" s="8">
+        <v>0.80752080793495895</v>
+      </c>
+      <c r="AN7" s="8">
+        <v>0.11162012037263089</v>
+      </c>
+      <c r="AO7" s="8">
+        <v>1.5874660032480394</v>
+      </c>
+      <c r="AP7" s="8">
+        <v>6.3464187648353562E-5</v>
+      </c>
+      <c r="AQ7" s="5">
+        <f t="shared" si="5"/>
+        <v>0.30752080793495895</v>
+      </c>
+      <c r="AR7" s="5">
+        <f t="shared" si="6"/>
+        <v>1.1620120372630882E-2</v>
+      </c>
+      <c r="AS7" s="5">
+        <f t="shared" si="7"/>
+        <v>1.6669676453142879E-2</v>
+      </c>
+      <c r="AT7" s="5">
+        <f t="shared" si="8"/>
+        <v>0.30752080793495895</v>
+      </c>
+      <c r="AU7" s="5">
+        <f t="shared" si="1"/>
+        <v>1.1620120372630882E-2</v>
+      </c>
+      <c r="AV7" s="5">
+        <f t="shared" si="2"/>
+        <v>1.6669676453142879E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <f>'Proximal Validation'!A7</f>
         <v>0.7</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B8" s="5">
         <f>'Proximal Validation'!B7</f>
         <v>0.1</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C8" s="5">
         <f>'Proximal Validation'!C7</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D8" s="5">
         <f>'Proximal Validation'!D7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E8" s="5">
         <f>'Proximal Validation'!E7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F8" s="5">
         <f>'Proximal Validation'!F7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G8" s="5">
         <f>'Proximal Validation'!G7</f>
         <v>-1.5179968904703901E-3</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H8" s="5">
         <f>'Proximal Validation'!H7</f>
         <v>-0.13914526998996701</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I8" s="5">
         <f>'Proximal Validation'!I7</f>
         <v>-1.6895274166017799E-3</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J8" s="5">
         <f>'Proximal Validation'!J7</f>
         <v>-0.208347618579865</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K8" s="5">
         <f>'Proximal Validation'!K7</f>
         <v>-2.6145353913307199E-3</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L8" s="5">
         <f>'Proximal Validation'!L7</f>
         <v>0.69233715534210205</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M8" s="8">
         <v>0.69137551224771843</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N8" s="8">
         <v>0.11069471761559577</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O8" s="8">
         <v>1.587425379177277</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P8" s="8">
         <v>3.0100158065422581E-5</v>
       </c>
-      <c r="Q7" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q8" s="5">
+        <f t="shared" si="3"/>
         <v>-8.6244877522815289E-3</v>
       </c>
-      <c r="R7" s="5">
-        <f t="shared" si="1"/>
+      <c r="R8" s="5">
+        <f t="shared" si="3"/>
         <v>1.0694717615595761E-2</v>
       </c>
-      <c r="S7" s="5">
-        <f t="shared" si="1"/>
+      <c r="S8" s="5">
+        <f t="shared" si="3"/>
         <v>1.6629052382380438E-2</v>
       </c>
-      <c r="T7" s="5">
-        <f t="shared" si="2"/>
+      <c r="T8" s="5">
+        <f t="shared" si="4"/>
         <v>8.6244877522815289E-3</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U8" s="5">
         <f t="shared" si="0"/>
         <v>1.0694717615595761E-2</v>
       </c>
-      <c r="V7" s="5">
+      <c r="V8" s="5">
         <f t="shared" si="0"/>
         <v>1.6629052382380438E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="AA8" s="5">
+        <f>'Proximal Validation'!A7</f>
+        <v>0.7</v>
+      </c>
+      <c r="AB8" s="5">
+        <f>'Proximal Validation'!B7</f>
+        <v>0.1</v>
+      </c>
+      <c r="AC8" s="5">
+        <f>'Proximal Validation'!C7</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD8" s="5">
+        <f>'Proximal Validation'!D7</f>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <f>'Proximal Validation'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="5">
+        <f>'Proximal Validation'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <f>'Proximal Validation'!G7</f>
+        <v>-1.5179968904703901E-3</v>
+      </c>
+      <c r="AH8" s="5">
+        <f>'Proximal Validation'!H7</f>
+        <v>-0.13914526998996701</v>
+      </c>
+      <c r="AI8" s="5">
+        <f>'Proximal Validation'!I7</f>
+        <v>-1.6895274166017799E-3</v>
+      </c>
+      <c r="AJ8" s="5">
+        <f>'Proximal Validation'!J7</f>
+        <v>-0.208347618579865</v>
+      </c>
+      <c r="AK8" s="5">
+        <f>'Proximal Validation'!K7</f>
+        <v>-2.6145353913307199E-3</v>
+      </c>
+      <c r="AL8" s="5">
+        <f>'Proximal Validation'!L7</f>
+        <v>0.69233715534210205</v>
+      </c>
+      <c r="AM8" s="8">
+        <v>0.88379744229303936</v>
+      </c>
+      <c r="AN8" s="8">
+        <v>0.11268546986401622</v>
+      </c>
+      <c r="AO8" s="8">
+        <v>1.5867762323810675</v>
+      </c>
+      <c r="AP8" s="8">
+        <v>9.2289561623872364E-5</v>
+      </c>
+      <c r="AQ8" s="5">
+        <f t="shared" si="5"/>
+        <v>0.1837974422930394</v>
+      </c>
+      <c r="AR8" s="5">
+        <f t="shared" si="6"/>
+        <v>1.2685469864016211E-2</v>
+      </c>
+      <c r="AS8" s="5">
+        <f t="shared" si="7"/>
+        <v>1.5979905586170906E-2</v>
+      </c>
+      <c r="AT8" s="5">
+        <f t="shared" si="8"/>
+        <v>0.1837974422930394</v>
+      </c>
+      <c r="AU8" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2685469864016211E-2</v>
+      </c>
+      <c r="AV8" s="5">
+        <f t="shared" si="2"/>
+        <v>1.5979905586170906E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <f>'Proximal Validation'!A8</f>
         <v>0.4</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B9" s="5">
         <f>'Proximal Validation'!B8</f>
         <v>0.16</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C9" s="5">
         <f>'Proximal Validation'!C8</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D9" s="5">
         <f>'Proximal Validation'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E9" s="5">
         <f>'Proximal Validation'!E8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F9" s="5">
         <f>'Proximal Validation'!F8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G9" s="5">
         <f>'Proximal Validation'!G8</f>
         <v>-6.0909817693754998E-4</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H9" s="5">
         <f>'Proximal Validation'!H8</f>
         <v>-9.3464262783527402E-2</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I9" s="5">
         <f>'Proximal Validation'!I8</f>
         <v>-1.42273562960327E-3</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J9" s="5">
         <f>'Proximal Validation'!J8</f>
         <v>-0.183252438902855</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K9" s="5">
         <f>'Proximal Validation'!K8</f>
         <v>-1.30194798111916E-3</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L9" s="5">
         <f>'Proximal Validation'!L8</f>
         <v>0.33158546686172502</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M9" s="8">
         <v>0.37550210442667975</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N9" s="8">
         <v>0.17311447561668428</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O9" s="8">
         <v>1.5796254680421602</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P9" s="8">
         <v>2.1109742122939963E-4</v>
       </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q9" s="5">
+        <f t="shared" si="3"/>
         <v>-2.4497895573320272E-2</v>
       </c>
-      <c r="R8" s="5">
-        <f t="shared" si="1"/>
+      <c r="R9" s="5">
+        <f t="shared" si="3"/>
         <v>1.3114475616684274E-2</v>
       </c>
-      <c r="S8" s="5">
-        <f t="shared" si="1"/>
+      <c r="S9" s="5">
+        <f t="shared" si="3"/>
         <v>8.8291412472636388E-3</v>
       </c>
-      <c r="T8" s="5">
-        <f t="shared" si="2"/>
+      <c r="T9" s="5">
+        <f t="shared" si="4"/>
         <v>2.4497895573320272E-2</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U9" s="5">
         <f t="shared" si="0"/>
         <v>1.3114475616684274E-2</v>
       </c>
-      <c r="V8" s="5">
+      <c r="V9" s="5">
         <f t="shared" si="0"/>
         <v>8.8291412472636388E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="AA9" s="5">
+        <f>'Proximal Validation'!A8</f>
+        <v>0.4</v>
+      </c>
+      <c r="AB9" s="5">
+        <f>'Proximal Validation'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="AC9" s="5">
+        <f>'Proximal Validation'!C8</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD9" s="5">
+        <f>'Proximal Validation'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="AE9" s="5">
+        <f>'Proximal Validation'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="5">
+        <f>'Proximal Validation'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="5">
+        <f>'Proximal Validation'!G8</f>
+        <v>-6.0909817693754998E-4</v>
+      </c>
+      <c r="AH9" s="5">
+        <f>'Proximal Validation'!H8</f>
+        <v>-9.3464262783527402E-2</v>
+      </c>
+      <c r="AI9" s="5">
+        <f>'Proximal Validation'!I8</f>
+        <v>-1.42273562960327E-3</v>
+      </c>
+      <c r="AJ9" s="5">
+        <f>'Proximal Validation'!J8</f>
+        <v>-0.183252438902855</v>
+      </c>
+      <c r="AK9" s="5">
+        <f>'Proximal Validation'!K8</f>
+        <v>-1.30194798111916E-3</v>
+      </c>
+      <c r="AL9" s="5">
+        <f>'Proximal Validation'!L8</f>
+        <v>0.33158546686172502</v>
+      </c>
+      <c r="AM9" s="8">
+        <v>0.37681576666845534</v>
+      </c>
+      <c r="AN9" s="8">
+        <v>0.17145293786707433</v>
+      </c>
+      <c r="AO9" s="8">
+        <v>1.5789638668037855</v>
+      </c>
+      <c r="AP9" s="8">
+        <v>3.3490254406438571E-4</v>
+      </c>
+      <c r="AQ9" s="5">
+        <f t="shared" si="5"/>
+        <v>-2.3184233331544679E-2</v>
+      </c>
+      <c r="AR9" s="5">
+        <f t="shared" si="6"/>
+        <v>1.1452937867074325E-2</v>
+      </c>
+      <c r="AS9" s="5">
+        <f t="shared" si="7"/>
+        <v>8.1675400088889738E-3</v>
+      </c>
+      <c r="AT9" s="5">
+        <f t="shared" si="8"/>
+        <v>2.3184233331544679E-2</v>
+      </c>
+      <c r="AU9" s="5">
+        <f t="shared" si="1"/>
+        <v>1.1452937867074325E-2</v>
+      </c>
+      <c r="AV9" s="5">
+        <f t="shared" si="2"/>
+        <v>8.1675400088889738E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <f>'Proximal Validation'!A9</f>
         <v>0.6</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B10" s="5">
         <f>'Proximal Validation'!B9</f>
         <v>0.16</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C10" s="5">
         <f>'Proximal Validation'!C9</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D10" s="5">
         <f>'Proximal Validation'!D9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E10" s="5">
         <f>'Proximal Validation'!E9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F10" s="5">
         <f>'Proximal Validation'!F9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G10" s="5">
         <f>'Proximal Validation'!G9</f>
         <v>-8.4166455781087301E-4</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H10" s="5">
         <f>'Proximal Validation'!H9</f>
         <v>-0.141347721219063</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I10" s="5">
         <f>'Proximal Validation'!I9</f>
         <v>-2.4875707458704701E-3</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J10" s="5">
         <f>'Proximal Validation'!J9</f>
         <v>-0.39468729496002197</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K10" s="5">
         <f>'Proximal Validation'!K9</f>
         <v>-9.2538818717002901E-4</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L10" s="5">
         <f>'Proximal Validation'!L9</f>
         <v>0.469948559999466</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M10" s="8">
         <v>0.56497426045613874</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N10" s="8">
         <v>0.16528493275999942</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O10" s="8">
         <v>1.580299241084306</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P10" s="8">
         <v>3.1827266330454809E-4</v>
       </c>
-      <c r="Q9" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q10" s="5">
+        <f t="shared" si="3"/>
         <v>-3.5025739543861234E-2</v>
       </c>
-      <c r="R9" s="5">
-        <f t="shared" si="1"/>
+      <c r="R10" s="5">
+        <f t="shared" si="3"/>
         <v>5.2849327599994167E-3</v>
       </c>
-      <c r="S9" s="5">
-        <f t="shared" si="1"/>
+      <c r="S10" s="5">
+        <f t="shared" si="3"/>
         <v>9.5029142894094143E-3</v>
       </c>
-      <c r="T9" s="5">
-        <f t="shared" si="2"/>
+      <c r="T10" s="5">
+        <f t="shared" si="4"/>
         <v>3.5025739543861234E-2</v>
       </c>
-      <c r="U9" s="5">
+      <c r="U10" s="5">
         <f t="shared" si="0"/>
         <v>5.2849327599994167E-3</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V10" s="5">
         <f t="shared" si="0"/>
         <v>9.5029142894094143E-3</v>
       </c>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="AA10" s="5">
+        <f>'Proximal Validation'!A9</f>
+        <v>0.6</v>
+      </c>
+      <c r="AB10" s="5">
+        <f>'Proximal Validation'!B9</f>
+        <v>0.16</v>
+      </c>
+      <c r="AC10" s="5">
+        <f>'Proximal Validation'!C9</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD10" s="5">
+        <f>'Proximal Validation'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="5">
+        <f>'Proximal Validation'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <f>'Proximal Validation'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <f>'Proximal Validation'!G9</f>
+        <v>-8.4166455781087301E-4</v>
+      </c>
+      <c r="AH10" s="5">
+        <f>'Proximal Validation'!H9</f>
+        <v>-0.141347721219063</v>
+      </c>
+      <c r="AI10" s="5">
+        <f>'Proximal Validation'!I9</f>
+        <v>-2.4875707458704701E-3</v>
+      </c>
+      <c r="AJ10" s="5">
+        <f>'Proximal Validation'!J9</f>
+        <v>-0.39468729496002197</v>
+      </c>
+      <c r="AK10" s="5">
+        <f>'Proximal Validation'!K9</f>
+        <v>-9.2538818717002901E-4</v>
+      </c>
+      <c r="AL10" s="5">
+        <f>'Proximal Validation'!L9</f>
+        <v>0.469948559999466</v>
+      </c>
+      <c r="AM10" s="8">
+        <v>0.53446524716448018</v>
+      </c>
+      <c r="AN10" s="8">
+        <v>0.16715553633788641</v>
+      </c>
+      <c r="AO10" s="8">
+        <v>1.5778248279571701</v>
+      </c>
+      <c r="AP10" s="8">
+        <v>3.781470249735663E-4</v>
+      </c>
+      <c r="AQ10" s="5">
+        <f t="shared" si="5"/>
+        <v>-6.5534752835519794E-2</v>
+      </c>
+      <c r="AR10" s="5">
+        <f t="shared" si="6"/>
+        <v>7.1555363378864034E-3</v>
+      </c>
+      <c r="AS10" s="5">
+        <f t="shared" si="7"/>
+        <v>7.0285011622734928E-3</v>
+      </c>
+      <c r="AT10" s="5">
+        <f t="shared" si="8"/>
+        <v>6.5534752835519794E-2</v>
+      </c>
+      <c r="AU10" s="5">
+        <f t="shared" si="1"/>
+        <v>7.1555363378864034E-3</v>
+      </c>
+      <c r="AV10" s="5">
+        <f t="shared" si="2"/>
+        <v>7.0285011622734928E-3</v>
+      </c>
+      <c r="AW10" s="7"/>
+      <c r="AX10" s="7"/>
+      <c r="AY10" s="7"/>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <f>'Proximal Validation'!A10</f>
         <v>0.8</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B11" s="5">
         <f>'Proximal Validation'!B10</f>
         <v>0.18</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C11" s="5">
         <f>'Proximal Validation'!C10</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D11" s="5">
         <f>'Proximal Validation'!D10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E11" s="5">
         <f>'Proximal Validation'!E10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F11" s="5">
         <f>'Proximal Validation'!F10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G11" s="5">
         <f>'Proximal Validation'!G10</f>
         <v>-2.5411224924027898E-3</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H11" s="5">
         <f>'Proximal Validation'!H10</f>
         <v>-0.16168536245822901</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I11" s="5">
         <f>'Proximal Validation'!I10</f>
         <v>-2.0260578021407101E-3</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J11" s="5">
         <f>'Proximal Validation'!J10</f>
         <v>-0.81751561164856001</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K11" s="5">
         <f>'Proximal Validation'!K10</f>
         <v>1.46271400153637E-2</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L11" s="5">
         <f>'Proximal Validation'!L10</f>
         <v>0.27560678124427801</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M11" s="8">
         <v>0.83481970399375527</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N11" s="8">
         <v>0.16829695270786463</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O11" s="8">
         <v>1.5875321449709592</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P11" s="8">
         <v>2.6277613828493574E-4</v>
       </c>
-      <c r="Q10" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q11" s="5">
+        <f t="shared" si="3"/>
         <v>3.4819703993755224E-2</v>
       </c>
-      <c r="R10" s="5">
-        <f t="shared" si="1"/>
+      <c r="R11" s="5">
+        <f t="shared" si="3"/>
         <v>-1.1703047292135366E-2</v>
       </c>
-      <c r="S10" s="5">
-        <f t="shared" si="1"/>
+      <c r="S11" s="5">
+        <f t="shared" si="3"/>
         <v>1.6735818176062622E-2</v>
       </c>
-      <c r="T10" s="5">
-        <f t="shared" si="2"/>
+      <c r="T11" s="5">
+        <f t="shared" si="4"/>
         <v>3.4819703993755224E-2</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U11" s="5">
         <f t="shared" si="0"/>
         <v>1.1703047292135366E-2</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V11" s="5">
         <f t="shared" si="0"/>
         <v>1.6735818176062622E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="AA11" s="5">
+        <f>'Proximal Validation'!A10</f>
+        <v>0.8</v>
+      </c>
+      <c r="AB11" s="5">
+        <f>'Proximal Validation'!B10</f>
+        <v>0.18</v>
+      </c>
+      <c r="AC11" s="5">
+        <f>'Proximal Validation'!C10</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD11" s="5">
+        <f>'Proximal Validation'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="5">
+        <f>'Proximal Validation'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <f>'Proximal Validation'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <f>'Proximal Validation'!G10</f>
+        <v>-2.5411224924027898E-3</v>
+      </c>
+      <c r="AH11" s="5">
+        <f>'Proximal Validation'!H10</f>
+        <v>-0.16168536245822901</v>
+      </c>
+      <c r="AI11" s="5">
+        <f>'Proximal Validation'!I10</f>
+        <v>-2.0260578021407101E-3</v>
+      </c>
+      <c r="AJ11" s="5">
+        <f>'Proximal Validation'!J10</f>
+        <v>-0.81751561164856001</v>
+      </c>
+      <c r="AK11" s="5">
+        <f>'Proximal Validation'!K10</f>
+        <v>1.46271400153637E-2</v>
+      </c>
+      <c r="AL11" s="5">
+        <f>'Proximal Validation'!L10</f>
+        <v>0.27560678124427801</v>
+      </c>
+      <c r="AM11" s="8">
+        <v>0.7316346965236179</v>
+      </c>
+      <c r="AN11" s="8">
+        <v>0.17208978326093791</v>
+      </c>
+      <c r="AO11" s="8">
+        <v>1.585755622395886</v>
+      </c>
+      <c r="AP11" s="8">
+        <v>3.0318542166298695E-4</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f t="shared" si="5"/>
+        <v>-6.8365303476382144E-2</v>
+      </c>
+      <c r="AR11" s="5">
+        <f t="shared" si="6"/>
+        <v>-7.910216739062087E-3</v>
+      </c>
+      <c r="AS11" s="5">
+        <f t="shared" si="7"/>
+        <v>1.4959295600989408E-2</v>
+      </c>
+      <c r="AT11" s="5">
+        <f t="shared" si="8"/>
+        <v>6.8365303476382144E-2</v>
+      </c>
+      <c r="AU11" s="5">
+        <f t="shared" si="1"/>
+        <v>7.910216739062087E-3</v>
+      </c>
+      <c r="AV11" s="5">
+        <f t="shared" si="2"/>
+        <v>1.4959295600989408E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <f>'Proximal Validation'!A11</f>
         <v>0.3</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B12" s="5">
         <f>'Proximal Validation'!B11</f>
         <v>0.2</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C12" s="5">
         <f>'Proximal Validation'!C11</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D12" s="5">
         <f>'Proximal Validation'!D11</f>
         <v>0</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="5">
         <f>'Proximal Validation'!E11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F12" s="5">
         <f>'Proximal Validation'!F11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G12" s="5">
         <f>'Proximal Validation'!G11</f>
         <v>-7.7232124749571096E-4</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H12" s="5">
         <f>'Proximal Validation'!H11</f>
         <v>-7.1722365915775299E-2</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I12" s="5">
         <f>'Proximal Validation'!I11</f>
         <v>-7.8877643682062604E-4</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J12" s="5">
         <f>'Proximal Validation'!J11</f>
         <v>-0.14824971556663499</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K12" s="5">
         <f>'Proximal Validation'!K11</f>
         <v>-2.5316514074802399E-4</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L12" s="5">
         <f>'Proximal Validation'!L11</f>
         <v>0.21111465990543399</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M12" s="8">
         <v>0.30032903077135142</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N12" s="8">
         <v>0.19999999998884047</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O12" s="8">
         <v>1.577600833859351</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P12" s="8">
         <v>5.7301024997264923E-4</v>
       </c>
-      <c r="Q11" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q12" s="5">
+        <f t="shared" si="3"/>
         <v>3.290307713514351E-4</v>
       </c>
-      <c r="R11" s="5">
-        <f t="shared" si="1"/>
+      <c r="R12" s="5">
+        <f t="shared" si="3"/>
         <v>-1.1159545509897839E-11</v>
       </c>
-      <c r="S11" s="5">
-        <f t="shared" si="1"/>
+      <c r="S12" s="5">
+        <f t="shared" si="3"/>
         <v>6.804507064454457E-3</v>
       </c>
-      <c r="T11" s="5">
-        <f t="shared" si="2"/>
+      <c r="T12" s="5">
+        <f t="shared" si="4"/>
         <v>3.290307713514351E-4</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U12" s="5">
         <f t="shared" si="0"/>
         <v>1.1159545509897839E-11</v>
       </c>
-      <c r="V11" s="5">
+      <c r="V12" s="5">
         <f t="shared" si="0"/>
         <v>6.804507064454457E-3</v>
       </c>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="AA12" s="5">
+        <f>'Proximal Validation'!A11</f>
+        <v>0.3</v>
+      </c>
+      <c r="AB12" s="5">
+        <f>'Proximal Validation'!B11</f>
+        <v>0.2</v>
+      </c>
+      <c r="AC12" s="5">
+        <f>'Proximal Validation'!C11</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD12" s="5">
+        <f>'Proximal Validation'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="5">
+        <f>'Proximal Validation'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="5">
+        <f>'Proximal Validation'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="5">
+        <f>'Proximal Validation'!G11</f>
+        <v>-7.7232124749571096E-4</v>
+      </c>
+      <c r="AH12" s="5">
+        <f>'Proximal Validation'!H11</f>
+        <v>-7.1722365915775299E-2</v>
+      </c>
+      <c r="AI12" s="5">
+        <f>'Proximal Validation'!I11</f>
+        <v>-7.8877643682062604E-4</v>
+      </c>
+      <c r="AJ12" s="5">
+        <f>'Proximal Validation'!J11</f>
+        <v>-0.14824971556663499</v>
+      </c>
+      <c r="AK12" s="5">
+        <f>'Proximal Validation'!K11</f>
+        <v>-2.5316514074802399E-4</v>
+      </c>
+      <c r="AL12" s="5">
+        <f>'Proximal Validation'!L11</f>
+        <v>0.21111465990543399</v>
+      </c>
+      <c r="AM12" s="8">
+        <v>0.29592508164170878</v>
+      </c>
+      <c r="AN12" s="8">
+        <v>0.19999999999997781</v>
+      </c>
+      <c r="AO12" s="8">
+        <v>1.5785429502112804</v>
+      </c>
+      <c r="AP12" s="8">
+        <v>6.972532612836978E-4</v>
+      </c>
+      <c r="AQ12" s="5">
+        <f t="shared" si="5"/>
+        <v>-4.074918358291213E-3</v>
+      </c>
+      <c r="AR12" s="5">
+        <f t="shared" si="6"/>
+        <v>-2.2204460492503131E-14</v>
+      </c>
+      <c r="AS12" s="5">
+        <f t="shared" si="7"/>
+        <v>7.7466234163838799E-3</v>
+      </c>
+      <c r="AT12" s="5">
+        <f t="shared" si="8"/>
+        <v>4.074918358291213E-3</v>
+      </c>
+      <c r="AU12" s="5">
+        <f t="shared" si="1"/>
+        <v>2.2204460492503131E-14</v>
+      </c>
+      <c r="AV12" s="5">
+        <f t="shared" si="2"/>
+        <v>7.7466234163838799E-3</v>
+      </c>
+      <c r="AW12" s="7"/>
+      <c r="AX12" s="7"/>
+      <c r="AY12" s="7"/>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <f>'Proximal Validation'!A12</f>
         <v>0.7</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <f>'Proximal Validation'!B12</f>
         <v>0.2</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C13" s="5">
         <f>'Proximal Validation'!C12</f>
         <v>1.5707963267948966</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D13" s="5">
         <f>'Proximal Validation'!D12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="5">
         <f>'Proximal Validation'!E12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="5">
         <f>'Proximal Validation'!F12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G13" s="5">
         <f>'Proximal Validation'!G12</f>
         <v>-1.37498124968261E-3</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H13" s="5">
         <f>'Proximal Validation'!H12</f>
         <v>-0.13238599896431</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I13" s="5">
         <f>'Proximal Validation'!I12</f>
         <v>-1.95983843877912E-3</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="5">
         <f>'Proximal Validation'!J12</f>
         <v>-0.64118611812591597</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K13" s="5">
         <f>'Proximal Validation'!K12</f>
         <v>9.5805265009403194E-3</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L13" s="5">
         <f>'Proximal Validation'!L12</f>
         <v>0.17886316776275599</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M13" s="8">
         <v>0.6627908436895753</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N13" s="8">
         <v>0.178739938276433</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O13" s="8">
         <v>1.5816122798542704</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P13" s="8">
         <v>2.8685918484907337E-4</v>
       </c>
-      <c r="Q12" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q13" s="5">
+        <f t="shared" si="3"/>
         <v>-3.7209156310424651E-2</v>
       </c>
-      <c r="R12" s="5">
-        <f t="shared" si="1"/>
+      <c r="R13" s="5">
+        <f t="shared" si="3"/>
         <v>-2.1260061723567009E-2</v>
       </c>
-      <c r="S12" s="5">
-        <f t="shared" si="1"/>
+      <c r="S13" s="5">
+        <f t="shared" si="3"/>
         <v>1.0815953059373884E-2</v>
       </c>
-      <c r="T12" s="5">
-        <f t="shared" si="2"/>
+      <c r="T13" s="5">
+        <f t="shared" si="4"/>
         <v>3.7209156310424651E-2</v>
       </c>
-      <c r="U12" s="5">
+      <c r="U13" s="5">
         <f t="shared" si="0"/>
         <v>2.1260061723567009E-2</v>
       </c>
-      <c r="V12" s="5">
+      <c r="V13" s="5">
         <f t="shared" si="0"/>
         <v>1.0815953059373884E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="AA13" s="5">
+        <f>'Proximal Validation'!A12</f>
+        <v>0.7</v>
+      </c>
+      <c r="AB13" s="5">
+        <f>'Proximal Validation'!B12</f>
+        <v>0.2</v>
+      </c>
+      <c r="AC13" s="5">
+        <f>'Proximal Validation'!C12</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="AD13" s="5">
+        <f>'Proximal Validation'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="5">
+        <f>'Proximal Validation'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="5">
+        <f>'Proximal Validation'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="5">
+        <f>'Proximal Validation'!G12</f>
+        <v>-1.37498124968261E-3</v>
+      </c>
+      <c r="AH13" s="5">
+        <f>'Proximal Validation'!H12</f>
+        <v>-0.13238599896431</v>
+      </c>
+      <c r="AI13" s="5">
+        <f>'Proximal Validation'!I12</f>
+        <v>-1.95983843877912E-3</v>
+      </c>
+      <c r="AJ13" s="5">
+        <f>'Proximal Validation'!J12</f>
+        <v>-0.64118611812591597</v>
+      </c>
+      <c r="AK13" s="5">
+        <f>'Proximal Validation'!K12</f>
+        <v>9.5805265009403194E-3</v>
+      </c>
+      <c r="AL13" s="5">
+        <f>'Proximal Validation'!L12</f>
+        <v>0.17886316776275599</v>
+      </c>
+      <c r="AM13" s="8">
+        <v>0.6021084022972677</v>
+      </c>
+      <c r="AN13" s="8">
+        <v>0.18165086373278252</v>
+      </c>
+      <c r="AO13" s="8">
+        <v>1.5799400389930107</v>
+      </c>
+      <c r="AP13" s="8">
+        <v>3.464397181053898E-4</v>
+      </c>
+      <c r="AQ13" s="5">
+        <f t="shared" si="5"/>
+        <v>-9.7891597702732258E-2</v>
+      </c>
+      <c r="AR13" s="5">
+        <f t="shared" si="6"/>
+        <v>-1.8349136267217486E-2</v>
+      </c>
+      <c r="AS13" s="5">
+        <f t="shared" si="7"/>
+        <v>9.1437121981141622E-3</v>
+      </c>
+      <c r="AT13" s="5">
+        <f t="shared" si="8"/>
+        <v>9.7891597702732258E-2</v>
+      </c>
+      <c r="AU13" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8349136267217486E-2</v>
+      </c>
+      <c r="AV13" s="5">
+        <f t="shared" si="2"/>
+        <v>9.1437121981141622E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>1</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>0</v>
-      </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -6221,106 +7251,85 @@
         <v>0</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C20" s="1" t="s">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="10">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <f t="shared" ref="D21:L21" si="3">D3</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <f t="shared" si="3"/>
-        <v>-4.37921960838139E-4</v>
-      </c>
-      <c r="H21" s="5">
-        <f t="shared" si="3"/>
-        <v>-5.4464954882860198E-2</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="3"/>
-        <v>-2.8745096642523999E-4</v>
-      </c>
-      <c r="J21" s="5">
-        <f t="shared" si="3"/>
-        <v>-2.13129706680775E-2</v>
-      </c>
-      <c r="K21" s="5">
-        <f t="shared" si="3"/>
-        <v>1.85158103704453E-4</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="3"/>
-        <v>0.34822303056716902</v>
-      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C22" s="10">
         <v>1</v>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <f t="shared" ref="D22:L22" si="9">D4</f>
+        <v>0</v>
       </c>
       <c r="E22" s="5">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F22" s="5">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>3.1034613493829998E-4</v>
+        <f t="shared" si="9"/>
+        <v>-4.37921960838139E-4</v>
       </c>
       <c r="H22" s="5">
-        <v>-4.40637990832329E-2</v>
+        <f t="shared" si="9"/>
+        <v>-5.4464954882860198E-2</v>
       </c>
       <c r="I22" s="5">
-        <v>-2.6626966428011699E-4</v>
+        <f t="shared" si="9"/>
+        <v>-2.8745096642523999E-4</v>
       </c>
       <c r="J22" s="5">
-        <v>-1.2337492778897299E-2</v>
+        <f t="shared" si="9"/>
+        <v>-2.13129706680775E-2</v>
       </c>
       <c r="K22" s="5">
-        <v>-2.0012184977531398E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.85158103704453E-4</v>
       </c>
       <c r="L22" s="5">
-        <v>0.28711792826652499</v>
+        <f t="shared" si="9"/>
+        <v>0.34822303056716902</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -6328,31 +7337,31 @@
         <v>1</v>
       </c>
       <c r="D23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5">
         <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>-4.5217655133456003E-4</v>
+        <v>3.1034613493829998E-4</v>
       </c>
       <c r="H23" s="5">
-        <v>-4.2780064046382897E-2</v>
+        <v>-4.40637990832329E-2</v>
       </c>
       <c r="I23" s="5">
-        <v>-2.9174645897001001E-4</v>
+        <v>-2.6626966428011699E-4</v>
       </c>
       <c r="J23" s="5">
-        <v>-1.0398513637483099E-2</v>
+        <v>-1.2337492778897299E-2</v>
       </c>
       <c r="K23" s="5">
-        <v>2.8434172272682199E-3</v>
+        <v>-2.0012184977531398E-3</v>
       </c>
       <c r="L23" s="5">
-        <v>0.27934211492538502</v>
+        <v>0.28711792826652499</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -6363,33 +7372,33 @@
         <v>0</v>
       </c>
       <c r="E24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5">
-        <v>-2.58053187280893E-4</v>
+        <v>-4.5217655133456003E-4</v>
       </c>
       <c r="H24" s="5">
-        <v>-6.3121601939201397E-2</v>
+        <v>-4.2780064046382897E-2</v>
       </c>
       <c r="I24" s="5">
-        <v>-4.25372389145195E-4</v>
+        <v>-2.9174645897001001E-4</v>
       </c>
       <c r="J24" s="5">
-        <v>-2.1438803523778902E-2</v>
+        <v>-1.0398513637483099E-2</v>
       </c>
       <c r="K24" s="5">
-        <v>8.5363537073135398E-4</v>
+        <v>2.8434172272682199E-3</v>
       </c>
       <c r="L24" s="5">
-        <v>0.41041621565818798</v>
+        <v>0.27934211492538502</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C25" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5">
         <v>0</v>
@@ -6398,31 +7407,25 @@
         <v>0</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5">
-        <f>G4</f>
-        <v>-1.2904058676213E-3</v>
+        <v>-2.58053187280893E-4</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:L25" si="4">H4</f>
-        <v>-0.130890563130379</v>
+        <v>-6.3121601939201397E-2</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="4"/>
-        <v>-5.0724833272397496E-4</v>
+        <v>-4.25372389145195E-4</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="4"/>
-        <v>-0.12710034847259499</v>
+        <v>-2.1438803523778902E-2</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="4"/>
-        <v>3.3702701330184902E-3</v>
+        <v>8.5363537073135398E-4</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="4"/>
-        <v>0.83409011363983199</v>
+        <v>0.41041621565818798</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -6430,7 +7433,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="5">
         <v>0</v>
@@ -6439,22 +7442,28 @@
         <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>-1.5963241457939099E-4</v>
+        <f>G5</f>
+        <v>-1.2904058676213E-3</v>
       </c>
       <c r="H26" s="5">
-        <v>-0.121562890708447</v>
+        <f t="shared" ref="H26:L26" si="10">H5</f>
+        <v>-0.130890563130379</v>
       </c>
       <c r="I26" s="5">
-        <v>-8.2839734386652697E-4</v>
+        <f t="shared" si="10"/>
+        <v>-5.0724833272397496E-4</v>
       </c>
       <c r="J26" s="5">
-        <v>-0.11515100300312001</v>
+        <f t="shared" si="10"/>
+        <v>-0.12710034847259499</v>
       </c>
       <c r="K26" s="5">
-        <v>-2.1543055772781398E-3</v>
+        <f t="shared" si="10"/>
+        <v>3.3702701330184902E-3</v>
       </c>
       <c r="L26" s="5">
-        <v>0.782032251358032</v>
+        <f t="shared" si="10"/>
+        <v>0.83409011363983199</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -6462,31 +7471,31 @@
         <v>2</v>
       </c>
       <c r="D27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="5">
         <v>0</v>
       </c>
       <c r="G27" s="5">
-        <v>-1.9617278594523699E-3</v>
+        <v>-1.5963241457939099E-4</v>
       </c>
       <c r="H27" s="5">
-        <v>-0.121123254299164</v>
+        <v>-0.121562890708447</v>
       </c>
       <c r="I27" s="5">
-        <v>-6.2098959460854503E-5</v>
+        <v>-8.2839734386652697E-4</v>
       </c>
       <c r="J27" s="5">
-        <v>-0.11508367210626599</v>
+        <v>-0.11515100300312001</v>
       </c>
       <c r="K27" s="5">
-        <v>8.6164399981498701E-3</v>
+        <v>-2.1543055772781398E-3</v>
       </c>
       <c r="L27" s="5">
-        <v>0.77998018264770497</v>
+        <v>0.782032251358032</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -6497,33 +7506,33 @@
         <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5">
-        <v>-1.25816813670099E-3</v>
+        <v>-1.9617278594523699E-3</v>
       </c>
       <c r="H28" s="5">
-        <v>-0.13559269905090299</v>
+        <v>-0.121123254299164</v>
       </c>
       <c r="I28" s="5">
-        <v>-5.3044769447296901E-4</v>
+        <v>-6.2098959460854503E-5</v>
       </c>
       <c r="J28" s="5">
-        <v>-0.134366035461426</v>
+        <v>-0.11508367210626599</v>
       </c>
       <c r="K28" s="5">
-        <v>4.1586309671402004E-3</v>
+        <v>8.6164399981498701E-3</v>
       </c>
       <c r="L28" s="5">
-        <v>0.87226921319961503</v>
+        <v>0.77998018264770497</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C29" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5">
         <v>0</v>
@@ -6532,31 +7541,25 @@
         <v>0</v>
       </c>
       <c r="F29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5">
-        <f>G5</f>
-        <v>-4.4532003812491899E-4</v>
+        <v>-1.25816813670099E-3</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" ref="H29:L29" si="5">H5</f>
-        <v>-4.79050725698471E-2</v>
+        <v>-0.13559269905090299</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="5"/>
-        <v>-1.45487196277827E-4</v>
+        <v>-5.3044769447296901E-4</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" si="5"/>
-        <v>-1.52218556031585E-2</v>
+        <v>-0.134366035461426</v>
       </c>
       <c r="K29" s="5">
-        <f t="shared" si="5"/>
-        <v>-1.61819159984589E-4</v>
+        <v>4.1586309671402004E-3</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="5"/>
-        <v>0.269099742174149</v>
+        <v>0.87226921319961503</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -6564,7 +7567,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
         <v>0</v>
@@ -6573,22 +7576,28 @@
         <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>1.9974156748503401E-4</v>
+        <f>G6</f>
+        <v>-4.4532003812491899E-4</v>
       </c>
       <c r="H30" s="5">
-        <v>-3.2512675970792798E-2</v>
+        <f t="shared" ref="H30:L30" si="11">H6</f>
+        <v>-4.79050725698471E-2</v>
       </c>
       <c r="I30" s="5">
-        <v>-1.71057123225182E-4</v>
+        <f t="shared" si="11"/>
+        <v>-1.45487196277827E-4</v>
       </c>
       <c r="J30" s="5">
-        <v>-8.0844657495617901E-3</v>
+        <f t="shared" si="11"/>
+        <v>-1.52218556031585E-2</v>
       </c>
       <c r="K30" s="5">
-        <v>-3.18075716495514E-3</v>
+        <f t="shared" si="11"/>
+        <v>-1.61819159984589E-4</v>
       </c>
       <c r="L30" s="5">
-        <v>0.18479597568511999</v>
+        <f t="shared" si="11"/>
+        <v>0.269099742174149</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -6596,31 +7605,31 @@
         <v>3</v>
       </c>
       <c r="D31" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
       </c>
       <c r="G31" s="5">
-        <v>-5.7576800463721199E-4</v>
+        <v>1.9974156748503401E-4</v>
       </c>
       <c r="H31" s="5">
-        <v>-3.0636494979262401E-2</v>
+        <v>-3.2512675970792798E-2</v>
       </c>
       <c r="I31" s="5">
-        <v>-9.7063733846880496E-5</v>
+        <v>-1.71057123225182E-4</v>
       </c>
       <c r="J31" s="5">
-        <v>-7.2050262242555601E-3</v>
+        <v>-8.0844657495617901E-3</v>
       </c>
       <c r="K31" s="5">
-        <v>1.8094088882207901E-3</v>
+        <v>-3.18075716495514E-3</v>
       </c>
       <c r="L31" s="5">
-        <v>0.17424859106540699</v>
+        <v>0.18479597568511999</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -6631,33 +7640,33 @@
         <v>0</v>
       </c>
       <c r="E32" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
-        <v>-5.8534357231110302E-4</v>
+        <v>-5.7576800463721199E-4</v>
       </c>
       <c r="H32" s="5">
-        <v>-6.0917992144823102E-2</v>
+        <v>-3.0636494979262401E-2</v>
       </c>
       <c r="I32" s="5">
-        <v>-1.45592755870894E-4</v>
+        <v>-9.7063733846880496E-5</v>
       </c>
       <c r="J32" s="5">
-        <v>-1.8382957205176399E-2</v>
+        <v>-7.2050262242555601E-3</v>
       </c>
       <c r="K32" s="5">
-        <v>9.1800466179847696E-4</v>
+        <v>1.8094088882207901E-3</v>
       </c>
       <c r="L32" s="5">
-        <v>0.34572017192840598</v>
+        <v>0.17424859106540699</v>
       </c>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C33" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="5">
         <v>0</v>
@@ -6666,31 +7675,25 @@
         <v>0</v>
       </c>
       <c r="F33" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="5">
-        <f>G6</f>
-        <v>-1.1705639772117101E-3</v>
+        <v>-5.8534357231110302E-4</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:L33" si="6">H6</f>
-        <v>-9.4456188380718203E-2</v>
+        <v>-6.0917992144823102E-2</v>
       </c>
       <c r="I33" s="5">
-        <f t="shared" si="6"/>
-        <v>-1.20323454029858E-3</v>
+        <v>-1.45592755870894E-4</v>
       </c>
       <c r="J33" s="5">
-        <f t="shared" si="6"/>
-        <v>-0.111187651753426</v>
+        <v>-1.8382957205176399E-2</v>
       </c>
       <c r="K33" s="5">
-        <f t="shared" si="6"/>
-        <v>-3.2553412020206499E-3</v>
+        <v>9.1800466179847696E-4</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="6"/>
-        <v>0.47075057029724099</v>
+        <v>0.34572017192840598</v>
       </c>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
@@ -6698,7 +7701,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="5">
         <v>0</v>
@@ -6707,22 +7710,28 @@
         <v>0</v>
       </c>
       <c r="G34" s="5">
-        <v>8.7243388406932395E-5</v>
+        <f>G7</f>
+        <v>-1.1705639772117101E-3</v>
       </c>
       <c r="H34" s="5">
-        <v>-8.1967003643512698E-2</v>
+        <f t="shared" ref="H34:L34" si="12">H7</f>
+        <v>-9.4456188380718203E-2</v>
       </c>
       <c r="I34" s="5">
-        <v>-1.8417512765154199E-3</v>
+        <f t="shared" si="12"/>
+        <v>-1.20323454029858E-3</v>
       </c>
       <c r="J34" s="5">
-        <v>-9.5461010932922405E-2</v>
+        <f t="shared" si="12"/>
+        <v>-0.111187651753426</v>
       </c>
       <c r="K34" s="5">
-        <v>-1.02448388934135E-2</v>
+        <f t="shared" si="12"/>
+        <v>-3.2553412020206499E-3</v>
       </c>
       <c r="L34" s="5">
-        <v>0.411044031381607</v>
+        <f t="shared" si="12"/>
+        <v>0.47075057029724099</v>
       </c>
     </row>
     <row r="35" spans="3:12" x14ac:dyDescent="0.25">
@@ -6730,31 +7739,31 @@
         <v>4</v>
       </c>
       <c r="D35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>-2.6281357277184699E-3</v>
+        <v>8.7243388406932395E-5</v>
       </c>
       <c r="H35" s="5">
-        <v>-7.9778142273426098E-2</v>
+        <v>-8.1967003643512698E-2</v>
       </c>
       <c r="I35" s="5">
-        <v>8.1456964835524593E-6</v>
+        <v>-1.8417512765154199E-3</v>
       </c>
       <c r="J35" s="5">
-        <v>-9.1968797147274003E-2</v>
+        <v>-9.5461010932922405E-2</v>
       </c>
       <c r="K35" s="5">
-        <v>4.9324836581945402E-3</v>
+        <v>-1.02448388934135E-2</v>
       </c>
       <c r="L35" s="5">
-        <v>0.401186943054199</v>
+        <v>0.411044031381607</v>
       </c>
     </row>
     <row r="36" spans="3:12" x14ac:dyDescent="0.25">
@@ -6765,33 +7774,33 @@
         <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5">
-        <v>-1.7928605666384101E-3</v>
+        <v>-2.6281357277184699E-3</v>
       </c>
       <c r="H36" s="5">
-        <v>-0.106283381581306</v>
+        <v>-7.9778142273426098E-2</v>
       </c>
       <c r="I36" s="5">
-        <v>-1.05142686516047E-3</v>
+        <v>8.1456964835524593E-6</v>
       </c>
       <c r="J36" s="5">
-        <v>-0.124293893575668</v>
+        <v>-9.1968797147274003E-2</v>
       </c>
       <c r="K36" s="5">
-        <v>-1.8899887800216701E-3</v>
+        <v>4.9324836581945402E-3</v>
       </c>
       <c r="L36" s="5">
-        <v>0.53177243471145597</v>
+        <v>0.401186943054199</v>
       </c>
     </row>
     <row r="37" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C37" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" s="5">
         <v>0</v>
@@ -6800,31 +7809,25 @@
         <v>0</v>
       </c>
       <c r="F37" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="5">
-        <f>G7</f>
-        <v>-1.5179968904703901E-3</v>
+        <v>-1.7928605666384101E-3</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37:L37" si="7">H7</f>
-        <v>-0.13914526998996701</v>
+        <v>-0.106283381581306</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" si="7"/>
-        <v>-1.6895274166017799E-3</v>
+        <v>-1.05142686516047E-3</v>
       </c>
       <c r="J37" s="5">
-        <f t="shared" si="7"/>
-        <v>-0.208347618579865</v>
+        <v>-0.124293893575668</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" si="7"/>
-        <v>-2.6145353913307199E-3</v>
+        <v>-1.8899887800216701E-3</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="7"/>
-        <v>0.69233715534210205</v>
+        <v>0.53177243471145597</v>
       </c>
     </row>
     <row r="38" spans="3:12" x14ac:dyDescent="0.25">
@@ -6832,7 +7835,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5">
         <v>0</v>
@@ -6841,22 +7844,28 @@
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>4.0320260450243999E-4</v>
+        <f>G8</f>
+        <v>-1.5179968904703901E-3</v>
       </c>
       <c r="H38" s="5">
-        <v>-0.12612909078598</v>
+        <f t="shared" ref="H38:L38" si="13">H8</f>
+        <v>-0.13914526998996701</v>
       </c>
       <c r="I38" s="5">
-        <v>-2.7437012176960698E-3</v>
+        <f t="shared" si="13"/>
+        <v>-1.6895274166017799E-3</v>
       </c>
       <c r="J38" s="5">
-        <v>-0.18591290712356601</v>
+        <f t="shared" si="13"/>
+        <v>-0.208347618579865</v>
       </c>
       <c r="K38" s="5">
-        <v>-1.28864273428917E-2</v>
+        <f t="shared" si="13"/>
+        <v>-2.6145353913307199E-3</v>
       </c>
       <c r="L38" s="5">
-        <v>0.63056266307830799</v>
+        <f t="shared" si="13"/>
+        <v>0.69233715534210205</v>
       </c>
     </row>
     <row r="39" spans="3:12" x14ac:dyDescent="0.25">
@@ -6864,31 +7873,31 @@
         <v>5</v>
       </c>
       <c r="D39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>-3.60359740443528E-3</v>
+        <v>4.0320260450243999E-4</v>
       </c>
       <c r="H39" s="5">
-        <v>-0.123284801840782</v>
+        <v>-0.12612909078598</v>
       </c>
       <c r="I39" s="5">
-        <v>1.3838161248713699E-4</v>
+        <v>-2.7437012176960698E-3</v>
       </c>
       <c r="J39" s="5">
-        <v>-0.18036614358425099</v>
+        <v>-0.18591290712356601</v>
       </c>
       <c r="K39" s="5">
-        <v>9.5373615622520395E-3</v>
+        <v>-1.28864273428917E-2</v>
       </c>
       <c r="L39" s="5">
-        <v>0.61717545986175504</v>
+        <v>0.63056266307830799</v>
       </c>
     </row>
     <row r="40" spans="3:12" x14ac:dyDescent="0.25">
@@ -6899,33 +7908,33 @@
         <v>0</v>
       </c>
       <c r="E40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>-2.0965661387890599E-3</v>
+        <v>-3.60359740443528E-3</v>
       </c>
       <c r="H40" s="5">
-        <v>-0.147491469979286</v>
+        <v>-0.123284801840782</v>
       </c>
       <c r="I40" s="5">
-        <v>-1.3944744132459201E-3</v>
+        <v>1.3838161248713699E-4</v>
       </c>
       <c r="J40" s="5">
-        <v>-0.22115431725978901</v>
+        <v>-0.18036614358425099</v>
       </c>
       <c r="K40" s="5">
-        <v>-3.3147633075714098E-5</v>
+        <v>9.5373615622520395E-3</v>
       </c>
       <c r="L40" s="5">
-        <v>0.73367011547088601</v>
+        <v>0.61717545986175504</v>
       </c>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C41" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" s="5">
         <v>0</v>
@@ -6934,31 +7943,25 @@
         <v>0</v>
       </c>
       <c r="F41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5">
-        <f>G8</f>
-        <v>-6.0909817693754998E-4</v>
+        <v>-2.0965661387890599E-3</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" ref="H41:L41" si="8">H8</f>
-        <v>-9.3464262783527402E-2</v>
+        <v>-0.147491469979286</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" si="8"/>
-        <v>-1.42273562960327E-3</v>
+        <v>-1.3944744132459201E-3</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="8"/>
-        <v>-0.183252438902855</v>
+        <v>-0.22115431725978901</v>
       </c>
       <c r="K41" s="5">
-        <f t="shared" si="8"/>
-        <v>-1.30194798111916E-3</v>
+        <v>-3.3147633075714098E-5</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="8"/>
-        <v>0.33158546686172502</v>
+        <v>0.73367011547088601</v>
       </c>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.25">
@@ -6966,7 +7969,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
         <v>0</v>
@@ -6975,22 +7978,28 @@
         <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>2.1256739273667301E-3</v>
+        <f>G9</f>
+        <v>-6.0909817693754998E-4</v>
       </c>
       <c r="H42" s="5">
-        <v>-8.1501223146915394E-2</v>
+        <f t="shared" ref="H42:L42" si="14">H9</f>
+        <v>-9.3464262783527402E-2</v>
       </c>
       <c r="I42" s="5">
-        <v>-3.6365091800689702E-3</v>
+        <f t="shared" si="14"/>
+        <v>-1.42273562960327E-3</v>
       </c>
       <c r="J42" s="5">
-        <v>-0.15839047729969</v>
+        <f t="shared" si="14"/>
+        <v>-0.183252438902855</v>
       </c>
       <c r="K42" s="5">
-        <v>-1.5761572867631898E-2</v>
+        <f t="shared" si="14"/>
+        <v>-1.30194798111916E-3</v>
       </c>
       <c r="L42" s="5">
-        <v>0.29118153452873202</v>
+        <f t="shared" si="14"/>
+        <v>0.33158546686172502</v>
       </c>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.25">
@@ -6998,31 +8007,31 @@
         <v>6</v>
       </c>
       <c r="D43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>-3.4697111696004898E-3</v>
+        <v>2.1256739273667301E-3</v>
       </c>
       <c r="H43" s="5">
-        <v>-7.9126335680484799E-2</v>
+        <v>-8.1501223146915394E-2</v>
       </c>
       <c r="I43" s="5">
-        <v>1.4140863204374901E-3</v>
+        <v>-3.6365091800689702E-3</v>
       </c>
       <c r="J43" s="5">
-        <v>-0.15318381786346399</v>
+        <v>-0.15839047729969</v>
       </c>
       <c r="K43" s="5">
-        <v>1.42920073121786E-2</v>
+        <v>-1.5761572867631898E-2</v>
       </c>
       <c r="L43" s="5">
-        <v>0.28343707323074302</v>
+        <v>0.29118153452873202</v>
       </c>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.25">
@@ -7033,33 +8042,33 @@
         <v>0</v>
       </c>
       <c r="E44" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>-1.4034989289939399E-3</v>
+        <v>-3.4697111696004898E-3</v>
       </c>
       <c r="H44" s="5">
-        <v>-0.10893576592206999</v>
+        <v>-7.9126335680484799E-2</v>
       </c>
       <c r="I44" s="5">
-        <v>-1.0244118748232701E-3</v>
+        <v>1.4140863204374901E-3</v>
       </c>
       <c r="J44" s="5">
-        <v>-0.21598881483078</v>
+        <v>-0.15318381786346399</v>
       </c>
       <c r="K44" s="5">
-        <v>2.0247809588909101E-3</v>
+        <v>1.42920073121786E-2</v>
       </c>
       <c r="L44" s="5">
-        <v>0.38628801703453097</v>
+        <v>0.28343707323074302</v>
       </c>
     </row>
     <row r="45" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C45" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" s="5">
         <v>0</v>
@@ -7068,31 +8077,25 @@
         <v>0</v>
       </c>
       <c r="F45" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5">
-        <f>G9</f>
-        <v>-8.4166455781087301E-4</v>
+        <v>-1.4034989289939399E-3</v>
       </c>
       <c r="H45" s="5">
-        <f t="shared" ref="H45:L45" si="9">H9</f>
-        <v>-0.141347721219063</v>
+        <v>-0.10893576592206999</v>
       </c>
       <c r="I45" s="5">
-        <f t="shared" si="9"/>
-        <v>-2.4875707458704701E-3</v>
+        <v>-1.0244118748232701E-3</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="9"/>
-        <v>-0.39468729496002197</v>
+        <v>-0.21598881483078</v>
       </c>
       <c r="K45" s="5">
-        <f t="shared" si="9"/>
-        <v>-9.2538818717002901E-4</v>
+        <v>2.0247809588909101E-3</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="9"/>
-        <v>0.469948559999466</v>
+        <v>0.38628801703453097</v>
       </c>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.25">
@@ -7100,7 +8103,7 @@
         <v>7</v>
       </c>
       <c r="D46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="5">
         <v>0</v>
@@ -7109,22 +8112,28 @@
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>3.8443636149168002E-3</v>
+        <f>G10</f>
+        <v>-8.4166455781087301E-4</v>
       </c>
       <c r="H46" s="5">
-        <v>-0.12736497819423701</v>
+        <f t="shared" ref="H46:L46" si="15">H10</f>
+        <v>-0.141347721219063</v>
       </c>
       <c r="I46" s="5">
-        <v>-5.8701047673821397E-3</v>
+        <f t="shared" si="15"/>
+        <v>-2.4875707458704701E-3</v>
       </c>
       <c r="J46" s="5">
-        <v>-0.35098621249198902</v>
+        <f t="shared" si="15"/>
+        <v>-0.39468729496002197</v>
       </c>
       <c r="K46" s="5">
-        <v>-2.6046320796012899E-2</v>
+        <f t="shared" si="15"/>
+        <v>-9.2538818717002901E-4</v>
       </c>
       <c r="L46" s="5">
-        <v>0.426019728183746</v>
+        <f t="shared" si="15"/>
+        <v>0.469948559999466</v>
       </c>
     </row>
     <row r="47" spans="3:12" x14ac:dyDescent="0.25">
@@ -7132,31 +8141,31 @@
         <v>7</v>
       </c>
       <c r="D47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="5">
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>-4.7293268144130698E-3</v>
+        <v>3.8443636149168002E-3</v>
       </c>
       <c r="H47" s="5">
-        <v>-0.12588208913803101</v>
+        <v>-0.12736497819423701</v>
       </c>
       <c r="I47" s="5">
-        <v>9.4564992468804099E-4</v>
+        <v>-5.8701047673821397E-3</v>
       </c>
       <c r="J47" s="5">
-        <v>-0.346735060214996</v>
+        <v>-0.35098621249198902</v>
       </c>
       <c r="K47" s="5">
-        <v>2.07273736596107E-2</v>
+        <v>-2.6046320796012899E-2</v>
       </c>
       <c r="L47" s="5">
-        <v>0.42136827111244202</v>
+        <v>0.426019728183746</v>
       </c>
     </row>
     <row r="48" spans="3:12" x14ac:dyDescent="0.25">
@@ -7167,33 +8176,33 @@
         <v>0</v>
       </c>
       <c r="E48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>-1.6190472524613101E-3</v>
+        <v>-4.7293268144130698E-3</v>
       </c>
       <c r="H48" s="5">
-        <v>-0.15216569602489499</v>
+        <v>-0.12588208913803101</v>
       </c>
       <c r="I48" s="5">
-        <v>-2.0947058219462598E-3</v>
+        <v>9.4564992468804099E-4</v>
       </c>
       <c r="J48" s="5">
-        <v>-0.42657080292701699</v>
+        <v>-0.346735060214996</v>
       </c>
       <c r="K48" s="5">
-        <v>2.95922160148621E-3</v>
+        <v>2.07273736596107E-2</v>
       </c>
       <c r="L48" s="5">
-        <v>0.50341123342514005</v>
+        <v>0.42136827111244202</v>
       </c>
     </row>
     <row r="49" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C49" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="5">
         <v>0</v>
@@ -7202,31 +8211,25 @@
         <v>0</v>
       </c>
       <c r="F49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="5">
-        <f>G10</f>
-        <v>-2.5411224924027898E-3</v>
+        <v>-1.6190472524613101E-3</v>
       </c>
       <c r="H49" s="5">
-        <f t="shared" ref="H49:L49" si="10">H10</f>
-        <v>-0.16168536245822901</v>
+        <v>-0.15216569602489499</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="10"/>
-        <v>-2.0260578021407101E-3</v>
+        <v>-2.0947058219462598E-3</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="10"/>
-        <v>-0.81751561164856001</v>
+        <v>-0.42657080292701699</v>
       </c>
       <c r="K49" s="5">
-        <f t="shared" si="10"/>
-        <v>1.46271400153637E-2</v>
+        <v>2.95922160148621E-3</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="10"/>
-        <v>0.27560678124427801</v>
+        <v>0.50341123342514005</v>
       </c>
     </row>
     <row r="50" spans="3:12" x14ac:dyDescent="0.25">
@@ -7234,7 +8237,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="5">
         <v>0</v>
@@ -7243,22 +8246,28 @@
         <v>0</v>
       </c>
       <c r="G50" s="5">
-        <v>2.7138160075992298E-3</v>
+        <f>G11</f>
+        <v>-2.5411224924027898E-3</v>
       </c>
       <c r="H50" s="5">
-        <v>-0.148533850908279</v>
+        <f t="shared" ref="H50:L50" si="16">H11</f>
+        <v>-0.16168536245822901</v>
       </c>
       <c r="I50" s="5">
-        <v>-4.7276630066335201E-3</v>
+        <f t="shared" si="16"/>
+        <v>-2.0260578021407101E-3</v>
       </c>
       <c r="J50" s="5">
-        <v>-0.74681681394577004</v>
+        <f t="shared" si="16"/>
+        <v>-0.81751561164856001</v>
       </c>
       <c r="K50" s="5">
-        <v>-1.84046011418104E-2</v>
+        <f t="shared" si="16"/>
+        <v>1.46271400153637E-2</v>
       </c>
       <c r="L50" s="5">
-        <v>0.25869399309158297</v>
+        <f t="shared" si="16"/>
+        <v>0.27560678124427801</v>
       </c>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.25">
@@ -7266,31 +8275,31 @@
         <v>8</v>
       </c>
       <c r="D51" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5">
         <v>0</v>
       </c>
       <c r="G51" s="5">
-        <v>-8.3056669682264293E-3</v>
+        <v>2.7138160075992298E-3</v>
       </c>
       <c r="H51" s="5">
-        <v>-0.14515875279903401</v>
+        <v>-0.148533850908279</v>
       </c>
       <c r="I51" s="5">
-        <v>1.6626357100904001E-3</v>
+        <v>-4.7276630066335201E-3</v>
       </c>
       <c r="J51" s="5">
-        <v>-0.72912079095840499</v>
+        <v>-0.74681681394577004</v>
       </c>
       <c r="K51" s="5">
-        <v>4.7625131905078902E-2</v>
+        <v>-1.84046011418104E-2</v>
       </c>
       <c r="L51" s="5">
-        <v>0.255448818206787</v>
+        <v>0.25869399309158297</v>
       </c>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
@@ -7301,33 +8310,33 @@
         <v>0</v>
       </c>
       <c r="E52" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5">
-        <v>-3.82994743995368E-3</v>
+        <v>-8.3056669682264293E-3</v>
       </c>
       <c r="H52" s="5">
-        <v>-0.16439875960350001</v>
+        <v>-0.14515875279903401</v>
       </c>
       <c r="I52" s="5">
-        <v>-1.33302470203489E-3</v>
+        <v>1.6626357100904001E-3</v>
       </c>
       <c r="J52" s="5">
-        <v>-0.83642917871475198</v>
+        <v>-0.72912079095840499</v>
       </c>
       <c r="K52" s="5">
-        <v>2.1142318844795199E-2</v>
+        <v>4.7625131905078902E-2</v>
       </c>
       <c r="L52" s="5">
-        <v>0.275511234998703</v>
+        <v>0.255448818206787</v>
       </c>
     </row>
     <row r="53" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C53" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="5">
         <v>0</v>
@@ -7336,31 +8345,25 @@
         <v>0</v>
       </c>
       <c r="F53" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="5">
-        <f>G11</f>
-        <v>-7.7232124749571096E-4</v>
+        <v>-3.82994743995368E-3</v>
       </c>
       <c r="H53" s="5">
-        <f t="shared" ref="H53:L53" si="11">H11</f>
-        <v>-7.1722365915775299E-2</v>
+        <v>-0.16439875960350001</v>
       </c>
       <c r="I53" s="5">
-        <f t="shared" si="11"/>
-        <v>-7.8877643682062604E-4</v>
+        <v>-1.33302470203489E-3</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="11"/>
-        <v>-0.14824971556663499</v>
+        <v>-0.83642917871475198</v>
       </c>
       <c r="K53" s="5">
-        <f t="shared" si="11"/>
-        <v>-2.5316514074802399E-4</v>
+        <v>2.1142318844795199E-2</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="11"/>
-        <v>0.21111465990543399</v>
+        <v>0.275511234998703</v>
       </c>
     </row>
     <row r="54" spans="3:12" x14ac:dyDescent="0.25">
@@ -7368,7 +8371,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="5">
         <v>0</v>
@@ -7377,22 +8380,28 @@
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>2.1917819976806602E-3</v>
+        <f>G12</f>
+        <v>-7.7232124749571096E-4</v>
       </c>
       <c r="H54" s="5">
-        <v>-5.7274989783763899E-2</v>
+        <f t="shared" ref="H54:L54" si="17">H12</f>
+        <v>-7.1722365915775299E-2</v>
       </c>
       <c r="I54" s="5">
-        <v>-3.6934348754584798E-3</v>
+        <f t="shared" si="17"/>
+        <v>-7.8877643682062604E-4</v>
       </c>
       <c r="J54" s="5">
-        <v>-0.115169636905193</v>
+        <f t="shared" si="17"/>
+        <v>-0.14824971556663499</v>
       </c>
       <c r="K54" s="5">
-        <v>-1.6218468546867398E-2</v>
+        <f t="shared" si="17"/>
+        <v>-2.5316514074802399E-4</v>
       </c>
       <c r="L54" s="5">
-        <v>0.169412106275558</v>
+        <f t="shared" si="17"/>
+        <v>0.21111465990543399</v>
       </c>
     </row>
     <row r="55" spans="3:12" x14ac:dyDescent="0.25">
@@ -7400,31 +8409,31 @@
         <v>9</v>
       </c>
       <c r="D55" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="5">
         <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>-4.1306661441922196E-3</v>
+        <v>2.1917819976806602E-3</v>
       </c>
       <c r="H55" s="5">
-        <v>-5.5268872529268299E-2</v>
+        <v>-5.7274989783763899E-2</v>
       </c>
       <c r="I55" s="5">
-        <v>3.15179536119103E-3</v>
+        <v>-3.6934348754584798E-3</v>
       </c>
       <c r="J55" s="5">
-        <v>-0.111157171428204</v>
+        <v>-0.115169636905193</v>
       </c>
       <c r="K55" s="5">
-        <v>1.7719671130180401E-2</v>
+        <v>-1.6218468546867398E-2</v>
       </c>
       <c r="L55" s="5">
-        <v>0.16463512182235701</v>
+        <v>0.169412106275558</v>
       </c>
     </row>
     <row r="56" spans="3:12" x14ac:dyDescent="0.25">
@@ -7435,33 +8444,33 @@
         <v>0</v>
       </c>
       <c r="E56" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5">
-        <v>-1.69308739714324E-3</v>
+        <v>-4.1306661441922196E-3</v>
       </c>
       <c r="H56" s="5">
-        <v>-8.5631921887397794E-2</v>
+        <v>-5.5268872529268299E-2</v>
       </c>
       <c r="I56" s="5">
-        <v>-4.7984158300096203E-5</v>
+        <v>3.15179536119103E-3</v>
       </c>
       <c r="J56" s="5">
-        <v>-0.18053941428661299</v>
+        <v>-0.111157171428204</v>
       </c>
       <c r="K56" s="5">
-        <v>4.4441134668886696E-3</v>
+        <v>1.7719671130180401E-2</v>
       </c>
       <c r="L56" s="5">
-        <v>0.24911113083362599</v>
+        <v>0.16463512182235701</v>
       </c>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C57" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D57" s="5">
         <v>0</v>
@@ -7470,31 +8479,25 @@
         <v>0</v>
       </c>
       <c r="F57" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="5">
-        <f>G12</f>
-        <v>-1.37498124968261E-3</v>
+        <v>-1.69308739714324E-3</v>
       </c>
       <c r="H57" s="5">
-        <f t="shared" ref="H57:L57" si="12">H12</f>
-        <v>-0.13238599896431</v>
+        <v>-8.5631921887397794E-2</v>
       </c>
       <c r="I57" s="5">
-        <f t="shared" si="12"/>
-        <v>-1.95983843877912E-3</v>
+        <v>-4.7984158300096203E-5</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="12"/>
-        <v>-0.64118611812591597</v>
+        <v>-0.18053941428661299</v>
       </c>
       <c r="K57" s="5">
-        <f t="shared" si="12"/>
-        <v>9.5805265009403194E-3</v>
+        <v>4.4441134668886696E-3</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="12"/>
-        <v>0.17886316776275599</v>
+        <v>0.24911113083362599</v>
       </c>
     </row>
     <row r="58" spans="3:12" x14ac:dyDescent="0.25">
@@ -7502,7 +8505,7 @@
         <v>10</v>
       </c>
       <c r="D58" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="5">
         <v>0</v>
@@ -7511,22 +8514,28 @@
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>4.5564956963062304E-3</v>
+        <f>G13</f>
+        <v>-1.37498124968261E-3</v>
       </c>
       <c r="H58" s="5">
-        <v>-0.11865180730819699</v>
+        <f t="shared" ref="H58:L58" si="18">H13</f>
+        <v>-0.13238599896431</v>
       </c>
       <c r="I58" s="5">
-        <v>-5.4197912104427797E-3</v>
+        <f t="shared" si="18"/>
+        <v>-1.95983843877912E-3</v>
       </c>
       <c r="J58" s="5">
-        <v>-0.57230144739151001</v>
+        <f t="shared" si="18"/>
+        <v>-0.64118611812591597</v>
       </c>
       <c r="K58" s="5">
-        <v>-2.49174889177084E-2</v>
+        <f t="shared" si="18"/>
+        <v>9.5805265009403194E-3</v>
       </c>
       <c r="L58" s="5">
-        <v>0.16460032761096999</v>
+        <f t="shared" si="18"/>
+        <v>0.17886316776275599</v>
       </c>
     </row>
     <row r="59" spans="3:12" x14ac:dyDescent="0.25">
@@ -7534,31 +8543,31 @@
         <v>10</v>
       </c>
       <c r="D59" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
       </c>
       <c r="G59" s="5">
-        <v>-8.2255862653255497E-3</v>
+        <v>4.5564956963062304E-3</v>
       </c>
       <c r="H59" s="5">
-        <v>-0.116225816309452</v>
+        <v>-0.11865180730819699</v>
       </c>
       <c r="I59" s="5">
-        <v>2.8010047972202301E-3</v>
+        <v>-5.4197912104427797E-3</v>
       </c>
       <c r="J59" s="5">
-        <v>-0.55895280838012695</v>
+        <v>-0.57230144739151001</v>
       </c>
       <c r="K59" s="5">
-        <v>4.7850877046585097E-2</v>
+        <v>-2.49174889177084E-2</v>
       </c>
       <c r="L59" s="5">
-        <v>0.16345152258873</v>
+        <v>0.16460032761096999</v>
       </c>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
@@ -7569,42 +8578,84 @@
         <v>0</v>
       </c>
       <c r="E60" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5">
+        <v>-8.2255862653255497E-3</v>
+      </c>
+      <c r="H60" s="5">
+        <v>-0.116225816309452</v>
+      </c>
+      <c r="I60" s="5">
+        <v>2.8010047972202301E-3</v>
+      </c>
+      <c r="J60" s="5">
+        <v>-0.55895280838012695</v>
+      </c>
+      <c r="K60" s="5">
+        <v>4.7850877046585097E-2</v>
+      </c>
+      <c r="L60" s="5">
+        <v>0.16345152258873</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="10">
+        <v>10</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5">
         <v>1</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G61" s="5">
         <v>-2.96032964251935E-3</v>
       </c>
-      <c r="H60" s="5">
+      <c r="H61" s="5">
         <v>-0.13688300549984</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I61" s="5">
         <v>-1.02491653524339E-3</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J61" s="5">
         <v>-0.67123001813888605</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K61" s="5">
         <v>1.8216177821159401E-2</v>
       </c>
-      <c r="L60" s="5">
+      <c r="L61" s="5">
         <v>0.17770855128765101</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="W5:Y5"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="W1:Y1"/>
+  <mergeCells count="20">
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="G21:L21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G2:L2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="AW2:AY2"/>
+    <mergeCell ref="AW3:AY3"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="AA1:AY1"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="T2:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7653,7 +8704,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N1" s="26"/>
       <c r="O1" s="26"/>
@@ -7664,7 +8715,7 @@
       <c r="R1" s="27"/>
       <c r="S1" s="27"/>
       <c r="T1" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U1" s="30"/>
       <c r="V1" s="30"/>
@@ -7794,41 +8845,33 @@
         <f>'Proximal Validation'!L3</f>
         <v>0.34822303056716902</v>
       </c>
-      <c r="M3" s="5">
-        <v>0.68318709074379724</v>
-      </c>
-      <c r="N3" s="5">
-        <v>3.4221233907528452E-2</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1.5830206295629312</v>
-      </c>
-      <c r="P3" s="11">
-        <v>1.2256772931549169E-6</v>
-      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="11"/>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>0.28318709074379722</v>
+        <v>-0.4</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>-2.5778766092471546E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>1.2224302768034656E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>0.28318709074379722</v>
+        <v>0.4</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
-        <v>2.5778766092471546E-2</v>
+        <v>0.06</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>1.2224302768034656E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -7889,53 +8932,45 @@
         <f>'Proximal Validation'!L4</f>
         <v>0.83409011363983199</v>
       </c>
-      <c r="M4" s="8">
-        <v>0.53883367944199079</v>
-      </c>
-      <c r="N4" s="8">
-        <v>0.1048630186446293</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1.5853094441798949</v>
-      </c>
-      <c r="P4" s="12">
-        <v>7.572229257873068E-6</v>
-      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="12"/>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
-        <v>-0.26116632055800926</v>
+        <v>-0.8</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="1"/>
-        <v>4.4863018644629299E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" si="1"/>
-        <v>1.4513117384998386E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
-        <v>0.26116632055800926</v>
+        <v>0.8</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
-        <v>4.4863018644629299E-2</v>
+        <v>0.06</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>1.4513117384998386E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.15535884224181812</v>
+        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
+        <v>1.2659034551614564E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>2.1779361506368125E-2</v>
+        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
+        <v>2.0952413683089388E-3</v>
       </c>
       <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.7918842694283545E-2</v>
+        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
+        <v>1.2254767198828564E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -7987,41 +9022,33 @@
         <f>'Proximal Validation'!L5</f>
         <v>0.269099742174149</v>
       </c>
-      <c r="M5" s="5">
-        <v>0.69262816048351983</v>
-      </c>
-      <c r="N5" s="5">
-        <v>3.4458875615166612E-2</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1.5762461571050057</v>
-      </c>
-      <c r="P5" s="11">
-        <v>4.8201114878327667E-7</v>
-      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="11"/>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>0.39262816048351984</v>
+        <v>-0.3</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="1"/>
-        <v>-4.554112438483339E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="1"/>
-        <v>5.4498303101091494E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="2"/>
-        <v>0.39262816048351984</v>
+        <v>0.3</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>4.554112438483339E-2</v>
+        <v>0.08</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="0"/>
-        <v>5.4498303101091494E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -8076,41 +9103,33 @@
         <f>'Proximal Validation'!L6</f>
         <v>0.47075057029724099</v>
       </c>
-      <c r="M6" s="5">
-        <v>0.45706628050418213</v>
-      </c>
-      <c r="N6" s="5">
-        <v>0.11540182264722286</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1.5886418567596667</v>
-      </c>
-      <c r="P6" s="11">
-        <v>4.0541087584333053E-6</v>
-      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="11"/>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-4.2933719495817868E-2</v>
+        <v>-0.5</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>1.5401822647222854E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="1"/>
-        <v>1.7845529964770179E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="2"/>
-        <v>4.2933719495817868E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>1.5401822647222854E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="0"/>
-        <v>1.7845529964770179E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -8163,40 +9182,40 @@
         <v>0.69233715534210205</v>
       </c>
       <c r="M7" s="5">
-        <v>0.87911360257791171</v>
+        <v>0.69504833452452852</v>
       </c>
       <c r="N7" s="5">
-        <v>8.8095775040584759E-2</v>
+        <v>0.10029090788627264</v>
       </c>
       <c r="O7" s="5">
-        <v>1.5901426757745893</v>
+        <v>1.5906566095799319</v>
       </c>
       <c r="P7" s="11">
-        <v>5.9118055371933157E-6</v>
+        <v>3.9556327352723991E-3</v>
       </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>0.17911360257791176</v>
+        <v>-4.951665475471434E-3</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
-        <v>-1.1904224959415247E-2</v>
+        <v>2.9090788627263164E-4</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="1"/>
-        <v>1.9346348979692785E-2</v>
+        <v>1.9860282785035377E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>0.17911360257791176</v>
+        <v>4.951665475471434E-3</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>1.1904224959415247E-2</v>
+        <v>2.9090788627263164E-4</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.9346348979692785E-2</v>
+        <v>1.9860282785035377E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -8249,40 +9268,40 @@
         <v>0.33158546686172502</v>
       </c>
       <c r="M8" s="5">
-        <v>0.37145751913505048</v>
+        <v>0.40459527077086904</v>
       </c>
       <c r="N8" s="5">
-        <v>0.17734541183066621</v>
+        <v>0.16175637690841743</v>
       </c>
       <c r="O8" s="5">
-        <v>1.5911752283601686</v>
+        <v>1.5836335089828215</v>
       </c>
       <c r="P8" s="11">
-        <v>6.7430530731628813E-6</v>
+        <v>2.380305243305101E-2</v>
       </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>-2.8542480864949538E-2</v>
+        <v>4.5952707708690199E-3</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
-        <v>1.7345411830666208E-2</v>
+        <v>1.7563769084174286E-3</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="1"/>
-        <v>2.0378901565272001E-2</v>
+        <v>1.2837182187924956E-2</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="2"/>
-        <v>2.8542480864949538E-2</v>
+        <v>4.5952707708690199E-3</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>1.7345411830666208E-2</v>
+        <v>1.7563769084174286E-3</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>2.0378901565272001E-2</v>
+        <v>1.2837182187924956E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -8335,40 +9354,40 @@
         <v>0.469948559999466</v>
       </c>
       <c r="M9" s="5">
-        <v>0.75251101548010546</v>
+        <v>0.62115298051829904</v>
       </c>
       <c r="N9" s="5">
-        <v>0.13702541331801257</v>
+        <v>0.16352876190014334</v>
       </c>
       <c r="O9" s="5">
-        <v>1.5951008388198655</v>
+        <v>1.5795319928440903</v>
       </c>
       <c r="P9" s="11">
-        <v>1.1981659466211517E-5</v>
+        <v>2.4817324474598803E-2</v>
       </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>0.15251101548010548</v>
+        <v>2.1152980518299058E-2</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
-        <v>-2.297458668198743E-2</v>
+        <v>3.5287619001433401E-3</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="1"/>
-        <v>2.4304512024968972E-2</v>
+        <v>8.7356660491937355E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="2"/>
-        <v>0.15251101548010548</v>
+        <v>2.1152980518299058E-2</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>2.297458668198743E-2</v>
+        <v>3.5287619001433401E-3</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>2.4304512024968972E-2</v>
+        <v>8.7356660491937355E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -8424,40 +9443,40 @@
         <v>0.27560678124427801</v>
       </c>
       <c r="M10" s="5">
-        <v>0.95462558730508762</v>
+        <v>0.80178352293570265</v>
       </c>
       <c r="N10" s="5">
-        <v>0.16393936023141586</v>
+        <v>0.18245653056188688</v>
       </c>
       <c r="O10" s="5">
-        <v>1.5954199692733784</v>
+        <v>1.5843969453589328</v>
       </c>
       <c r="P10" s="11">
-        <v>2.6815014969590085E-5</v>
+        <v>2.1775497766055568E-3</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>0.15462558730508758</v>
+        <v>1.7835229357026083E-3</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
-        <v>-1.6060639768584128E-2</v>
+        <v>2.4565305618868827E-3</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="1"/>
-        <v>2.4623642478481811E-2</v>
+        <v>1.3600618564036271E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="2"/>
-        <v>0.15462558730508758</v>
+        <v>1.7835229357026083E-3</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>1.6060639768584128E-2</v>
+        <v>2.4565305618868827E-3</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>2.4623642478481811E-2</v>
+        <v>1.3600618564036271E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -8510,40 +9529,40 @@
         <v>0.21111465990543399</v>
       </c>
       <c r="M11" s="5">
-        <v>0.27993629059311864</v>
+        <v>0.31067219880910124</v>
       </c>
       <c r="N11" s="5">
-        <v>0.19999999999997781</v>
+        <v>0.19999997619169832</v>
       </c>
       <c r="O11" s="5">
-        <v>1.5865803476636622</v>
+        <v>1.5800621430982547</v>
       </c>
       <c r="P11" s="11">
-        <v>1.0871915106185044E-5</v>
+        <v>4.4694929795126917E-2</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>-2.0063709406881347E-2</v>
+        <v>1.0672198809101252E-2</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
-        <v>-2.2204460492503131E-14</v>
+        <v>-2.3808301691241596E-8</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="1"/>
-        <v>1.5784020868765625E-2</v>
+        <v>9.2658163033580987E-3</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="2"/>
-        <v>2.0063709406881347E-2</v>
+        <v>1.0672198809101252E-2</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>2.2204460492503131E-14</v>
+        <v>2.3808301691241596E-8</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.5784020868765625E-2</v>
+        <v>9.2658163033580987E-3</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -8599,40 +9618,40 @@
         <v>0.17886316776275599</v>
       </c>
       <c r="M12" s="5">
-        <v>0.73881673550210125</v>
+        <v>0.66720143119975595</v>
       </c>
       <c r="N12" s="5">
-        <v>0.18207597994615105</v>
+        <v>0.19546115285516835</v>
       </c>
       <c r="O12" s="5">
-        <v>1.5955145473926384</v>
+        <v>1.5800253640983195</v>
       </c>
       <c r="P12" s="11">
-        <v>2.6102257317992768E-5</v>
+        <v>7.1563424099087966E-3</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>3.8816735502101296E-2</v>
+        <v>-3.279856880024401E-2</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
-        <v>-1.7924020053848966E-2</v>
+        <v>-4.5388471448316592E-3</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="1"/>
-        <v>2.4718220597741869E-2</v>
+        <v>9.2290373034229489E-3</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="2"/>
-        <v>3.8816735502101296E-2</v>
+        <v>3.279856880024401E-2</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>1.7924020053848966E-2</v>
+        <v>4.5388471448316592E-3</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>2.4718220597741869E-2</v>
+        <v>9.2290373034229489E-3</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -10065,7 +11084,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="32"/>
@@ -10073,7 +11092,7 @@
       <c r="D1" s="32"/>
       <c r="E1" s="32"/>
       <c r="F1" s="33"/>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="35" t="s">
         <v>22</v>
       </c>
       <c r="I1" s="32"/>
@@ -17025,16 +18044,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4569" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30C4FC50-9AF3-43C4-8663-A7663941BC8F}"/>
+  <xr:revisionPtr revIDLastSave="4589" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{854BF339-036A-47D1-8C0C-6092FE9122F7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
@@ -2898,41 +2898,33 @@
         <f>'Proximal Validation'!L3</f>
         <v>0.34822303056716902</v>
       </c>
-      <c r="M3" s="5">
-        <v>0.41553954528208881</v>
-      </c>
-      <c r="N3" s="5">
-        <v>6.7586423368890466E-2</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1.5942535066255172</v>
-      </c>
-      <c r="P3" s="11">
-        <v>3.1859655855985016E-4</v>
-      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="11"/>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>1.5539545282088785E-2</v>
+        <v>-0.4</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>7.5864233688904686E-3</v>
+        <v>-0.06</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>2.3457179830620678E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>1.5539545282088785E-2</v>
+        <v>0.4</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V3" si="0">ABS(R3)</f>
-        <v>7.5864233688904686E-3</v>
+        <v>0.06</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>2.3457179830620678E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -2993,53 +2985,45 @@
         <f>'Proximal Validation'!L4</f>
         <v>0.83409011363983199</v>
       </c>
-      <c r="M4" s="8">
-        <v>0.84710125095211031</v>
-      </c>
-      <c r="N4" s="8">
-        <v>6.9876606593779714E-2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1.5975875435204436</v>
-      </c>
-      <c r="P4" s="12">
-        <v>1.0595002718595083E-3</v>
-      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="12"/>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:Q12" si="1">M4-A4</f>
-        <v>4.7101250952110263E-2</v>
+        <v>-0.8</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" ref="R4:R12" si="2">N4-B4</f>
-        <v>9.8766065937797159E-3</v>
+        <v>-0.06</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" ref="S4:S12" si="3">O4-C4</f>
-        <v>2.6791216725547073E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="4">ABS(Q4)</f>
-        <v>4.7101250952110263E-2</v>
+        <v>0.8</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:U12" si="5">ABS(R4)</f>
-        <v>9.8766065937797159E-3</v>
+        <v>0.06</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" ref="V4:V12" si="6">ABS(S4)</f>
-        <v>2.6791216725547073E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W4" s="6" cm="1">
         <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>4.2523991372479829E-2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X4" s="6" cm="1">
         <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>1.0829170549000348E-2</v>
+        <v>0.13</v>
       </c>
       <c r="Y4" s="6" cm="1">
         <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>2.5292302579239822E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -3091,41 +3075,33 @@
         <f>'Proximal Validation'!L5</f>
         <v>0.269099742174149</v>
       </c>
-      <c r="M5" s="5">
-        <v>0.28522939561051408</v>
-      </c>
-      <c r="N5" s="5">
-        <v>8.4915813659740186E-2</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1.5827769924240351</v>
-      </c>
-      <c r="P5" s="11">
-        <v>1.1970874690918172E-4</v>
-      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="11"/>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>-1.4770604389485908E-2</v>
+        <v>-0.3</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="2"/>
-        <v>4.9158136597401841E-3</v>
+        <v>-0.08</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="3"/>
-        <v>1.1980665629138576E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="4"/>
-        <v>1.4770604389485908E-2</v>
+        <v>0.3</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="5"/>
-        <v>4.9158136597401841E-3</v>
+        <v>0.08</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="6"/>
-        <v>1.1980665629138576E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -3180,41 +3156,33 @@
         <f>'Proximal Validation'!L6</f>
         <v>0.47075057029724099</v>
       </c>
-      <c r="M6" s="5">
-        <v>0.47643338484485187</v>
-      </c>
-      <c r="N6" s="5">
-        <v>0.1105004765444883</v>
-      </c>
-      <c r="O6" s="5">
-        <v>1.5830404836724534</v>
-      </c>
-      <c r="P6" s="11">
-        <v>1.0890150419537683E-4</v>
-      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="11"/>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-2.356661515514813E-2</v>
+        <v>-0.5</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="2"/>
-        <v>1.0500476544488296E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="3"/>
-        <v>1.2244156877556867E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>2.356661515514813E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="5"/>
-        <v>1.0500476544488296E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="6"/>
-        <v>1.2244156877556867E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -3266,41 +3234,33 @@
         <f>'Proximal Validation'!L7</f>
         <v>0.69233715534210205</v>
       </c>
-      <c r="M7" s="5">
-        <v>0.76553039235818787</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0.10073987505760774</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1.5591809194429029</v>
-      </c>
-      <c r="P7" s="11">
-        <v>3.2442525164216813E-4</v>
-      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="11"/>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>6.5530392358187917E-2</v>
+        <v>-0.7</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="2"/>
-        <v>7.3987505760773897E-4</v>
+        <v>-0.1</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="3"/>
-        <v>-1.1615407351993623E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>6.5530392358187917E-2</v>
+        <v>0.7</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="5"/>
-        <v>7.3987505760773897E-4</v>
+        <v>0.1</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="6"/>
-        <v>1.1615407351993623E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -3352,41 +3312,33 @@
         <f>'Proximal Validation'!L8</f>
         <v>0.33158546686172502</v>
       </c>
-      <c r="M8" s="5">
-        <v>0.33534267112782717</v>
-      </c>
-      <c r="N8" s="5">
-        <v>0.16956084100986696</v>
-      </c>
-      <c r="O8" s="5">
-        <v>1.562285411805975</v>
-      </c>
-      <c r="P8" s="11">
-        <v>3.111200989257263E-4</v>
-      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="11"/>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>-6.4657328872172848E-2</v>
+        <v>-0.4</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="2"/>
-        <v>9.560841009866955E-3</v>
+        <v>-0.16</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="3"/>
-        <v>-8.5109149889215363E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>6.4657328872172848E-2</v>
+        <v>0.4</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="5"/>
-        <v>9.560841009866955E-3</v>
+        <v>0.16</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="6"/>
-        <v>8.5109149889215363E-3</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -3438,41 +3390,33 @@
         <f>'Proximal Validation'!L9</f>
         <v>0.469948559999466</v>
       </c>
-      <c r="M9" s="5">
-        <v>0.60041075475288275</v>
-      </c>
-      <c r="N9" s="5">
-        <v>0.1566705848227011</v>
-      </c>
-      <c r="O9" s="5">
-        <v>1.5656310545718017</v>
-      </c>
-      <c r="P9" s="11">
-        <v>3.4944284913766577E-4</v>
-      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="11"/>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>4.107547528827693E-4</v>
+        <v>-0.6</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="2"/>
-        <v>-3.3294151772989E-3</v>
+        <v>-0.16</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="3"/>
-        <v>-5.1652722230948189E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>4.107547528827693E-4</v>
+        <v>0.6</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="5"/>
-        <v>3.3294151772989E-3</v>
+        <v>0.16</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="6"/>
-        <v>5.1652722230948189E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -3527,41 +3471,33 @@
         <f>'Proximal Validation'!L10</f>
         <v>0.27560678124427801</v>
       </c>
-      <c r="M10" s="5">
-        <v>0.75400562839900798</v>
-      </c>
-      <c r="N10" s="5">
-        <v>0.18125389088066388</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1.6294545928293671</v>
-      </c>
-      <c r="P10" s="11">
-        <v>6.1455125978496618E-4</v>
-      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="11"/>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>-4.5994371600992068E-2</v>
+        <v>-0.8</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="2"/>
-        <v>1.2538908806638827E-3</v>
+        <v>-0.18</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>5.8658266034470552E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>4.5994371600992068E-2</v>
+        <v>0.8</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="5"/>
-        <v>1.2538908806638827E-3</v>
+        <v>0.18</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="6"/>
-        <v>5.8658266034470552E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -3613,41 +3549,33 @@
         <f>'Proximal Validation'!L11</f>
         <v>0.21111465990543399</v>
       </c>
-      <c r="M11" s="5">
-        <v>0.29413891095281969</v>
-      </c>
-      <c r="N11" s="5">
-        <v>0.19999999999997781</v>
-      </c>
-      <c r="O11" s="5">
-        <v>1.5421446553139395</v>
-      </c>
-      <c r="P11" s="11">
-        <v>9.4727875734425065E-4</v>
-      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="11"/>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>-5.8610890471803012E-3</v>
+        <v>-0.3</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="2"/>
-        <v>-2.2204460492503131E-14</v>
+        <v>-0.2</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="3"/>
-        <v>-2.8651671480957042E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>5.8610890471803012E-3</v>
+        <v>0.3</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="5"/>
-        <v>2.2204460492503131E-14</v>
+        <v>0.2</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="6"/>
-        <v>2.8651671480957042E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -3702,41 +3630,33 @@
         <f>'Proximal Validation'!L12</f>
         <v>0.17886316776275599</v>
       </c>
-      <c r="M12" s="5">
-        <v>0.84180796131454927</v>
-      </c>
-      <c r="N12" s="5">
-        <v>0.13947163680235489</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1.636644601444994</v>
-      </c>
-      <c r="P12" s="11">
-        <v>1.2213309215035062E-3</v>
-      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="11"/>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>0.14180796131454931</v>
+        <v>-0.7</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="2"/>
-        <v>-6.0528363197645124E-2</v>
+        <v>-0.2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="3"/>
-        <v>6.584827465009746E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="4"/>
-        <v>0.14180796131454931</v>
+        <v>0.7</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="5"/>
-        <v>6.0528363197645124E-2</v>
+        <v>0.2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="6"/>
-        <v>6.584827465009746E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -5517,41 +5437,33 @@
         <f>'Proximal Validation'!L3</f>
         <v>0.34822303056716902</v>
       </c>
-      <c r="M4" s="8">
-        <v>0.40202965392158824</v>
-      </c>
-      <c r="N4" s="8">
-        <v>6.9789383849933759E-2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>1.58612318996072</v>
-      </c>
-      <c r="P4" s="8">
-        <v>1.6932000391698518E-4</v>
-      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="5">
         <f>M4-A4</f>
-        <v>2.0296539215882148E-3</v>
+        <v>-0.4</v>
       </c>
       <c r="R4" s="5">
         <f>N4-B4</f>
-        <v>9.789383849933761E-3</v>
+        <v>-0.06</v>
       </c>
       <c r="S4" s="5">
         <f>O4-C4</f>
-        <v>1.5326863165823434E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T4" s="5">
         <f>ABS(Q4)</f>
-        <v>2.0296539215882148E-3</v>
+        <v>0.4</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" ref="U4:V13" si="0">ABS(R4)</f>
-        <v>9.789383849933761E-3</v>
+        <v>0.06</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>1.5326863165823434E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>23</v>
@@ -5705,53 +5617,45 @@
         <f>'Proximal Validation'!L4</f>
         <v>0.83409011363983199</v>
       </c>
-      <c r="M5" s="8">
-        <v>0.75713708359141785</v>
-      </c>
-      <c r="N5" s="8">
-        <v>7.2421632945224593E-2</v>
-      </c>
-      <c r="O5" s="8">
-        <v>1.5945817689101296</v>
-      </c>
-      <c r="P5" s="8">
-        <v>4.7490785077414997E-4</v>
-      </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="5">
         <f t="shared" ref="Q5:S13" si="3">M5-A5</f>
-        <v>-4.2862916408582197E-2</v>
+        <v>-0.8</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="3"/>
-        <v>1.2421632945224595E-2</v>
+        <v>-0.06</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="3"/>
-        <v>2.3785442115233035E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" ref="T5:T13" si="4">ABS(Q5)</f>
-        <v>4.2862916408582197E-2</v>
+        <v>0.8</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>1.2421632945224595E-2</v>
+        <v>0.06</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="0"/>
-        <v>2.3785442115233035E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W5" s="6" cm="1">
         <f t="array" ref="W5">AVERAGE(ABS(Q4:Q13))</f>
-        <v>2.3919911823198969E-2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X5" s="6" cm="1">
         <f t="array" ref="X5">AVERAGE(ABS(R4:R13))</f>
-        <v>1.0326971317622804E-2</v>
+        <v>0.13</v>
       </c>
       <c r="Y5" s="6" cm="1">
         <f t="array" ref="Y5">AVERAGE(ABS(S4:S13))</f>
-        <v>1.3631851876260814E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="AA5" s="8">
         <f>'Proximal Validation'!A4</f>
@@ -5899,41 +5803,33 @@
         <f>'Proximal Validation'!L5</f>
         <v>0.269099742174149</v>
       </c>
-      <c r="M6" s="8">
-        <v>0.27154159433860381</v>
-      </c>
-      <c r="N6" s="8">
-        <v>8.7965747246715797E-2</v>
-      </c>
-      <c r="O6" s="8">
-        <v>1.5813627191821027</v>
-      </c>
-      <c r="P6" s="8">
-        <v>2.4160611469808265E-5</v>
-      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
       <c r="Q6" s="5">
         <f t="shared" si="3"/>
-        <v>-2.845840566139618E-2</v>
+        <v>-0.3</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="3"/>
-        <v>7.9657472467157958E-3</v>
+        <v>-0.08</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="3"/>
-        <v>1.0566392387206136E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>2.845840566139618E-2</v>
+        <v>0.3</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>7.9657472467157958E-3</v>
+        <v>0.08</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="0"/>
-        <v>1.0566392387206136E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W6" s="24"/>
       <c r="X6" s="24"/>
@@ -6075,41 +5971,33 @@
         <f>'Proximal Validation'!L6</f>
         <v>0.47075057029724099</v>
       </c>
-      <c r="M7" s="8">
-        <v>0.47465787170457124</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0.11103571411521253</v>
-      </c>
-      <c r="O7" s="8">
-        <v>1.5881187616702976</v>
-      </c>
-      <c r="P7" s="8">
-        <v>3.7665609979489553E-5</v>
-      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="5">
         <f t="shared" si="3"/>
-        <v>-2.5342128295428756E-2</v>
+        <v>-0.5</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="3"/>
-        <v>1.1035714115212522E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="3"/>
-        <v>1.7322434875401083E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>2.5342128295428756E-2</v>
+        <v>0.5</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>1.1035714115212522E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.7322434875401083E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="AA7" s="5">
         <f>'Proximal Validation'!A6</f>
@@ -6245,41 +6133,33 @@
         <f>'Proximal Validation'!L7</f>
         <v>0.69233715534210205</v>
       </c>
-      <c r="M8" s="8">
-        <v>0.69137551224771843</v>
-      </c>
-      <c r="N8" s="8">
-        <v>0.11069471761559577</v>
-      </c>
-      <c r="O8" s="8">
-        <v>1.587425379177277</v>
-      </c>
-      <c r="P8" s="8">
-        <v>3.0100158065422581E-5</v>
-      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
       <c r="Q8" s="5">
         <f t="shared" si="3"/>
-        <v>-8.6244877522815289E-3</v>
+        <v>-0.7</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="3"/>
-        <v>1.0694717615595761E-2</v>
+        <v>-0.1</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="3"/>
-        <v>1.6629052382380438E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>8.6244877522815289E-3</v>
+        <v>0.7</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>1.0694717615595761E-2</v>
+        <v>0.1</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>1.6629052382380438E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="AA8" s="5">
         <f>'Proximal Validation'!A7</f>
@@ -6415,41 +6295,33 @@
         <f>'Proximal Validation'!L8</f>
         <v>0.33158546686172502</v>
       </c>
-      <c r="M9" s="8">
-        <v>0.37550210442667975</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0.17311447561668428</v>
-      </c>
-      <c r="O9" s="8">
-        <v>1.5796254680421602</v>
-      </c>
-      <c r="P9" s="8">
-        <v>2.1109742122939963E-4</v>
-      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="5">
         <f t="shared" si="3"/>
-        <v>-2.4497895573320272E-2</v>
+        <v>-0.4</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="3"/>
-        <v>1.3114475616684274E-2</v>
+        <v>-0.16</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="3"/>
-        <v>8.8291412472636388E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>2.4497895573320272E-2</v>
+        <v>0.4</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>1.3114475616684274E-2</v>
+        <v>0.16</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>8.8291412472636388E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="AA9" s="5">
         <f>'Proximal Validation'!A8</f>
@@ -6585,41 +6457,33 @@
         <f>'Proximal Validation'!L9</f>
         <v>0.469948559999466</v>
       </c>
-      <c r="M10" s="8">
-        <v>0.56497426045613874</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0.16528493275999942</v>
-      </c>
-      <c r="O10" s="8">
-        <v>1.580299241084306</v>
-      </c>
-      <c r="P10" s="8">
-        <v>3.1827266330454809E-4</v>
-      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="5">
         <f t="shared" si="3"/>
-        <v>-3.5025739543861234E-2</v>
+        <v>-0.6</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
-        <v>5.2849327599994167E-3</v>
+        <v>-0.16</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>9.5029142894094143E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>3.5025739543861234E-2</v>
+        <v>0.6</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>5.2849327599994167E-3</v>
+        <v>0.16</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>9.5029142894094143E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
@@ -6761,41 +6625,33 @@
         <f>'Proximal Validation'!L10</f>
         <v>0.27560678124427801</v>
       </c>
-      <c r="M11" s="8">
-        <v>0.83481970399375527</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0.16829695270786463</v>
-      </c>
-      <c r="O11" s="8">
-        <v>1.5875321449709592</v>
-      </c>
-      <c r="P11" s="8">
-        <v>2.6277613828493574E-4</v>
-      </c>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
       <c r="Q11" s="5">
         <f t="shared" si="3"/>
-        <v>3.4819703993755224E-2</v>
+        <v>-0.8</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="3"/>
-        <v>-1.1703047292135366E-2</v>
+        <v>-0.18</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="3"/>
-        <v>1.6735818176062622E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>3.4819703993755224E-2</v>
+        <v>0.8</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>1.1703047292135366E-2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.6735818176062622E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="AA11" s="5">
         <f>'Proximal Validation'!A10</f>
@@ -6931,41 +6787,33 @@
         <f>'Proximal Validation'!L11</f>
         <v>0.21111465990543399</v>
       </c>
-      <c r="M12" s="8">
-        <v>0.30032903077135142</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0.19999999998884047</v>
-      </c>
-      <c r="O12" s="8">
-        <v>1.577600833859351</v>
-      </c>
-      <c r="P12" s="8">
-        <v>5.7301024997264923E-4</v>
-      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
       <c r="Q12" s="5">
         <f t="shared" si="3"/>
-        <v>3.290307713514351E-4</v>
+        <v>-0.3</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="3"/>
-        <v>-1.1159545509897839E-11</v>
+        <v>-0.2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="3"/>
-        <v>6.804507064454457E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="4"/>
-        <v>3.290307713514351E-4</v>
+        <v>0.3</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>1.1159545509897839E-11</v>
+        <v>0.2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>6.804507064454457E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
@@ -7107,41 +6955,33 @@
         <f>'Proximal Validation'!L12</f>
         <v>0.17886316776275599</v>
       </c>
-      <c r="M13" s="8">
-        <v>0.6627908436895753</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0.178739938276433</v>
-      </c>
-      <c r="O13" s="8">
-        <v>1.5816122798542704</v>
-      </c>
-      <c r="P13" s="8">
-        <v>2.8685918484907337E-4</v>
-      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="5">
         <f t="shared" si="3"/>
-        <v>-3.7209156310424651E-2</v>
+        <v>-0.7</v>
       </c>
       <c r="R13" s="5">
         <f t="shared" si="3"/>
-        <v>-2.1260061723567009E-2</v>
+        <v>-0.2</v>
       </c>
       <c r="S13" s="5">
         <f t="shared" si="3"/>
-        <v>1.0815953059373884E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T13" s="5">
         <f t="shared" si="4"/>
-        <v>3.7209156310424651E-2</v>
+        <v>0.7</v>
       </c>
       <c r="U13" s="5">
         <f t="shared" si="0"/>
-        <v>2.1260061723567009E-2</v>
+        <v>0.2</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="0"/>
-        <v>1.0815953059373884E-2</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="AA13" s="5">
         <f>'Proximal Validation'!A12</f>
@@ -8961,16 +8801,16 @@
         <v>1.5707963267948966</v>
       </c>
       <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
-        <v>1.2659034551614564E-2</v>
+        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
-        <v>2.0952413683089388E-3</v>
+        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
+        <v>0.13</v>
       </c>
       <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
-        <v>1.2254767198828564E-2</v>
+        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -9181,41 +9021,33 @@
         <f>'Proximal Validation'!L7</f>
         <v>0.69233715534210205</v>
       </c>
-      <c r="M7" s="5">
-        <v>0.69504833452452852</v>
-      </c>
-      <c r="N7" s="5">
-        <v>0.10029090788627264</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1.5906566095799319</v>
-      </c>
-      <c r="P7" s="11">
-        <v>3.9556327352723991E-3</v>
-      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="11"/>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>-4.951665475471434E-3</v>
+        <v>-0.7</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
-        <v>2.9090788627263164E-4</v>
+        <v>-0.1</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="1"/>
-        <v>1.9860282785035377E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>4.951665475471434E-3</v>
+        <v>0.7</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>2.9090788627263164E-4</v>
+        <v>0.1</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.9860282785035377E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -9267,41 +9099,33 @@
         <f>'Proximal Validation'!L8</f>
         <v>0.33158546686172502</v>
       </c>
-      <c r="M8" s="5">
-        <v>0.40459527077086904</v>
-      </c>
-      <c r="N8" s="5">
-        <v>0.16175637690841743</v>
-      </c>
-      <c r="O8" s="5">
-        <v>1.5836335089828215</v>
-      </c>
-      <c r="P8" s="11">
-        <v>2.380305243305101E-2</v>
-      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="11"/>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>4.5952707708690199E-3</v>
+        <v>-0.4</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
-        <v>1.7563769084174286E-3</v>
+        <v>-0.16</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="1"/>
-        <v>1.2837182187924956E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="2"/>
-        <v>4.5952707708690199E-3</v>
+        <v>0.4</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>1.7563769084174286E-3</v>
+        <v>0.16</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>1.2837182187924956E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -9353,41 +9177,33 @@
         <f>'Proximal Validation'!L9</f>
         <v>0.469948559999466</v>
       </c>
-      <c r="M9" s="5">
-        <v>0.62115298051829904</v>
-      </c>
-      <c r="N9" s="5">
-        <v>0.16352876190014334</v>
-      </c>
-      <c r="O9" s="5">
-        <v>1.5795319928440903</v>
-      </c>
-      <c r="P9" s="11">
-        <v>2.4817324474598803E-2</v>
-      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="11"/>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>2.1152980518299058E-2</v>
+        <v>-0.6</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
-        <v>3.5287619001433401E-3</v>
+        <v>-0.16</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="1"/>
-        <v>8.7356660491937355E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="2"/>
-        <v>2.1152980518299058E-2</v>
+        <v>0.6</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>3.5287619001433401E-3</v>
+        <v>0.16</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>8.7356660491937355E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -9442,41 +9258,33 @@
         <f>'Proximal Validation'!L10</f>
         <v>0.27560678124427801</v>
       </c>
-      <c r="M10" s="5">
-        <v>0.80178352293570265</v>
-      </c>
-      <c r="N10" s="5">
-        <v>0.18245653056188688</v>
-      </c>
-      <c r="O10" s="5">
-        <v>1.5843969453589328</v>
-      </c>
-      <c r="P10" s="11">
-        <v>2.1775497766055568E-3</v>
-      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="11"/>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>1.7835229357026083E-3</v>
+        <v>-0.8</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
-        <v>2.4565305618868827E-3</v>
+        <v>-0.18</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="1"/>
-        <v>1.3600618564036271E-2</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="2"/>
-        <v>1.7835229357026083E-3</v>
+        <v>0.8</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>2.4565305618868827E-3</v>
+        <v>0.18</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>1.3600618564036271E-2</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -9528,41 +9336,33 @@
         <f>'Proximal Validation'!L11</f>
         <v>0.21111465990543399</v>
       </c>
-      <c r="M11" s="5">
-        <v>0.31067219880910124</v>
-      </c>
-      <c r="N11" s="5">
-        <v>0.19999997619169832</v>
-      </c>
-      <c r="O11" s="5">
-        <v>1.5800621430982547</v>
-      </c>
-      <c r="P11" s="11">
-        <v>4.4694929795126917E-2</v>
-      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="11"/>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>1.0672198809101252E-2</v>
+        <v>-0.3</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
-        <v>-2.3808301691241596E-8</v>
+        <v>-0.2</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="1"/>
-        <v>9.2658163033580987E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="2"/>
-        <v>1.0672198809101252E-2</v>
+        <v>0.3</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>2.3808301691241596E-8</v>
+        <v>0.2</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>9.2658163033580987E-3</v>
+        <v>1.5707963267948966</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -9617,41 +9417,33 @@
         <f>'Proximal Validation'!L12</f>
         <v>0.17886316776275599</v>
       </c>
-      <c r="M12" s="5">
-        <v>0.66720143119975595</v>
-      </c>
-      <c r="N12" s="5">
-        <v>0.19546115285516835</v>
-      </c>
-      <c r="O12" s="5">
-        <v>1.5800253640983195</v>
-      </c>
-      <c r="P12" s="11">
-        <v>7.1563424099087966E-3</v>
-      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="11"/>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>-3.279856880024401E-2</v>
+        <v>-0.7</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
-        <v>-4.5388471448316592E-3</v>
+        <v>-0.2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="1"/>
-        <v>9.2290373034229489E-3</v>
+        <v>-1.5707963267948966</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="2"/>
-        <v>3.279856880024401E-2</v>
+        <v>0.7</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>4.5388471448316592E-3</v>
+        <v>0.2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>9.2290373034229489E-3</v>
+        <v>1.5707963267948966</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4589" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{854BF339-036A-47D1-8C0C-6092FE9122F7}"/>
+  <xr:revisionPtr revIDLastSave="4628" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787A0572-3DD8-40ED-BA2D-BC313E0CDC71}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="47">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -198,7 +198,13 @@
     <t>3 Perturbation (relative only)</t>
   </si>
   <si>
-    <t>SoRoSim get_distal_value (lambda = 0.3)</t>
+    <t>SoRoSim get_distal_value (3 Perturbations)</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (2 Perturbations)</t>
+  </si>
+  <si>
+    <t>SoRoSim get_distal_value (1 Perturbations)</t>
   </si>
 </sst>
 </file>
@@ -8517,7 +8523,7 @@
     <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" customWidth="1"/>
     <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8801,16 +8807,16 @@
         <v>1.5707963267948966</v>
       </c>
       <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.55000000000000004</v>
+        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
+        <v>4.3732467828106324E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>0.13</v>
+        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
+        <v>9.2053043532432325E-3</v>
       </c>
       <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.5707963267948966</v>
+        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
+        <v>1.2277037003567933E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -9021,33 +9027,41 @@
         <f>'Proximal Validation'!L7</f>
         <v>0.69233715534210205</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="11"/>
+      <c r="M7" s="5">
+        <v>0.69615947991023996</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.10071391548769121</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1.5905381284842586</v>
+      </c>
+      <c r="P7" s="11">
+        <v>3.9969747079750644E-3</v>
+      </c>
       <c r="Q7" s="5">
         <f t="shared" si="1"/>
-        <v>-0.7</v>
+        <v>-3.8405200897599912E-3</v>
       </c>
       <c r="R7" s="5">
         <f t="shared" si="1"/>
-        <v>-0.1</v>
+        <v>7.1391548769120239E-4</v>
       </c>
       <c r="S7" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>1.9741801689362015E-2</v>
       </c>
       <c r="T7" s="5">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>3.8405200897599912E-3</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>7.1391548769120239E-4</v>
       </c>
       <c r="V7" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>1.9741801689362015E-2</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -9099,33 +9113,41 @@
         <f>'Proximal Validation'!L8</f>
         <v>0.33158546686172502</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="11"/>
+      <c r="M8" s="5">
+        <v>0.51201170918090533</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.13758461085295529</v>
+      </c>
+      <c r="O8" s="5">
+        <v>1.5836854626595922</v>
+      </c>
+      <c r="P8" s="11">
+        <v>2.3753509742121082E-2</v>
+      </c>
       <c r="Q8" s="5">
         <f t="shared" si="1"/>
-        <v>-0.4</v>
+        <v>0.11201170918090531</v>
       </c>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
-        <v>-0.16</v>
+        <v>-2.2415389147044718E-2</v>
       </c>
       <c r="S8" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>1.2889135864695644E-2</v>
       </c>
       <c r="T8" s="5">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.11201170918090531</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>2.2415389147044718E-2</v>
       </c>
       <c r="V8" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>1.2889135864695644E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -9177,33 +9199,41 @@
         <f>'Proximal Validation'!L9</f>
         <v>0.469948559999466</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="11"/>
+      <c r="M9" s="5">
+        <v>0.63861944140637905</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.16064875761773398</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.5794604693861756</v>
+      </c>
+      <c r="P9" s="11">
+        <v>2.4814225789448929E-2</v>
+      </c>
       <c r="Q9" s="5">
         <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <v>3.8619441406379074E-2</v>
       </c>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
-        <v>-0.16</v>
+        <v>6.4875761773397489E-4</v>
       </c>
       <c r="S9" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>8.6641425912790115E-3</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>3.8619441406379074E-2</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>6.4875761773397489E-4</v>
       </c>
       <c r="V9" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>8.6641425912790115E-3</v>
       </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
@@ -9258,33 +9288,41 @@
         <f>'Proximal Validation'!L10</f>
         <v>0.27560678124427801</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="11"/>
+      <c r="M10" s="5">
+        <v>0.80509763204284068</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.18463605534635863</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1.5841617982713447</v>
+      </c>
+      <c r="P10" s="11">
+        <v>2.6225649853001075E-3</v>
+      </c>
       <c r="Q10" s="5">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>5.0976320428406385E-3</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="1"/>
-        <v>-0.18</v>
+        <v>4.6360553463586363E-3</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>1.3365471476448176E-2</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>5.0976320428406385E-3</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>4.6360553463586363E-3</v>
       </c>
       <c r="V10" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>1.3365471476448176E-2</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
@@ -9336,33 +9374,41 @@
         <f>'Proximal Validation'!L11</f>
         <v>0.21111465990543399</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="11"/>
+      <c r="M11" s="5">
+        <v>0.32040703415587396</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.1999961495656345</v>
+      </c>
+      <c r="O11" s="5">
+        <v>1.5800046564561681</v>
+      </c>
+      <c r="P11" s="11">
+        <v>4.4421447363002256E-2</v>
+      </c>
       <c r="Q11" s="5">
         <f t="shared" si="1"/>
-        <v>-0.3</v>
+        <v>2.0407034155873971E-2</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="1"/>
-        <v>-0.2</v>
+        <v>-3.8504343655154649E-6</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>9.2083296612714971E-3</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>2.0407034155873971E-2</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>3.8504343655154649E-6</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>9.2083296612714971E-3</v>
       </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
@@ -9417,34 +9463,63 @@
         <f>'Proximal Validation'!L12</f>
         <v>0.17886316776275599</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="11"/>
+      <c r="M12" s="5">
+        <v>0.7824184700928789</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.17318614191373466</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1.5805896675332478</v>
+      </c>
+      <c r="P12" s="11">
+        <v>7.1493408222710452E-3</v>
+      </c>
       <c r="Q12" s="5">
         <f t="shared" si="1"/>
-        <v>-0.7</v>
+        <v>8.2418470092878948E-2</v>
       </c>
       <c r="R12" s="5">
         <f t="shared" si="1"/>
-        <v>-0.2</v>
+        <v>-2.6813858086265352E-2</v>
       </c>
       <c r="S12" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>9.7933407383512527E-3</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="2"/>
-        <v>0.7</v>
+        <v>8.2418470092878948E-2</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>2.6813858086265352E-2</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
-      </c>
+        <v>9.7933407383512527E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M13" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
     </row>
     <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
@@ -9452,8 +9527,43 @@
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="33"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="M14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W14" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1.5</v>
       </c>
@@ -9463,6 +9573,43 @@
       <c r="C15">
         <v>0</v>
       </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="5">
+        <f>M15-A3</f>
+        <v>-0.4</v>
+      </c>
+      <c r="R15" s="5">
+        <f t="shared" ref="R15:S15" si="3">N15-B3</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S15" s="5">
+        <f t="shared" si="3"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T15" s="5">
+        <f>ABS(Q15)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U15" s="5">
+        <f t="shared" ref="U15:U24" si="4">ABS(R15)</f>
+        <v>0.06</v>
+      </c>
+      <c r="V15" s="5">
+        <f t="shared" ref="V15:V24" si="5">ABS(S15)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -9474,8 +9621,48 @@
       <c r="C16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="5">
+        <f t="shared" ref="Q16:Q24" si="6">M16-A4</f>
+        <v>-0.8</v>
+      </c>
+      <c r="R16" s="5">
+        <f t="shared" ref="R16:R24" si="7">N16-B4</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S16" s="5">
+        <f t="shared" ref="S16:S24" si="8">O16-C4</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T16" s="5">
+        <f t="shared" ref="T16:T24" si="9">ABS(Q16)</f>
+        <v>0.8</v>
+      </c>
+      <c r="U16" s="5">
+        <f t="shared" si="4"/>
+        <v>0.06</v>
+      </c>
+      <c r="V16" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W16" s="6" cm="1">
+        <f t="array" ref="W16">AVERAGE(ABS(Q19:Q24))</f>
+        <v>6.8903238977231121E-2</v>
+      </c>
+      <c r="X16" s="6" cm="1">
+        <f t="array" ref="X16">AVERAGE(ABS(R19:R24))</f>
+        <v>1.2003750170200613E-2</v>
+      </c>
+      <c r="Y16" s="6" cm="1">
+        <f t="array" ref="Y16">AVERAGE(ABS(S19:S24))</f>
+        <v>2.723727209581232E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -9485,9 +9672,107 @@
       <c r="C17">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.3</v>
+      </c>
+      <c r="R17" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.08</v>
+      </c>
+      <c r="S17" s="5">
+        <f t="shared" si="8"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T17" s="5">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="4"/>
+        <v>0.08</v>
+      </c>
+      <c r="V17" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="5">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="R18" s="5">
+        <f t="shared" si="7"/>
+        <v>-0.1</v>
+      </c>
+      <c r="S18" s="5">
+        <f t="shared" si="8"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T18" s="5">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="U18" s="5">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="V18" s="5">
+        <f t="shared" si="5"/>
+        <v>1.5707963267948966</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="5">
+        <v>0.64689638992439769</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0.11746668809596479</v>
+      </c>
+      <c r="O19" s="5">
+        <v>1.6043990970981421</v>
+      </c>
+      <c r="P19" s="11">
+        <v>2.8122989366596621E-3</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="6"/>
+        <v>-5.310361007560227E-2</v>
+      </c>
+      <c r="R19" s="5">
+        <f t="shared" si="7"/>
+        <v>1.7466688095964786E-2</v>
+      </c>
+      <c r="S19" s="5">
+        <f t="shared" si="8"/>
+        <v>3.3602770303245544E-2</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" si="9"/>
+        <v>5.310361007560227E-2</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="4"/>
+        <v>1.7466688095964786E-2</v>
+      </c>
+      <c r="V19" s="5">
+        <f t="shared" si="5"/>
+        <v>3.3602770303245544E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>33</v>
       </c>
@@ -9508,49 +9793,124 @@
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="5">
+        <v>0.43690578520692841</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0.15432279590939299</v>
+      </c>
+      <c r="O20" s="5">
+        <v>1.5941794764398824</v>
+      </c>
+      <c r="P20" s="11">
+        <v>2.316401141279547E-2</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" si="6"/>
+        <v>3.6905785206928388E-2</v>
+      </c>
+      <c r="R20" s="5">
+        <f t="shared" si="7"/>
+        <v>-5.6772040906070131E-3</v>
+      </c>
+      <c r="S20" s="5">
+        <f t="shared" si="8"/>
+        <v>2.338314964498589E-2</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" si="9"/>
+        <v>3.6905785206928388E-2</v>
+      </c>
+      <c r="U20" s="5">
+        <f t="shared" si="4"/>
+        <v>5.6772040906070131E-3</v>
+      </c>
+      <c r="V20" s="5">
+        <f t="shared" si="5"/>
+        <v>2.338314964498589E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C21" s="10">
         <v>1</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" ref="D21:L21" si="3">D3</f>
+        <f t="shared" ref="D21:L21" si="10">D3</f>
         <v>0</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-4.37921960838139E-4</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-5.4464954882860198E-2</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-2.8745096642523999E-4</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>-2.13129706680775E-2</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>1.85158103704453E-4</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0.34822303056716902</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="5">
+        <v>0.63574976428953611</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0.16115678485654764</v>
+      </c>
+      <c r="O21" s="5">
+        <v>1.5891343698790081</v>
+      </c>
+      <c r="P21" s="11">
+        <v>2.4396182971127174E-2</v>
+      </c>
+      <c r="Q21" s="5">
+        <f t="shared" si="6"/>
+        <v>3.5749764289536134E-2</v>
+      </c>
+      <c r="R21" s="5">
+        <f t="shared" si="7"/>
+        <v>1.1567848565476324E-3</v>
+      </c>
+      <c r="S21" s="5">
+        <f t="shared" si="8"/>
+        <v>1.8338043084111577E-2</v>
+      </c>
+      <c r="T21" s="5">
+        <f t="shared" si="9"/>
+        <v>3.5749764289536134E-2</v>
+      </c>
+      <c r="U21" s="5">
+        <f t="shared" si="4"/>
+        <v>1.1567848565476324E-3</v>
+      </c>
+      <c r="V21" s="5">
+        <f t="shared" si="5"/>
+        <v>1.8338043084111577E-2</v>
+      </c>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C22" s="10">
         <v>1</v>
       </c>
@@ -9581,8 +9941,44 @@
       <c r="L22" s="5">
         <v>0.25637444853782698</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="5">
+        <v>0.9999999978725217</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0.15559907018035021</v>
+      </c>
+      <c r="O22" s="5">
+        <v>1.6056566890294823</v>
+      </c>
+      <c r="P22" s="11">
+        <v>2.2135648315431807E-4</v>
+      </c>
+      <c r="Q22" s="5">
+        <f t="shared" si="6"/>
+        <v>0.19999999787252165</v>
+      </c>
+      <c r="R22" s="5">
+        <f t="shared" si="7"/>
+        <v>-2.440092981964978E-2</v>
+      </c>
+      <c r="S22" s="5">
+        <f t="shared" si="8"/>
+        <v>3.4860362234585773E-2</v>
+      </c>
+      <c r="T22" s="5">
+        <f t="shared" si="9"/>
+        <v>0.19999999787252165</v>
+      </c>
+      <c r="U22" s="5">
+        <f t="shared" si="4"/>
+        <v>2.440092981964978E-2</v>
+      </c>
+      <c r="V22" s="5">
+        <f t="shared" si="5"/>
+        <v>3.4860362234585773E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C23" s="10">
         <v>1</v>
       </c>
@@ -9613,8 +10009,47 @@
       <c r="L23" s="5">
         <v>0.24494989216327701</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="5">
+        <v>0.32061444702957659</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0.19999999997439072</v>
+      </c>
+      <c r="O23" s="5">
+        <v>1.5962639170006037</v>
+      </c>
+      <c r="P23" s="11">
+        <v>4.3153616360907587E-2</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" si="6"/>
+        <v>2.0614447029576599E-2</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="7"/>
+        <v>-2.5609292464423561E-11</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="8"/>
+        <v>2.5467590205707102E-2</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="9"/>
+        <v>2.0614447029576599E-2</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="4"/>
+        <v>2.5609292464423561E-11</v>
+      </c>
+      <c r="V23" s="5">
+        <f t="shared" si="5"/>
+        <v>2.5467590205707102E-2</v>
+      </c>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C24" s="10">
         <v>1</v>
       </c>
@@ -9645,8 +10080,44 @@
       <c r="L24" s="5">
         <v>0.44520068168640098</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="5">
+        <v>0.76704582938922161</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0.17667910586717483</v>
+      </c>
+      <c r="O24" s="5">
+        <v>1.5985680438971346</v>
+      </c>
+      <c r="P24" s="11">
+        <v>5.8782115741874228E-3</v>
+      </c>
+      <c r="Q24" s="5">
+        <f t="shared" si="6"/>
+        <v>6.7045829389221656E-2</v>
+      </c>
+      <c r="R24" s="5">
+        <f t="shared" si="7"/>
+        <v>-2.3320894132825176E-2</v>
+      </c>
+      <c r="S24" s="5">
+        <f t="shared" si="8"/>
+        <v>2.7771717102238025E-2</v>
+      </c>
+      <c r="T24" s="5">
+        <f t="shared" si="9"/>
+        <v>6.7045829389221656E-2</v>
+      </c>
+      <c r="U24" s="5">
+        <f t="shared" si="4"/>
+        <v>2.3320894132825176E-2</v>
+      </c>
+      <c r="V24" s="5">
+        <f t="shared" si="5"/>
+        <v>2.7771717102238025E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C25" s="10">
         <v>2</v>
       </c>
@@ -9664,27 +10135,46 @@
         <v>-1.2904058676213E-3</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:L25" si="4">H4</f>
+        <f t="shared" ref="H25:L25" si="11">H4</f>
         <v>-0.130890563130379</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>-5.0724833272397496E-4</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>-0.12710034847259499</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>3.3702701330184902E-3</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0.83409011363983199</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28"/>
+      <c r="Y25" s="28"/>
+    </row>
+    <row r="26" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C26" s="10">
         <v>2</v>
       </c>
@@ -9715,8 +10205,43 @@
       <c r="L26" s="5">
         <v>0.75616359710693404</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W26" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C27" s="10">
         <v>2</v>
       </c>
@@ -9747,8 +10272,45 @@
       <c r="L27" s="5">
         <v>0.74502885341644298</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="5">
+        <f>M27-A3</f>
+        <v>-0.4</v>
+      </c>
+      <c r="R27" s="5">
+        <f t="shared" ref="R27:S27" si="12">N27-B3</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S27" s="5">
+        <f t="shared" si="12"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T27" s="5">
+        <f>ABS(Q27)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U27" s="5">
+        <f t="shared" ref="U27:U36" si="13">ABS(R27)</f>
+        <v>0.06</v>
+      </c>
+      <c r="V27" s="5">
+        <f t="shared" ref="V27:V36" si="14">ABS(S27)</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C28" s="10">
         <v>2</v>
       </c>
@@ -9779,8 +10341,48 @@
       <c r="L28" s="5">
         <v>0.90219867229461703</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="5">
+        <f t="shared" ref="Q28:Q36" si="15">M28-A4</f>
+        <v>-0.8</v>
+      </c>
+      <c r="R28" s="5">
+        <f t="shared" ref="R28:R36" si="16">N28-B4</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S28" s="5">
+        <f t="shared" ref="S28:S36" si="17">O28-C4</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T28" s="5">
+        <f t="shared" ref="T28:T36" si="18">ABS(Q28)</f>
+        <v>0.8</v>
+      </c>
+      <c r="U28" s="5">
+        <f t="shared" si="13"/>
+        <v>0.06</v>
+      </c>
+      <c r="V28" s="5">
+        <f t="shared" si="14"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W28" s="6" cm="1">
+        <f t="array" ref="W28">AVERAGE(ABS(Q31:Q36))</f>
+        <v>0.11062792862557298</v>
+      </c>
+      <c r="X28" s="6" cm="1">
+        <f t="array" ref="X28">AVERAGE(ABS(R31:R36))</f>
+        <v>2.8492892761701843E-2</v>
+      </c>
+      <c r="Y28" s="6" cm="1">
+        <f t="array" ref="Y28">AVERAGE(ABS(S31:S36))</f>
+        <v>9.7190398398940947E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C29" s="10">
         <v>3</v>
       </c>
@@ -9798,27 +10400,58 @@
         <v>-4.4532003812491899E-4</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" ref="H29:L29" si="5">H5</f>
+        <f t="shared" ref="H29:L29" si="19">H5</f>
         <v>-4.79050725698471E-2</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>-1.45487196277827E-4</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>-1.52218556031585E-2</v>
       </c>
       <c r="K29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>-1.61819159984589E-4</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="19"/>
         <v>0.269099742174149</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="5">
+        <f t="shared" si="15"/>
+        <v>-0.3</v>
+      </c>
+      <c r="R29" s="5">
+        <f t="shared" si="16"/>
+        <v>-0.08</v>
+      </c>
+      <c r="S29" s="5">
+        <f t="shared" si="17"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T29" s="5">
+        <f t="shared" si="18"/>
+        <v>0.3</v>
+      </c>
+      <c r="U29" s="5">
+        <f t="shared" si="13"/>
+        <v>0.08</v>
+      </c>
+      <c r="V29" s="5">
+        <f t="shared" si="14"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="24"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C30" s="10">
         <v>3</v>
       </c>
@@ -9849,8 +10482,36 @@
       <c r="L30" s="5">
         <v>0.14487913250923201</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="5">
+        <f t="shared" si="15"/>
+        <v>-0.5</v>
+      </c>
+      <c r="R30" s="5">
+        <f t="shared" si="16"/>
+        <v>-0.1</v>
+      </c>
+      <c r="S30" s="5">
+        <f t="shared" si="17"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T30" s="5">
+        <f t="shared" si="18"/>
+        <v>0.5</v>
+      </c>
+      <c r="U30" s="5">
+        <f t="shared" si="13"/>
+        <v>0.1</v>
+      </c>
+      <c r="V30" s="5">
+        <f t="shared" si="14"/>
+        <v>1.5707963267948966</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C31" s="10">
         <v>3</v>
       </c>
@@ -9881,8 +10542,44 @@
       <c r="L31" s="5">
         <v>0.126792147755623</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="5">
+        <v>0.59737948536634056</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.12607915580399745</v>
+      </c>
+      <c r="O31" s="5">
+        <v>1.5518258052738867</v>
+      </c>
+      <c r="P31" s="11">
+        <v>2.0462628661399925E-24</v>
+      </c>
+      <c r="Q31" s="5">
+        <f t="shared" si="15"/>
+        <v>-0.1026205146336594</v>
+      </c>
+      <c r="R31" s="5">
+        <f t="shared" si="16"/>
+        <v>2.6079155803997445E-2</v>
+      </c>
+      <c r="S31" s="5">
+        <f t="shared" si="17"/>
+        <v>-1.8970521521009864E-2</v>
+      </c>
+      <c r="T31" s="5">
+        <f t="shared" si="18"/>
+        <v>0.1026205146336594</v>
+      </c>
+      <c r="U31" s="5">
+        <f t="shared" si="13"/>
+        <v>2.6079155803997445E-2</v>
+      </c>
+      <c r="V31" s="5">
+        <f t="shared" si="14"/>
+        <v>1.8970521521009864E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C32" s="10">
         <v>3</v>
       </c>
@@ -9913,8 +10610,44 @@
       <c r="L32" s="5">
         <v>0.394207954406738</v>
       </c>
-    </row>
-    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="5">
+        <v>0.59920052760901488</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0.11745250764333384</v>
+      </c>
+      <c r="O32" s="5">
+        <v>1.475641878280294</v>
+      </c>
+      <c r="P32" s="11">
+        <v>4.7535702011840262E-18</v>
+      </c>
+      <c r="Q32" s="5">
+        <f t="shared" si="15"/>
+        <v>0.19920052760901485</v>
+      </c>
+      <c r="R32" s="5">
+        <f t="shared" si="16"/>
+        <v>-4.2547492356666161E-2</v>
+      </c>
+      <c r="S32" s="5">
+        <f t="shared" si="17"/>
+        <v>-9.515444851460253E-2</v>
+      </c>
+      <c r="T32" s="5">
+        <f t="shared" si="18"/>
+        <v>0.19920052760901485</v>
+      </c>
+      <c r="U32" s="5">
+        <f t="shared" si="13"/>
+        <v>4.2547492356666161E-2</v>
+      </c>
+      <c r="V32" s="5">
+        <f t="shared" si="14"/>
+        <v>9.515444851460253E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C33" s="10">
         <v>4</v>
       </c>
@@ -9932,27 +10665,66 @@
         <v>-1.1705639772117101E-3</v>
       </c>
       <c r="H33" s="5">
-        <f t="shared" ref="H33:L33" si="6">H6</f>
+        <f t="shared" ref="H33:L33" si="20">H6</f>
         <v>-9.4456188380718203E-2</v>
       </c>
       <c r="I33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-1.20323454029858E-3</v>
       </c>
       <c r="J33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-0.111187651753426</v>
       </c>
       <c r="K33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>-3.2553412020206499E-3</v>
       </c>
       <c r="L33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="20"/>
         <v>0.47075057029724099</v>
       </c>
-    </row>
-    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="5">
+        <v>0.68097057704943564</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0.15168074074843899</v>
+      </c>
+      <c r="O33" s="5">
+        <v>1.4403670186927306</v>
+      </c>
+      <c r="P33" s="11">
+        <v>2.7651277007210815E-19</v>
+      </c>
+      <c r="Q33" s="5">
+        <f t="shared" si="15"/>
+        <v>8.0970577049435666E-2</v>
+      </c>
+      <c r="R33" s="5">
+        <f t="shared" si="16"/>
+        <v>-8.3192592515610175E-3</v>
+      </c>
+      <c r="S33" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.13042930810216591</v>
+      </c>
+      <c r="T33" s="5">
+        <f t="shared" si="18"/>
+        <v>8.0970577049435666E-2</v>
+      </c>
+      <c r="U33" s="5">
+        <f t="shared" si="13"/>
+        <v>8.3192592515610175E-3</v>
+      </c>
+      <c r="V33" s="5">
+        <f t="shared" si="14"/>
+        <v>0.13042930810216591</v>
+      </c>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C34" s="10">
         <v>4</v>
       </c>
@@ -9983,8 +10755,44 @@
       <c r="L34" s="5">
         <v>0.376007050275803</v>
       </c>
-    </row>
-    <row r="35" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="5">
+        <v>0.85136647867739701</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0.19091596837568098</v>
+      </c>
+      <c r="O34" s="5">
+        <v>1.4678007810114051</v>
+      </c>
+      <c r="P34" s="11">
+        <v>3.3374478539756067E-19</v>
+      </c>
+      <c r="Q34" s="5">
+        <f t="shared" si="15"/>
+        <v>5.1366478677396965E-2</v>
+      </c>
+      <c r="R34" s="5">
+        <f t="shared" si="16"/>
+        <v>1.0915968375680984E-2</v>
+      </c>
+      <c r="S34" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.10299554578349146</v>
+      </c>
+      <c r="T34" s="5">
+        <f t="shared" si="18"/>
+        <v>5.1366478677396965E-2</v>
+      </c>
+      <c r="U34" s="5">
+        <f t="shared" si="13"/>
+        <v>1.0915968375680984E-2</v>
+      </c>
+      <c r="V34" s="5">
+        <f t="shared" si="14"/>
+        <v>0.10299554578349146</v>
+      </c>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C35" s="10">
         <v>4</v>
       </c>
@@ -10015,8 +10823,47 @@
       <c r="L35" s="5">
         <v>0.36251398921012901</v>
       </c>
-    </row>
-    <row r="36" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="5">
+        <v>0.46372241953120669</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0.13979485870596078</v>
+      </c>
+      <c r="O35" s="5">
+        <v>1.4405983853726132</v>
+      </c>
+      <c r="P35" s="11">
+        <v>2.1132132176362104E-5</v>
+      </c>
+      <c r="Q35" s="5">
+        <f t="shared" si="15"/>
+        <v>0.1637224195312067</v>
+      </c>
+      <c r="R35" s="5">
+        <f t="shared" si="16"/>
+        <v>-6.0205141294039227E-2</v>
+      </c>
+      <c r="S35" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.13019794142228336</v>
+      </c>
+      <c r="T35" s="5">
+        <f t="shared" si="18"/>
+        <v>0.1637224195312067</v>
+      </c>
+      <c r="U35" s="5">
+        <f t="shared" si="13"/>
+        <v>6.0205141294039227E-2</v>
+      </c>
+      <c r="V35" s="5">
+        <f t="shared" si="14"/>
+        <v>0.13019794142228336</v>
+      </c>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C36" s="10">
         <v>4</v>
       </c>
@@ -10047,8 +10894,44 @@
       <c r="L36" s="5">
         <v>0.57029646635055498</v>
       </c>
-    </row>
-    <row r="37" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="5">
+        <v>0.7658870542527243</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0.1771096605117338</v>
+      </c>
+      <c r="O36" s="5">
+        <v>1.465401701744804</v>
+      </c>
+      <c r="P36" s="11">
+        <v>1.9021868830536531E-21</v>
+      </c>
+      <c r="Q36" s="5">
+        <f t="shared" si="15"/>
+        <v>6.5887054252724342E-2</v>
+      </c>
+      <c r="R36" s="5">
+        <f t="shared" si="16"/>
+        <v>-2.2890339488266215E-2</v>
+      </c>
+      <c r="S36" s="5">
+        <f t="shared" si="17"/>
+        <v>-0.10539462505009256</v>
+      </c>
+      <c r="T36" s="5">
+        <f t="shared" si="18"/>
+        <v>6.5887054252724342E-2</v>
+      </c>
+      <c r="U36" s="5">
+        <f t="shared" si="13"/>
+        <v>2.2890339488266215E-2</v>
+      </c>
+      <c r="V36" s="5">
+        <f t="shared" si="14"/>
+        <v>0.10539462505009256</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C37" s="10">
         <v>5</v>
       </c>
@@ -10066,27 +10949,27 @@
         <v>-1.5179968904703901E-3</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" ref="H37:L37" si="7">H7</f>
+        <f t="shared" ref="H37:L37" si="21">H7</f>
         <v>-0.13914526998996701</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>-1.6895274166017799E-3</v>
       </c>
       <c r="J37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>-0.208347618579865</v>
       </c>
       <c r="K37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>-2.6145353913307199E-3</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="21"/>
         <v>0.69233715534210205</v>
       </c>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C38" s="10">
         <v>5</v>
       </c>
@@ -10118,7 +11001,7 @@
         <v>0.60103619098663297</v>
       </c>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C39" s="10">
         <v>5</v>
       </c>
@@ -10150,7 +11033,7 @@
         <v>0.58477991819381703</v>
       </c>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C40" s="10">
         <v>5</v>
       </c>
@@ -10182,7 +11065,7 @@
         <v>0.76777732372283902</v>
       </c>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C41" s="10">
         <v>6</v>
       </c>
@@ -10200,27 +11083,27 @@
         <v>-6.0909817693754998E-4</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" ref="H41:L41" si="8">H8</f>
+        <f t="shared" ref="H41:L41" si="22">H8</f>
         <v>-9.3464262783527402E-2</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>-1.42273562960327E-3</v>
       </c>
       <c r="J41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>-0.183252438902855</v>
       </c>
       <c r="K41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>-1.30194798111916E-3</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="22"/>
         <v>0.33158546686172502</v>
       </c>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C42" s="10">
         <v>6</v>
       </c>
@@ -10252,7 +11135,7 @@
         <v>0.26543587446212802</v>
       </c>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C43" s="10">
         <v>6</v>
       </c>
@@ -10284,7 +11167,7 @@
         <v>0.25937113165855402</v>
       </c>
     </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C44" s="10">
         <v>6</v>
       </c>
@@ -10316,7 +11199,7 @@
         <v>0.41029143333435097</v>
       </c>
     </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C45" s="10">
         <v>7</v>
       </c>
@@ -10334,27 +11217,27 @@
         <v>-8.4166455781087301E-4</v>
       </c>
       <c r="H45" s="5">
-        <f t="shared" ref="H45:L45" si="9">H9</f>
+        <f t="shared" ref="H45:L45" si="23">H9</f>
         <v>-0.141347721219063</v>
       </c>
       <c r="I45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>-2.4875707458704701E-3</v>
       </c>
       <c r="J45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>-0.39468729496002197</v>
       </c>
       <c r="K45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>-9.2538818717002901E-4</v>
       </c>
       <c r="L45" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="23"/>
         <v>0.469948559999466</v>
       </c>
     </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C46" s="10">
         <v>7</v>
       </c>
@@ -10386,7 +11269,7 @@
         <v>0.40802216529846203</v>
       </c>
     </row>
-    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C47" s="10">
         <v>7</v>
       </c>
@@ -10418,7 +11301,7 @@
         <v>0.40057820081710799</v>
       </c>
     </row>
-    <row r="48" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.25">
       <c r="C48" s="10">
         <v>7</v>
       </c>
@@ -10468,23 +11351,23 @@
         <v>-2.5411224924027898E-3</v>
       </c>
       <c r="H49" s="5">
-        <f t="shared" ref="H49:L49" si="10">H10</f>
+        <f t="shared" ref="H49:L49" si="24">H10</f>
         <v>-0.16168536245822901</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>-2.0260578021407101E-3</v>
       </c>
       <c r="J49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>-0.81751561164856001</v>
       </c>
       <c r="K49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>1.46271400153637E-2</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>0.27560678124427801</v>
       </c>
     </row>
@@ -10602,23 +11485,23 @@
         <v>-7.7232124749571096E-4</v>
       </c>
       <c r="H53" s="5">
-        <f t="shared" ref="H53:L53" si="11">H11</f>
+        <f t="shared" ref="H53:L53" si="25">H11</f>
         <v>-7.1722365915775299E-2</v>
       </c>
       <c r="I53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>-7.8877643682062604E-4</v>
       </c>
       <c r="J53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>-0.14824971556663499</v>
       </c>
       <c r="K53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>-2.5316514074802399E-4</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0.21111465990543399</v>
       </c>
     </row>
@@ -10736,23 +11619,23 @@
         <v>-1.37498124968261E-3</v>
       </c>
       <c r="H57" s="5">
-        <f t="shared" ref="H57:L57" si="12">H12</f>
+        <f t="shared" ref="H57:L57" si="26">H12</f>
         <v>-0.13238599896431</v>
       </c>
       <c r="I57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>-1.95983843877912E-3</v>
       </c>
       <c r="J57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>-0.64118611812591597</v>
       </c>
       <c r="K57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>9.5805265009403194E-3</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="26"/>
         <v>0.17886316776275599</v>
       </c>
     </row>
@@ -10853,7 +11736,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="22">
+    <mergeCell ref="W29:Y29"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="W25:Y25"/>
+    <mergeCell ref="W26:Y26"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="W13:Y13"/>
     <mergeCell ref="W5:Y5"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="G20:L20"/>
@@ -10864,6 +11757,8 @@
     <mergeCell ref="W1:Y1"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W14:Y14"/>
+    <mergeCell ref="W17:Y17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
+++ b/Raw Data/single force (10 trials)(perturbed)/Validation(1.7to1.25)(3tendon).xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/Raw Data/single force (10 trials)(perturbed)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4628" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{787A0572-3DD8-40ED-BA2D-BC313E0CDC71}"/>
+  <xr:revisionPtr revIDLastSave="4670" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBE4E2FD-B8B9-43D8-BE16-1990BF95D951}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation" sheetId="12" r:id="rId1"/>
     <sheet name="Distal Vali (0N perturb)" sheetId="37" r:id="rId2"/>
-    <sheet name="Distal Vali (0.5N perturb)" sheetId="19" r:id="rId3"/>
-    <sheet name="Distal Vali (1N perturb)" sheetId="38" r:id="rId4"/>
-    <sheet name="Distal Vali (1.5N perturb)" sheetId="39" r:id="rId5"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId6"/>
-    <sheet name="Sheet5" sheetId="36" r:id="rId7"/>
+    <sheet name="Distal Vali (0N pert 6prox)" sheetId="40" r:id="rId3"/>
+    <sheet name="Distal Vali (0.5N perturb)" sheetId="19" r:id="rId4"/>
+    <sheet name="Distal Vali (1N perturb)" sheetId="38" r:id="rId5"/>
+    <sheet name="Distal Vali (1.5N perturb)" sheetId="39" r:id="rId6"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="36" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="47">
   <si>
     <t>Fx (N)</t>
   </si>
@@ -1995,16 +1996,16 @@
         <v>1.4519522140979735E-2</v>
       </c>
       <c r="W4" s="6" cm="1">
-        <f t="array" ref="W4">AVERAGE(ABS(Q3:Q12))</f>
-        <v>0.14986298462635395</v>
+        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
+        <v>7.9819944321570288E-2</v>
       </c>
       <c r="X4" s="6" cm="1">
-        <f t="array" ref="X4">AVERAGE(ABS(R3:R12))</f>
-        <v>3.5020015147253135E-2</v>
+        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
+        <v>1.2849522287114203E-2</v>
       </c>
       <c r="Y4" s="6" cm="1">
-        <f t="array" ref="Y4">AVERAGE(ABS(S3:S12))</f>
-        <v>1.7758599375180338E-2</v>
+        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
+        <v>2.11525889259155E-2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -2721,6 +2722,1014 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC48AF8C-BA0F-4D6B-8197-0DD15032F82D}">
+  <dimension ref="A1:Y12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+    </row>
+    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+    </row>
+    <row r="3" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <f>'Proximal Validation'!A3</f>
+        <v>0.4</v>
+      </c>
+      <c r="B3" s="5">
+        <f>'Proximal Validation'!B3</f>
+        <v>0.06</v>
+      </c>
+      <c r="C3" s="5">
+        <f>'Proximal Validation'!C3</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D3" s="5">
+        <f>'Proximal Validation'!D3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <f>'Proximal Validation'!E3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <f>'Proximal Validation'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <f>'Proximal Validation'!G3</f>
+        <v>-4.37921960838139E-4</v>
+      </c>
+      <c r="H3" s="5">
+        <f>'Proximal Validation'!H3</f>
+        <v>-5.4464954882860198E-2</v>
+      </c>
+      <c r="I3" s="5">
+        <f>'Proximal Validation'!I3</f>
+        <v>-2.8745096642523999E-4</v>
+      </c>
+      <c r="J3" s="5">
+        <f>'Proximal Validation'!J3</f>
+        <v>-2.13129706680775E-2</v>
+      </c>
+      <c r="K3" s="5">
+        <f>'Proximal Validation'!K3</f>
+        <v>1.85158103704453E-4</v>
+      </c>
+      <c r="L3" s="5">
+        <f>'Proximal Validation'!L3</f>
+        <v>0.34822303056716902</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="5">
+        <f>M3-A3</f>
+        <v>-0.4</v>
+      </c>
+      <c r="R3" s="5">
+        <f>N3-B3</f>
+        <v>-0.06</v>
+      </c>
+      <c r="S3" s="5">
+        <f>O3-C3</f>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T3" s="5">
+        <f>ABS(Q3)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U3" s="5">
+        <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
+        <v>0.06</v>
+      </c>
+      <c r="V3" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <f>'Proximal Validation'!A4</f>
+        <v>0.8</v>
+      </c>
+      <c r="B4" s="8">
+        <f>'Proximal Validation'!B4</f>
+        <v>0.06</v>
+      </c>
+      <c r="C4" s="8">
+        <f>'Proximal Validation'!C4</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D4" s="8">
+        <f>'Proximal Validation'!D4</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <f>'Proximal Validation'!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <f>'Proximal Validation'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <f>'Proximal Validation'!G4</f>
+        <v>-1.2904058676213E-3</v>
+      </c>
+      <c r="H4" s="8">
+        <f>'Proximal Validation'!H4</f>
+        <v>-0.130890563130379</v>
+      </c>
+      <c r="I4" s="8">
+        <f>'Proximal Validation'!I4</f>
+        <v>-5.0724833272397496E-4</v>
+      </c>
+      <c r="J4" s="8">
+        <f>'Proximal Validation'!J4</f>
+        <v>-0.12710034847259499</v>
+      </c>
+      <c r="K4" s="8">
+        <f>'Proximal Validation'!K4</f>
+        <v>3.3702701330184902E-3</v>
+      </c>
+      <c r="L4" s="8">
+        <f>'Proximal Validation'!L4</f>
+        <v>0.83409011363983199</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="5">
+        <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.06</v>
+      </c>
+      <c r="S4" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T4" s="5">
+        <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
+        <v>0.8</v>
+      </c>
+      <c r="U4" s="5">
+        <f t="shared" si="0"/>
+        <v>0.06</v>
+      </c>
+      <c r="V4" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W4" s="6" cm="1">
+        <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
+        <v>3.6765321320119219E-2</v>
+      </c>
+      <c r="X4" s="6" cm="1">
+        <f t="array" ref="X4">AVERAGE(ABS(R7:R12))</f>
+        <v>5.574909039835982E-3</v>
+      </c>
+      <c r="Y4" s="6" cm="1">
+        <f t="array" ref="Y4">AVERAGE(ABS(S7:S12))</f>
+        <v>1.7417100305963291E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <f>'Proximal Validation'!A5</f>
+        <v>0.3</v>
+      </c>
+      <c r="B5" s="5">
+        <f>'Proximal Validation'!B5</f>
+        <v>0.08</v>
+      </c>
+      <c r="C5" s="5">
+        <f>'Proximal Validation'!C5</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D5" s="5">
+        <f>'Proximal Validation'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <f>'Proximal Validation'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <f>'Proximal Validation'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <f>'Proximal Validation'!G5</f>
+        <v>-4.4532003812491899E-4</v>
+      </c>
+      <c r="H5" s="5">
+        <f>'Proximal Validation'!H5</f>
+        <v>-4.79050725698471E-2</v>
+      </c>
+      <c r="I5" s="5">
+        <f>'Proximal Validation'!I5</f>
+        <v>-1.45487196277827E-4</v>
+      </c>
+      <c r="J5" s="5">
+        <f>'Proximal Validation'!J5</f>
+        <v>-1.52218556031585E-2</v>
+      </c>
+      <c r="K5" s="5">
+        <f>'Proximal Validation'!K5</f>
+        <v>-1.61819159984589E-4</v>
+      </c>
+      <c r="L5" s="5">
+        <f>'Proximal Validation'!L5</f>
+        <v>0.269099742174149</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.3</v>
+      </c>
+      <c r="R5" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.08</v>
+      </c>
+      <c r="S5" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T5" s="5">
+        <f t="shared" si="2"/>
+        <v>0.3</v>
+      </c>
+      <c r="U5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="V5" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <f>'Proximal Validation'!A6</f>
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="5">
+        <f>'Proximal Validation'!B6</f>
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="5">
+        <f>'Proximal Validation'!C6</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D6" s="5">
+        <f>'Proximal Validation'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <f>'Proximal Validation'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <f>'Proximal Validation'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <f>'Proximal Validation'!G6</f>
+        <v>-1.1705639772117101E-3</v>
+      </c>
+      <c r="H6" s="5">
+        <f>'Proximal Validation'!H6</f>
+        <v>-9.4456188380718203E-2</v>
+      </c>
+      <c r="I6" s="5">
+        <f>'Proximal Validation'!I6</f>
+        <v>-1.20323454029858E-3</v>
+      </c>
+      <c r="J6" s="5">
+        <f>'Proximal Validation'!J6</f>
+        <v>-0.111187651753426</v>
+      </c>
+      <c r="K6" s="5">
+        <f>'Proximal Validation'!K6</f>
+        <v>-3.2553412020206499E-3</v>
+      </c>
+      <c r="L6" s="5">
+        <f>'Proximal Validation'!L6</f>
+        <v>0.47075057029724099</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="R6" s="5">
+        <f t="shared" si="1"/>
+        <v>-0.1</v>
+      </c>
+      <c r="S6" s="5">
+        <f t="shared" si="1"/>
+        <v>-1.5707963267948966</v>
+      </c>
+      <c r="T6" s="5">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="V6" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5707963267948966</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <f>'Proximal Validation'!A7</f>
+        <v>0.7</v>
+      </c>
+      <c r="B7" s="5">
+        <f>'Proximal Validation'!B7</f>
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="5">
+        <f>'Proximal Validation'!C7</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D7" s="5">
+        <f>'Proximal Validation'!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <f>'Proximal Validation'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <f>'Proximal Validation'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <f>'Proximal Validation'!G7</f>
+        <v>-1.5179968904703901E-3</v>
+      </c>
+      <c r="H7" s="5">
+        <f>'Proximal Validation'!H7</f>
+        <v>-0.13914526998996701</v>
+      </c>
+      <c r="I7" s="5">
+        <f>'Proximal Validation'!I7</f>
+        <v>-1.6895274166017799E-3</v>
+      </c>
+      <c r="J7" s="5">
+        <f>'Proximal Validation'!J7</f>
+        <v>-0.208347618579865</v>
+      </c>
+      <c r="K7" s="5">
+        <f>'Proximal Validation'!K7</f>
+        <v>-2.6145353913307199E-3</v>
+      </c>
+      <c r="L7" s="5">
+        <f>'Proximal Validation'!L7</f>
+        <v>0.69233715534210205</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.72494634990772444</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.10662094941285304</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1.5829152161191393</v>
+      </c>
+      <c r="P7" s="11">
+        <v>3.3288807721640497E-4</v>
+      </c>
+      <c r="Q7" s="5">
+        <f t="shared" si="1"/>
+        <v>2.4946349907724485E-2</v>
+      </c>
+      <c r="R7" s="5">
+        <f t="shared" si="1"/>
+        <v>6.6209494128530305E-3</v>
+      </c>
+      <c r="S7" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2118889324242765E-2</v>
+      </c>
+      <c r="T7" s="5">
+        <f t="shared" si="2"/>
+        <v>2.4946349907724485E-2</v>
+      </c>
+      <c r="U7" s="5">
+        <f t="shared" si="0"/>
+        <v>6.6209494128530305E-3</v>
+      </c>
+      <c r="V7" s="5">
+        <f t="shared" si="0"/>
+        <v>1.2118889324242765E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <f>'Proximal Validation'!A8</f>
+        <v>0.4</v>
+      </c>
+      <c r="B8" s="5">
+        <f>'Proximal Validation'!B8</f>
+        <v>0.16</v>
+      </c>
+      <c r="C8" s="5">
+        <f>'Proximal Validation'!C8</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D8" s="5">
+        <f>'Proximal Validation'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <f>'Proximal Validation'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <f>'Proximal Validation'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <f>'Proximal Validation'!G8</f>
+        <v>-6.0909817693754998E-4</v>
+      </c>
+      <c r="H8" s="5">
+        <f>'Proximal Validation'!H8</f>
+        <v>-9.3464262783527402E-2</v>
+      </c>
+      <c r="I8" s="5">
+        <f>'Proximal Validation'!I8</f>
+        <v>-1.42273562960327E-3</v>
+      </c>
+      <c r="J8" s="5">
+        <f>'Proximal Validation'!J8</f>
+        <v>-0.183252438902855</v>
+      </c>
+      <c r="K8" s="5">
+        <f>'Proximal Validation'!K8</f>
+        <v>-1.30194798111916E-3</v>
+      </c>
+      <c r="L8" s="5">
+        <f>'Proximal Validation'!L8</f>
+        <v>0.33158546686172502</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0.37461772570696172</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.17584726831853761</v>
+      </c>
+      <c r="O8" s="5">
+        <v>1.5878003217554957</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1.2109854882938493E-4</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="1"/>
+        <v>-2.5382274293038298E-2</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="1"/>
+        <v>1.5847268318537611E-2</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" si="1"/>
+        <v>1.7003994960599123E-2</v>
+      </c>
+      <c r="T8" s="5">
+        <f t="shared" si="2"/>
+        <v>2.5382274293038298E-2</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.5847268318537611E-2</v>
+      </c>
+      <c r="V8" s="5">
+        <f t="shared" si="0"/>
+        <v>1.7003994960599123E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <f>'Proximal Validation'!A9</f>
+        <v>0.6</v>
+      </c>
+      <c r="B9" s="5">
+        <f>'Proximal Validation'!B9</f>
+        <v>0.16</v>
+      </c>
+      <c r="C9" s="5">
+        <f>'Proximal Validation'!C9</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D9" s="5">
+        <f>'Proximal Validation'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <f>'Proximal Validation'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <f>'Proximal Validation'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <f>'Proximal Validation'!G9</f>
+        <v>-8.4166455781087301E-4</v>
+      </c>
+      <c r="H9" s="5">
+        <f>'Proximal Validation'!H9</f>
+        <v>-0.141347721219063</v>
+      </c>
+      <c r="I9" s="5">
+        <f>'Proximal Validation'!I9</f>
+        <v>-2.4875707458704701E-3</v>
+      </c>
+      <c r="J9" s="5">
+        <f>'Proximal Validation'!J9</f>
+        <v>-0.39468729496002197</v>
+      </c>
+      <c r="K9" s="5">
+        <f>'Proximal Validation'!K9</f>
+        <v>-9.2538818717002901E-4</v>
+      </c>
+      <c r="L9" s="5">
+        <f>'Proximal Validation'!L9</f>
+        <v>0.469948559999466</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0.62483472511339833</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.16677168840130902</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.5909034914421638</v>
+      </c>
+      <c r="P9" s="11">
+        <v>4.8729854942259601E-4</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" si="1"/>
+        <v>2.4834725113398348E-2</v>
+      </c>
+      <c r="R9" s="5">
+        <f t="shared" si="1"/>
+        <v>6.7716884013090117E-3</v>
+      </c>
+      <c r="S9" s="5">
+        <f t="shared" si="1"/>
+        <v>2.0107164647267251E-2</v>
+      </c>
+      <c r="T9" s="5">
+        <f t="shared" si="2"/>
+        <v>2.4834725113398348E-2</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" si="0"/>
+        <v>6.7716884013090117E-3</v>
+      </c>
+      <c r="V9" s="5">
+        <f t="shared" si="0"/>
+        <v>2.0107164647267251E-2</v>
+      </c>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <f>'Proximal Validation'!A10</f>
+        <v>0.8</v>
+      </c>
+      <c r="B10" s="5">
+        <f>'Proximal Validation'!B10</f>
+        <v>0.18</v>
+      </c>
+      <c r="C10" s="5">
+        <f>'Proximal Validation'!C10</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D10" s="5">
+        <f>'Proximal Validation'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <f>'Proximal Validation'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <f>'Proximal Validation'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <f>'Proximal Validation'!G10</f>
+        <v>-2.5411224924027898E-3</v>
+      </c>
+      <c r="H10" s="5">
+        <f>'Proximal Validation'!H10</f>
+        <v>-0.16168536245822901</v>
+      </c>
+      <c r="I10" s="5">
+        <f>'Proximal Validation'!I10</f>
+        <v>-2.0260578021407101E-3</v>
+      </c>
+      <c r="J10" s="5">
+        <f>'Proximal Validation'!J10</f>
+        <v>-0.81751561164856001</v>
+      </c>
+      <c r="K10" s="5">
+        <f>'Proximal Validation'!K10</f>
+        <v>1.46271400153637E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <f>'Proximal Validation'!L10</f>
+        <v>0.27560678124427801</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0.89432810860073297</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.18420954810621448</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1.5920039262280163</v>
+      </c>
+      <c r="P10" s="11">
+        <v>3.3236578515797276E-3</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="1"/>
+        <v>9.4328108600732929E-2</v>
+      </c>
+      <c r="R10" s="5">
+        <f t="shared" si="1"/>
+        <v>4.209548106214489E-3</v>
+      </c>
+      <c r="S10" s="5">
+        <f t="shared" si="1"/>
+        <v>2.1207599433119784E-2</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" si="2"/>
+        <v>9.4328108600732929E-2</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="0"/>
+        <v>4.209548106214489E-3</v>
+      </c>
+      <c r="V10" s="5">
+        <f t="shared" si="0"/>
+        <v>2.1207599433119784E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <f>'Proximal Validation'!A11</f>
+        <v>0.3</v>
+      </c>
+      <c r="B11" s="5">
+        <f>'Proximal Validation'!B11</f>
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="5">
+        <f>'Proximal Validation'!C11</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D11" s="5">
+        <f>'Proximal Validation'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <f>'Proximal Validation'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <f>'Proximal Validation'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f>'Proximal Validation'!G11</f>
+        <v>-7.7232124749571096E-4</v>
+      </c>
+      <c r="H11" s="5">
+        <f>'Proximal Validation'!H11</f>
+        <v>-7.1722365915775299E-2</v>
+      </c>
+      <c r="I11" s="5">
+        <f>'Proximal Validation'!I11</f>
+        <v>-7.8877643682062604E-4</v>
+      </c>
+      <c r="J11" s="5">
+        <f>'Proximal Validation'!J11</f>
+        <v>-0.14824971556663499</v>
+      </c>
+      <c r="K11" s="5">
+        <f>'Proximal Validation'!K11</f>
+        <v>-2.5316514074802399E-4</v>
+      </c>
+      <c r="L11" s="5">
+        <f>'Proximal Validation'!L11</f>
+        <v>0.21111465990543399</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0.2740378269579935</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.19999999999997592</v>
+      </c>
+      <c r="O11" s="5">
+        <v>1.5832391236606946</v>
+      </c>
+      <c r="P11" s="11">
+        <v>1.6539266535709118E-3</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="1"/>
+        <v>-2.5962173042006487E-2</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="1"/>
+        <v>-2.4091839634365897E-14</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2442796865798078E-2</v>
+      </c>
+      <c r="T11" s="5">
+        <f t="shared" si="2"/>
+        <v>2.5962173042006487E-2</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" si="0"/>
+        <v>2.4091839634365897E-14</v>
+      </c>
+      <c r="V11" s="5">
+        <f t="shared" si="0"/>
+        <v>1.2442796865798078E-2</v>
+      </c>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <f>'Proximal Validation'!A12</f>
+        <v>0.7</v>
+      </c>
+      <c r="B12" s="5">
+        <f>'Proximal Validation'!B12</f>
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="5">
+        <f>'Proximal Validation'!C12</f>
+        <v>1.5707963267948966</v>
+      </c>
+      <c r="D12" s="5">
+        <f>'Proximal Validation'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <f>'Proximal Validation'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <f>'Proximal Validation'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <f>'Proximal Validation'!G12</f>
+        <v>-1.37498124968261E-3</v>
+      </c>
+      <c r="H12" s="5">
+        <f>'Proximal Validation'!H12</f>
+        <v>-0.13238599896431</v>
+      </c>
+      <c r="I12" s="5">
+        <f>'Proximal Validation'!I12</f>
+        <v>-1.95983843877912E-3</v>
+      </c>
+      <c r="J12" s="5">
+        <f>'Proximal Validation'!J12</f>
+        <v>-0.64118611812591597</v>
+      </c>
+      <c r="K12" s="5">
+        <f>'Proximal Validation'!K12</f>
+        <v>9.5805265009403194E-3</v>
+      </c>
+      <c r="L12" s="5">
+        <f>'Proximal Validation'!L12</f>
+        <v>0.17886316776275599</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0.72513829696381471</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.19999999999992235</v>
+      </c>
+      <c r="O12" s="5">
+        <v>1.5924184833996493</v>
+      </c>
+      <c r="P12" s="11">
+        <v>9.6305608445636463E-3</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="1"/>
+        <v>2.5138296963814755E-2</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="1"/>
+        <v>-7.76601005725297E-14</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="1"/>
+        <v>2.1622156604752751E-2</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="2"/>
+        <v>2.5138296963814755E-2</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="0"/>
+        <v>7.76601005725297E-14</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" si="0"/>
+        <v>2.1622156604752751E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="T1:V1"/>
+    <mergeCell ref="W1:Y1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309BE333-3BAE-4E8D-AF02-67A9E2013036}">
   <dimension ref="A1:Y60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5098,7 +6107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EAE0736-1722-4350-9DE0-8A911956EF0F}">
   <dimension ref="A1:AY61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8508,7 +9517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05555DD-E413-4EEB-B18C-66E0D2A3A5AE}">
   <dimension ref="A1:Y60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8691,33 +9700,41 @@
         <f>'Proximal Validation'!L3</f>
         <v>0.34822303056716902</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="11"/>
+      <c r="M3" s="5">
+        <v>0.31408271603248117</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0.19999999899533699</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1.5865549262293448</v>
+      </c>
+      <c r="P3" s="11">
+        <v>4.8770789111221811E-3</v>
+      </c>
       <c r="Q3" s="5">
         <f>M3-A3</f>
-        <v>-0.4</v>
+        <v>-8.5917283967518854E-2</v>
       </c>
       <c r="R3" s="5">
         <f>N3-B3</f>
-        <v>-0.06</v>
+        <v>0.13999999899533699</v>
       </c>
       <c r="S3" s="5">
         <f>O3-C3</f>
-        <v>-1.5707963267948966</v>
+        <v>1.5758599434448239E-2</v>
       </c>
       <c r="T3" s="5">
         <f>ABS(Q3)</f>
-        <v>0.4</v>
+        <v>8.5917283967518854E-2</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:V12" si="0">ABS(R3)</f>
-        <v>0.06</v>
+        <v>0.13999999899533699</v>
       </c>
       <c r="V3" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>1.5758599434448239E-2</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>23</v>
@@ -8778,33 +9795,41 @@
         <f>'Proximal Validation'!L4</f>
         <v>0.83409011363983199</v>
       </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="12"/>
+      <c r="M4" s="8">
+        <v>0.31623114166253402</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.19999999953885811</v>
+      </c>
+      <c r="O4" s="8">
+        <v>1.5953492155841591</v>
+      </c>
+      <c r="P4" s="12">
+        <v>1.9835038986431488E-3</v>
+      </c>
       <c r="Q4" s="5">
         <f t="shared" ref="Q4:S12" si="1">M4-A4</f>
-        <v>-0.8</v>
+        <v>-0.48376885833746602</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="1"/>
-        <v>-0.06</v>
+        <v>0.13999999953885811</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>2.4552888789262539E-2</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" ref="T4:T12" si="2">ABS(Q4)</f>
-        <v>0.8</v>
+        <v>0.48376885833746602</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0.13999999953885811</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>2.4552888789262539E-2</v>
       </c>
       <c r="W4" s="6" cm="1">
         <f t="array" ref="W4">AVERAGE(ABS(Q7:Q12))</f>
@@ -8868,33 +9893,41 @@
         <f>'Proximal Validation'!L5</f>
         <v>0.269099742174149</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="11"/>
+      <c r="M5" s="5">
+        <v>0.24194170964132397</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0.19999999446723285</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1.5786470563162476</v>
+      </c>
+      <c r="P5" s="11">
+        <v>8.655494073901422E-4</v>
+      </c>
       <c r="Q5" s="5">
         <f t="shared" si="1"/>
-        <v>-0.3</v>
+        <v>-5.8058290358676018E-2</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="1"/>
-        <v>-0.08</v>
+        <v>0.11999999446723285</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>7.8507295213510186E-3</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>5.8058290358676018E-2</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.11999999446723285</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>7.8507295213510186E-3</v>
       </c>
       <c r="W5" s="24"/>
       <c r="X5" s="24"/>
@@ -8949,33 +9982,41 @@
         <f>'Proximal Validation'!L6</f>
         <v>0.47075057029724099</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="11"/>
+      <c r="M6" s="5">
+        <v>0.64434807120690019</v>
+      </c>
+      <c r="N6" s="5">
+        <v>8.4705518234087701E-2</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1.5888921182016253</v>
+      </c>
+      <c r="P6" s="11">
+        <v>1.6532907634860328E-3</v>
+      </c>
       <c r="Q6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>0.14434807120690019</v>
       </c>
       <c r="R6" s="5">
         <f t="shared" si="1"/>
-        <v>-0.1</v>
+        <v>-1.5294481765912304E-2</v>
       </c>
       <c r="S6" s="5">
         <f t="shared" si="1"/>
-        <v>-1.5707963267948966</v>
+        <v>1.8095791406728789E-2</v>
       </c>
       <c r="T6" s="5">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.14434807120690019</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>1.5294481765912304E-2</v>
       </c>
       <c r="V6" s="5">
         <f t="shared" si="0"/>
-        <v>1.5707963267948966</v>
+        <v>1.8095791406728789E-2</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -11743,29 +12784,29 @@
     <mergeCell ref="T25:V25"/>
     <mergeCell ref="W25:Y25"/>
     <mergeCell ref="W26:Y26"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="W13:Y13"/>
-    <mergeCell ref="W5:Y5"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="G20:L20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="M1:P1"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="W17:Y17"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="W1:Y1"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="T1:V1"/>
     <mergeCell ref="W14:Y14"/>
-    <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="W5:Y5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14295,7 +15336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2AD273E-DEC3-4584-9987-9255339758ED}">
   <dimension ref="D39:AU91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -18451,15 +19492,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
@@ -18467,7 +19499,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E12580AD17ADB64691A1BA4C2E042DA4" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6532fc6a52f3455fe895a4f720bca71c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xmlns:ns4="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d9a2f75daf18a7097de825f86ff3fec6" ns3:_="" ns4:_="">
     <xsd:import namespace="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8"/>
@@ -18720,15 +19752,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -18745,7 +19778,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65923CC5-95C4-4597-AADE-A0DCE38786F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18762,4 +19795,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>